--- a/myapp/data_sampling_2026.xlsx
+++ b/myapp/data_sampling_2026.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\PROJECT PAPER ANALISIS SENTIMEN 2026\Project Paper 1, Shopee\simpan\PROJECT PAPER UGI ANALISIS SENTIMEN SHOPEE 2023 SAMPAI 2026\Data Sampling 2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A09AC213-5401-44D8-94F5-9F17B3BC814A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E78AC454-199F-482F-813B-219C1CCBD650}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5306" uniqueCount="2947">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5955" uniqueCount="2947">
   <si>
     <t>userName</t>
   </si>
@@ -17118,7 +17118,9 @@
       <c r="G302" s="2">
         <v>4</v>
       </c>
-      <c r="H302" s="2"/>
+      <c r="H302" s="2" t="s">
+        <v>2945</v>
+      </c>
     </row>
     <row r="303" spans="1:8" ht="29" x14ac:dyDescent="0.35">
       <c r="A303" s="2" t="s">
@@ -17142,7 +17144,9 @@
       <c r="G303" s="2">
         <v>4</v>
       </c>
-      <c r="H303" s="2"/>
+      <c r="H303" s="2" t="s">
+        <v>2945</v>
+      </c>
     </row>
     <row r="304" spans="1:8" ht="29" x14ac:dyDescent="0.35">
       <c r="A304" s="2" t="s">
@@ -17166,7 +17170,9 @@
       <c r="G304" s="2">
         <v>4</v>
       </c>
-      <c r="H304" s="2"/>
+      <c r="H304" s="2" t="s">
+        <v>2946</v>
+      </c>
     </row>
     <row r="305" spans="1:8" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A305" s="2" t="s">
@@ -17190,7 +17196,9 @@
       <c r="G305" s="2">
         <v>4</v>
       </c>
-      <c r="H305" s="2"/>
+      <c r="H305" s="2" t="s">
+        <v>2946</v>
+      </c>
     </row>
     <row r="306" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A306" s="2" t="s">
@@ -17214,7 +17222,9 @@
       <c r="G306" s="2">
         <v>4</v>
       </c>
-      <c r="H306" s="2"/>
+      <c r="H306" s="2" t="s">
+        <v>2946</v>
+      </c>
     </row>
     <row r="307" spans="1:8" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A307" s="2" t="s">
@@ -17238,7 +17248,9 @@
       <c r="G307" s="2">
         <v>4</v>
       </c>
-      <c r="H307" s="2"/>
+      <c r="H307" s="2" t="s">
+        <v>2946</v>
+      </c>
     </row>
     <row r="308" spans="1:8" ht="29" x14ac:dyDescent="0.35">
       <c r="A308" s="2" t="s">
@@ -17262,7 +17274,9 @@
       <c r="G308" s="2">
         <v>4</v>
       </c>
-      <c r="H308" s="2"/>
+      <c r="H308" s="2" t="s">
+        <v>2946</v>
+      </c>
     </row>
     <row r="309" spans="1:8" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A309" s="2" t="s">
@@ -17286,7 +17300,9 @@
       <c r="G309" s="2">
         <v>4</v>
       </c>
-      <c r="H309" s="2"/>
+      <c r="H309" s="2" t="s">
+        <v>2946</v>
+      </c>
     </row>
     <row r="310" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A310" s="2" t="s">
@@ -17310,7 +17326,9 @@
       <c r="G310" s="2">
         <v>4</v>
       </c>
-      <c r="H310" s="2"/>
+      <c r="H310" s="2" t="s">
+        <v>2946</v>
+      </c>
     </row>
     <row r="311" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A311" s="2" t="s">
@@ -17334,7 +17352,9 @@
       <c r="G311" s="2">
         <v>4</v>
       </c>
-      <c r="H311" s="2"/>
+      <c r="H311" s="2" t="s">
+        <v>2945</v>
+      </c>
     </row>
     <row r="312" spans="1:8" ht="29" x14ac:dyDescent="0.35">
       <c r="A312" s="2" t="s">
@@ -17358,7 +17378,9 @@
       <c r="G312" s="2">
         <v>4</v>
       </c>
-      <c r="H312" s="2"/>
+      <c r="H312" s="2" t="s">
+        <v>2945</v>
+      </c>
     </row>
     <row r="313" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A313" s="2" t="s">
@@ -17382,7 +17404,9 @@
       <c r="G313" s="2">
         <v>4</v>
       </c>
-      <c r="H313" s="2"/>
+      <c r="H313" s="2" t="s">
+        <v>2945</v>
+      </c>
     </row>
     <row r="314" spans="1:8" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A314" s="2" t="s">
@@ -17406,7 +17430,9 @@
       <c r="G314" s="2">
         <v>4</v>
       </c>
-      <c r="H314" s="2"/>
+      <c r="H314" s="2" t="s">
+        <v>2946</v>
+      </c>
     </row>
     <row r="315" spans="1:8" ht="87" x14ac:dyDescent="0.35">
       <c r="A315" s="2" t="s">
@@ -17430,7 +17456,9 @@
       <c r="G315" s="2">
         <v>4</v>
       </c>
-      <c r="H315" s="2"/>
+      <c r="H315" s="2" t="s">
+        <v>2946</v>
+      </c>
     </row>
     <row r="316" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A316" s="2" t="s">
@@ -17454,7 +17482,9 @@
       <c r="G316" s="2">
         <v>4</v>
       </c>
-      <c r="H316" s="2"/>
+      <c r="H316" s="2" t="s">
+        <v>2945</v>
+      </c>
     </row>
     <row r="317" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A317" s="2" t="s">
@@ -17478,7 +17508,9 @@
       <c r="G317" s="2">
         <v>4</v>
       </c>
-      <c r="H317" s="2"/>
+      <c r="H317" s="2" t="s">
+        <v>2946</v>
+      </c>
     </row>
     <row r="318" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A318" s="2" t="s">
@@ -17502,7 +17534,9 @@
       <c r="G318" s="2">
         <v>4</v>
       </c>
-      <c r="H318" s="2"/>
+      <c r="H318" s="2" t="s">
+        <v>2945</v>
+      </c>
     </row>
     <row r="319" spans="1:8" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A319" s="2" t="s">
@@ -17526,7 +17560,9 @@
       <c r="G319" s="2">
         <v>4</v>
       </c>
-      <c r="H319" s="2"/>
+      <c r="H319" s="2" t="s">
+        <v>2946</v>
+      </c>
     </row>
     <row r="320" spans="1:8" ht="29" x14ac:dyDescent="0.35">
       <c r="A320" s="2" t="s">
@@ -17550,7 +17586,9 @@
       <c r="G320" s="2">
         <v>4</v>
       </c>
-      <c r="H320" s="2"/>
+      <c r="H320" s="2" t="s">
+        <v>2946</v>
+      </c>
     </row>
     <row r="321" spans="1:8" ht="87" x14ac:dyDescent="0.35">
       <c r="A321" s="2" t="s">
@@ -17574,7 +17612,9 @@
       <c r="G321" s="2">
         <v>4</v>
       </c>
-      <c r="H321" s="2"/>
+      <c r="H321" s="2" t="s">
+        <v>2946</v>
+      </c>
     </row>
     <row r="322" spans="1:8" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A322" s="2" t="s">
@@ -17598,7 +17638,9 @@
       <c r="G322" s="2">
         <v>4</v>
       </c>
-      <c r="H322" s="2"/>
+      <c r="H322" s="2" t="s">
+        <v>2946</v>
+      </c>
     </row>
     <row r="323" spans="1:8" ht="29" x14ac:dyDescent="0.35">
       <c r="A323" s="2" t="s">
@@ -17622,7 +17664,9 @@
       <c r="G323" s="2">
         <v>4</v>
       </c>
-      <c r="H323" s="2"/>
+      <c r="H323" s="2" t="s">
+        <v>2945</v>
+      </c>
     </row>
     <row r="324" spans="1:8" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A324" s="2" t="s">
@@ -17646,7 +17690,9 @@
       <c r="G324" s="2">
         <v>4</v>
       </c>
-      <c r="H324" s="2"/>
+      <c r="H324" s="2" t="s">
+        <v>2946</v>
+      </c>
     </row>
     <row r="325" spans="1:8" ht="58" x14ac:dyDescent="0.35">
       <c r="A325" s="2" t="s">
@@ -17670,7 +17716,9 @@
       <c r="G325" s="2">
         <v>4</v>
       </c>
-      <c r="H325" s="2"/>
+      <c r="H325" s="2" t="s">
+        <v>2946</v>
+      </c>
     </row>
     <row r="326" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A326" s="2" t="s">
@@ -17694,7 +17742,9 @@
       <c r="G326" s="2">
         <v>4</v>
       </c>
-      <c r="H326" s="2"/>
+      <c r="H326" s="2" t="s">
+        <v>2945</v>
+      </c>
     </row>
     <row r="327" spans="1:8" ht="29" x14ac:dyDescent="0.35">
       <c r="A327" s="2" t="s">
@@ -17718,7 +17768,9 @@
       <c r="G327" s="2">
         <v>4</v>
       </c>
-      <c r="H327" s="2"/>
+      <c r="H327" s="2" t="s">
+        <v>2946</v>
+      </c>
     </row>
     <row r="328" spans="1:8" ht="87" x14ac:dyDescent="0.35">
       <c r="A328" s="2" t="s">
@@ -17742,7 +17794,9 @@
       <c r="G328" s="2">
         <v>4</v>
       </c>
-      <c r="H328" s="2"/>
+      <c r="H328" s="2" t="s">
+        <v>2946</v>
+      </c>
     </row>
     <row r="329" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A329" s="2" t="s">
@@ -17766,7 +17820,9 @@
       <c r="G329" s="2">
         <v>4</v>
       </c>
-      <c r="H329" s="2"/>
+      <c r="H329" s="2" t="s">
+        <v>2945</v>
+      </c>
     </row>
     <row r="330" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A330" s="2" t="s">
@@ -17790,7 +17846,9 @@
       <c r="G330" s="2">
         <v>4</v>
       </c>
-      <c r="H330" s="2"/>
+      <c r="H330" s="2" t="s">
+        <v>2945</v>
+      </c>
     </row>
     <row r="331" spans="1:8" ht="29" x14ac:dyDescent="0.35">
       <c r="A331" s="2" t="s">
@@ -17814,7 +17872,9 @@
       <c r="G331" s="2">
         <v>4</v>
       </c>
-      <c r="H331" s="2"/>
+      <c r="H331" s="2" t="s">
+        <v>2945</v>
+      </c>
     </row>
     <row r="332" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A332" s="2" t="s">
@@ -17838,7 +17898,9 @@
       <c r="G332" s="2">
         <v>4</v>
       </c>
-      <c r="H332" s="2"/>
+      <c r="H332" s="2" t="s">
+        <v>2945</v>
+      </c>
     </row>
     <row r="333" spans="1:8" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A333" s="2" t="s">
@@ -17862,7 +17924,9 @@
       <c r="G333" s="2">
         <v>4</v>
       </c>
-      <c r="H333" s="2"/>
+      <c r="H333" s="2" t="s">
+        <v>2946</v>
+      </c>
     </row>
     <row r="334" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A334" s="2" t="s">
@@ -17886,7 +17950,9 @@
       <c r="G334" s="2">
         <v>4</v>
       </c>
-      <c r="H334" s="2"/>
+      <c r="H334" s="2" t="s">
+        <v>2946</v>
+      </c>
     </row>
     <row r="335" spans="1:8" ht="29" x14ac:dyDescent="0.35">
       <c r="A335" s="2" t="s">
@@ -17910,7 +17976,9 @@
       <c r="G335" s="2">
         <v>4</v>
       </c>
-      <c r="H335" s="2"/>
+      <c r="H335" s="2" t="s">
+        <v>2946</v>
+      </c>
     </row>
     <row r="336" spans="1:8" ht="29" x14ac:dyDescent="0.35">
       <c r="A336" s="2" t="s">
@@ -17934,7 +18002,9 @@
       <c r="G336" s="2">
         <v>4</v>
       </c>
-      <c r="H336" s="2"/>
+      <c r="H336" s="2" t="s">
+        <v>2945</v>
+      </c>
     </row>
     <row r="337" spans="1:8" ht="58" x14ac:dyDescent="0.35">
       <c r="A337" s="2" t="s">
@@ -17958,7 +18028,9 @@
       <c r="G337" s="2">
         <v>4</v>
       </c>
-      <c r="H337" s="2"/>
+      <c r="H337" s="2" t="s">
+        <v>2945</v>
+      </c>
     </row>
     <row r="338" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A338" s="2" t="s">
@@ -17982,7 +18054,9 @@
       <c r="G338" s="2">
         <v>4</v>
       </c>
-      <c r="H338" s="2"/>
+      <c r="H338" s="2" t="s">
+        <v>2946</v>
+      </c>
     </row>
     <row r="339" spans="1:8" ht="29" x14ac:dyDescent="0.35">
       <c r="A339" s="2" t="s">
@@ -18006,7 +18080,9 @@
       <c r="G339" s="2">
         <v>4</v>
       </c>
-      <c r="H339" s="2"/>
+      <c r="H339" s="2" t="s">
+        <v>2946</v>
+      </c>
     </row>
     <row r="340" spans="1:8" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A340" s="2" t="s">
@@ -18030,7 +18106,9 @@
       <c r="G340" s="2">
         <v>4</v>
       </c>
-      <c r="H340" s="2"/>
+      <c r="H340" s="2" t="s">
+        <v>2945</v>
+      </c>
     </row>
     <row r="341" spans="1:8" ht="58" x14ac:dyDescent="0.35">
       <c r="A341" s="2" t="s">
@@ -18054,7 +18132,9 @@
       <c r="G341" s="2">
         <v>4</v>
       </c>
-      <c r="H341" s="2"/>
+      <c r="H341" s="2" t="s">
+        <v>2946</v>
+      </c>
     </row>
     <row r="342" spans="1:8" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A342" s="2" t="s">
@@ -18078,7 +18158,9 @@
       <c r="G342" s="2">
         <v>4</v>
       </c>
-      <c r="H342" s="2"/>
+      <c r="H342" s="2" t="s">
+        <v>2946</v>
+      </c>
     </row>
     <row r="343" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A343" s="2" t="s">
@@ -18102,7 +18184,9 @@
       <c r="G343" s="2">
         <v>4</v>
       </c>
-      <c r="H343" s="2"/>
+      <c r="H343" s="2" t="s">
+        <v>2945</v>
+      </c>
     </row>
     <row r="344" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A344" s="2" t="s">
@@ -18126,7 +18210,9 @@
       <c r="G344" s="2">
         <v>4</v>
       </c>
-      <c r="H344" s="2"/>
+      <c r="H344" s="2" t="s">
+        <v>2945</v>
+      </c>
     </row>
     <row r="345" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A345" s="2" t="s">
@@ -18150,7 +18236,9 @@
       <c r="G345" s="2">
         <v>4</v>
       </c>
-      <c r="H345" s="2"/>
+      <c r="H345" s="2" t="s">
+        <v>2946</v>
+      </c>
     </row>
     <row r="346" spans="1:8" ht="29" x14ac:dyDescent="0.35">
       <c r="A346" s="2" t="s">
@@ -18174,7 +18262,9 @@
       <c r="G346" s="2">
         <v>4</v>
       </c>
-      <c r="H346" s="2"/>
+      <c r="H346" s="2" t="s">
+        <v>2946</v>
+      </c>
     </row>
     <row r="347" spans="1:8" ht="29" x14ac:dyDescent="0.35">
       <c r="A347" s="2" t="s">
@@ -18198,7 +18288,9 @@
       <c r="G347" s="2">
         <v>4</v>
       </c>
-      <c r="H347" s="2"/>
+      <c r="H347" s="2" t="s">
+        <v>2946</v>
+      </c>
     </row>
     <row r="348" spans="1:8" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A348" s="2" t="s">
@@ -18222,7 +18314,9 @@
       <c r="G348" s="2">
         <v>4</v>
       </c>
-      <c r="H348" s="2"/>
+      <c r="H348" s="2" t="s">
+        <v>2946</v>
+      </c>
     </row>
     <row r="349" spans="1:8" ht="29" x14ac:dyDescent="0.35">
       <c r="A349" s="2" t="s">
@@ -18246,7 +18340,9 @@
       <c r="G349" s="2">
         <v>4</v>
       </c>
-      <c r="H349" s="2"/>
+      <c r="H349" s="2" t="s">
+        <v>2945</v>
+      </c>
     </row>
     <row r="350" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A350" s="2" t="s">
@@ -18270,7 +18366,9 @@
       <c r="G350" s="2">
         <v>4</v>
       </c>
-      <c r="H350" s="2"/>
+      <c r="H350" s="2" t="s">
+        <v>2945</v>
+      </c>
     </row>
     <row r="351" spans="1:8" ht="87" x14ac:dyDescent="0.35">
       <c r="A351" s="2" t="s">
@@ -18294,7 +18392,9 @@
       <c r="G351" s="2">
         <v>4</v>
       </c>
-      <c r="H351" s="2"/>
+      <c r="H351" s="2" t="s">
+        <v>2946</v>
+      </c>
     </row>
     <row r="352" spans="1:8" ht="72.5" x14ac:dyDescent="0.35">
       <c r="A352" s="2" t="s">
@@ -18318,7 +18418,9 @@
       <c r="G352" s="2">
         <v>4</v>
       </c>
-      <c r="H352" s="2"/>
+      <c r="H352" s="2" t="s">
+        <v>2946</v>
+      </c>
     </row>
     <row r="353" spans="1:8" ht="29" x14ac:dyDescent="0.35">
       <c r="A353" s="2" t="s">
@@ -18342,7 +18444,9 @@
       <c r="G353" s="2">
         <v>4</v>
       </c>
-      <c r="H353" s="2"/>
+      <c r="H353" s="2" t="s">
+        <v>2945</v>
+      </c>
     </row>
     <row r="354" spans="1:8" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A354" s="2" t="s">
@@ -18366,7 +18470,9 @@
       <c r="G354" s="2">
         <v>4</v>
       </c>
-      <c r="H354" s="2"/>
+      <c r="H354" s="2" t="s">
+        <v>2946</v>
+      </c>
     </row>
     <row r="355" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A355" s="2" t="s">
@@ -18390,7 +18496,9 @@
       <c r="G355" s="2">
         <v>4</v>
       </c>
-      <c r="H355" s="2"/>
+      <c r="H355" s="2" t="s">
+        <v>2945</v>
+      </c>
     </row>
     <row r="356" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A356" s="2" t="s">
@@ -18414,7 +18522,9 @@
       <c r="G356" s="2">
         <v>4</v>
       </c>
-      <c r="H356" s="2"/>
+      <c r="H356" s="2" t="s">
+        <v>2946</v>
+      </c>
     </row>
     <row r="357" spans="1:8" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A357" s="2" t="s">
@@ -18438,7 +18548,9 @@
       <c r="G357" s="2">
         <v>4</v>
       </c>
-      <c r="H357" s="2"/>
+      <c r="H357" s="2" t="s">
+        <v>2946</v>
+      </c>
     </row>
     <row r="358" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A358" s="2" t="s">
@@ -18462,7 +18574,9 @@
       <c r="G358" s="2">
         <v>4</v>
       </c>
-      <c r="H358" s="2"/>
+      <c r="H358" s="2" t="s">
+        <v>2945</v>
+      </c>
     </row>
     <row r="359" spans="1:8" ht="29" x14ac:dyDescent="0.35">
       <c r="A359" s="2" t="s">
@@ -18486,7 +18600,9 @@
       <c r="G359" s="2">
         <v>4</v>
       </c>
-      <c r="H359" s="2"/>
+      <c r="H359" s="2" t="s">
+        <v>2945</v>
+      </c>
     </row>
     <row r="360" spans="1:8" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A360" s="2" t="s">
@@ -18510,7 +18626,9 @@
       <c r="G360" s="2">
         <v>4</v>
       </c>
-      <c r="H360" s="2"/>
+      <c r="H360" s="2" t="s">
+        <v>2946</v>
+      </c>
     </row>
     <row r="361" spans="1:8" ht="58" x14ac:dyDescent="0.35">
       <c r="A361" s="2" t="s">
@@ -18534,7 +18652,9 @@
       <c r="G361" s="2">
         <v>4</v>
       </c>
-      <c r="H361" s="2"/>
+      <c r="H361" s="2" t="s">
+        <v>2946</v>
+      </c>
     </row>
     <row r="362" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A362" s="2" t="s">
@@ -18558,7 +18678,9 @@
       <c r="G362" s="2">
         <v>4</v>
       </c>
-      <c r="H362" s="2"/>
+      <c r="H362" s="2" t="s">
+        <v>2945</v>
+      </c>
     </row>
     <row r="363" spans="1:8" ht="87" x14ac:dyDescent="0.35">
       <c r="A363" s="2" t="s">
@@ -18582,7 +18704,9 @@
       <c r="G363" s="2">
         <v>4</v>
       </c>
-      <c r="H363" s="2"/>
+      <c r="H363" s="2" t="s">
+        <v>2946</v>
+      </c>
     </row>
     <row r="364" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A364" s="2" t="s">
@@ -18606,7 +18730,9 @@
       <c r="G364" s="2">
         <v>4</v>
       </c>
-      <c r="H364" s="2"/>
+      <c r="H364" s="2" t="s">
+        <v>2945</v>
+      </c>
     </row>
     <row r="365" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A365" s="2" t="s">
@@ -18630,7 +18756,9 @@
       <c r="G365" s="2">
         <v>4</v>
       </c>
-      <c r="H365" s="2"/>
+      <c r="H365" s="2" t="s">
+        <v>2945</v>
+      </c>
     </row>
     <row r="366" spans="1:8" ht="29" x14ac:dyDescent="0.35">
       <c r="A366" s="2" t="s">
@@ -18654,7 +18782,9 @@
       <c r="G366" s="2">
         <v>4</v>
       </c>
-      <c r="H366" s="2"/>
+      <c r="H366" s="2" t="s">
+        <v>2946</v>
+      </c>
     </row>
     <row r="367" spans="1:8" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A367" s="2" t="s">
@@ -18678,7 +18808,9 @@
       <c r="G367" s="2">
         <v>4</v>
       </c>
-      <c r="H367" s="2"/>
+      <c r="H367" s="2" t="s">
+        <v>2946</v>
+      </c>
     </row>
     <row r="368" spans="1:8" ht="29" x14ac:dyDescent="0.35">
       <c r="A368" s="2" t="s">
@@ -18702,7 +18834,9 @@
       <c r="G368" s="2">
         <v>4</v>
       </c>
-      <c r="H368" s="2"/>
+      <c r="H368" s="2" t="s">
+        <v>2945</v>
+      </c>
     </row>
     <row r="369" spans="1:8" ht="29" x14ac:dyDescent="0.35">
       <c r="A369" s="2" t="s">
@@ -18726,7 +18860,9 @@
       <c r="G369" s="2">
         <v>4</v>
       </c>
-      <c r="H369" s="2"/>
+      <c r="H369" s="2" t="s">
+        <v>2946</v>
+      </c>
     </row>
     <row r="370" spans="1:8" ht="87" x14ac:dyDescent="0.35">
       <c r="A370" s="2" t="s">
@@ -18750,7 +18886,9 @@
       <c r="G370" s="2">
         <v>4</v>
       </c>
-      <c r="H370" s="2"/>
+      <c r="H370" s="2" t="s">
+        <v>2946</v>
+      </c>
     </row>
     <row r="371" spans="1:8" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A371" s="2" t="s">
@@ -18774,7 +18912,9 @@
       <c r="G371" s="2">
         <v>4</v>
       </c>
-      <c r="H371" s="2"/>
+      <c r="H371" s="2" t="s">
+        <v>2945</v>
+      </c>
     </row>
     <row r="372" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A372" s="2" t="s">
@@ -18798,7 +18938,9 @@
       <c r="G372" s="2">
         <v>4</v>
       </c>
-      <c r="H372" s="2"/>
+      <c r="H372" s="2" t="s">
+        <v>2946</v>
+      </c>
     </row>
     <row r="373" spans="1:8" ht="29" x14ac:dyDescent="0.35">
       <c r="A373" s="2" t="s">
@@ -18822,7 +18964,9 @@
       <c r="G373" s="2">
         <v>4</v>
       </c>
-      <c r="H373" s="2"/>
+      <c r="H373" s="2" t="s">
+        <v>2946</v>
+      </c>
     </row>
     <row r="374" spans="1:8" ht="29" x14ac:dyDescent="0.35">
       <c r="A374" s="2" t="s">
@@ -18846,7 +18990,9 @@
       <c r="G374" s="2">
         <v>4</v>
       </c>
-      <c r="H374" s="2"/>
+      <c r="H374" s="2" t="s">
+        <v>2945</v>
+      </c>
     </row>
     <row r="375" spans="1:8" ht="29" x14ac:dyDescent="0.35">
       <c r="A375" s="2" t="s">
@@ -18870,7 +19016,9 @@
       <c r="G375" s="2">
         <v>4</v>
       </c>
-      <c r="H375" s="2"/>
+      <c r="H375" s="2" t="s">
+        <v>2946</v>
+      </c>
     </row>
     <row r="376" spans="1:8" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A376" s="2" t="s">
@@ -18894,7 +19042,9 @@
       <c r="G376" s="2">
         <v>4</v>
       </c>
-      <c r="H376" s="2"/>
+      <c r="H376" s="2" t="s">
+        <v>2946</v>
+      </c>
     </row>
     <row r="377" spans="1:8" ht="29" x14ac:dyDescent="0.35">
       <c r="A377" s="2" t="s">
@@ -18918,7 +19068,9 @@
       <c r="G377" s="2">
         <v>4</v>
       </c>
-      <c r="H377" s="2"/>
+      <c r="H377" s="2" t="s">
+        <v>2945</v>
+      </c>
     </row>
     <row r="378" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A378" s="2" t="s">
@@ -18942,7 +19094,9 @@
       <c r="G378" s="2">
         <v>4</v>
       </c>
-      <c r="H378" s="2"/>
+      <c r="H378" s="2" t="s">
+        <v>2946</v>
+      </c>
     </row>
     <row r="379" spans="1:8" ht="29" x14ac:dyDescent="0.35">
       <c r="A379" s="2" t="s">
@@ -18966,7 +19120,9 @@
       <c r="G379" s="2">
         <v>4</v>
       </c>
-      <c r="H379" s="2"/>
+      <c r="H379" s="2" t="s">
+        <v>2946</v>
+      </c>
     </row>
     <row r="380" spans="1:8" ht="72.5" x14ac:dyDescent="0.35">
       <c r="A380" s="2" t="s">
@@ -18990,7 +19146,9 @@
       <c r="G380" s="2">
         <v>4</v>
       </c>
-      <c r="H380" s="2"/>
+      <c r="H380" s="2" t="s">
+        <v>2945</v>
+      </c>
     </row>
     <row r="381" spans="1:8" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A381" s="2" t="s">
@@ -19014,7 +19172,9 @@
       <c r="G381" s="2">
         <v>4</v>
       </c>
-      <c r="H381" s="2"/>
+      <c r="H381" s="2" t="s">
+        <v>2946</v>
+      </c>
     </row>
     <row r="382" spans="1:8" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A382" s="2" t="s">
@@ -19038,7 +19198,9 @@
       <c r="G382" s="2">
         <v>4</v>
       </c>
-      <c r="H382" s="2"/>
+      <c r="H382" s="2" t="s">
+        <v>2946</v>
+      </c>
     </row>
     <row r="383" spans="1:8" ht="58" x14ac:dyDescent="0.35">
       <c r="A383" s="2" t="s">
@@ -19062,7 +19224,9 @@
       <c r="G383" s="2">
         <v>4</v>
       </c>
-      <c r="H383" s="2"/>
+      <c r="H383" s="2" t="s">
+        <v>2946</v>
+      </c>
     </row>
     <row r="384" spans="1:8" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A384" s="2" t="s">
@@ -19086,7 +19250,9 @@
       <c r="G384" s="2">
         <v>4</v>
       </c>
-      <c r="H384" s="2"/>
+      <c r="H384" s="2" t="s">
+        <v>2945</v>
+      </c>
     </row>
     <row r="385" spans="1:8" ht="29" x14ac:dyDescent="0.35">
       <c r="A385" s="2" t="s">
@@ -19110,7 +19276,9 @@
       <c r="G385" s="2">
         <v>4</v>
       </c>
-      <c r="H385" s="2"/>
+      <c r="H385" s="2" t="s">
+        <v>2946</v>
+      </c>
     </row>
     <row r="386" spans="1:8" ht="29" x14ac:dyDescent="0.35">
       <c r="A386" s="2" t="s">
@@ -19134,7 +19302,9 @@
       <c r="G386" s="2">
         <v>4</v>
       </c>
-      <c r="H386" s="2"/>
+      <c r="H386" s="2" t="s">
+        <v>2946</v>
+      </c>
     </row>
     <row r="387" spans="1:8" ht="87" x14ac:dyDescent="0.35">
       <c r="A387" s="2" t="s">
@@ -19158,7 +19328,9 @@
       <c r="G387" s="2">
         <v>4</v>
       </c>
-      <c r="H387" s="2"/>
+      <c r="H387" s="2" t="s">
+        <v>2946</v>
+      </c>
     </row>
     <row r="388" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A388" s="2" t="s">
@@ -19182,7 +19354,9 @@
       <c r="G388" s="2">
         <v>4</v>
       </c>
-      <c r="H388" s="2"/>
+      <c r="H388" s="2" t="s">
+        <v>2945</v>
+      </c>
     </row>
     <row r="389" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A389" s="2" t="s">
@@ -19206,7 +19380,9 @@
       <c r="G389" s="2">
         <v>4</v>
       </c>
-      <c r="H389" s="2"/>
+      <c r="H389" s="2" t="s">
+        <v>2945</v>
+      </c>
     </row>
     <row r="390" spans="1:8" ht="87" x14ac:dyDescent="0.35">
       <c r="A390" s="2" t="s">
@@ -19230,7 +19406,9 @@
       <c r="G390" s="2">
         <v>4</v>
       </c>
-      <c r="H390" s="2"/>
+      <c r="H390" s="2" t="s">
+        <v>2946</v>
+      </c>
     </row>
     <row r="391" spans="1:8" ht="72.5" x14ac:dyDescent="0.35">
       <c r="A391" s="2" t="s">
@@ -19254,7 +19432,9 @@
       <c r="G391" s="2">
         <v>4</v>
       </c>
-      <c r="H391" s="2"/>
+      <c r="H391" s="2" t="s">
+        <v>2946</v>
+      </c>
     </row>
     <row r="392" spans="1:8" ht="29" x14ac:dyDescent="0.35">
       <c r="A392" s="2" t="s">
@@ -19278,7 +19458,9 @@
       <c r="G392" s="2">
         <v>4</v>
       </c>
-      <c r="H392" s="2"/>
+      <c r="H392" s="2" t="s">
+        <v>2945</v>
+      </c>
     </row>
     <row r="393" spans="1:8" ht="72.5" x14ac:dyDescent="0.35">
       <c r="A393" s="2" t="s">
@@ -19302,7 +19484,9 @@
       <c r="G393" s="2">
         <v>4</v>
       </c>
-      <c r="H393" s="2"/>
+      <c r="H393" s="2" t="s">
+        <v>2946</v>
+      </c>
     </row>
     <row r="394" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A394" s="2" t="s">
@@ -19326,7 +19510,9 @@
       <c r="G394" s="2">
         <v>4</v>
       </c>
-      <c r="H394" s="2"/>
+      <c r="H394" s="2" t="s">
+        <v>2946</v>
+      </c>
     </row>
     <row r="395" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A395" s="2" t="s">
@@ -19350,7 +19536,9 @@
       <c r="G395" s="2">
         <v>4</v>
       </c>
-      <c r="H395" s="2"/>
+      <c r="H395" s="2" t="s">
+        <v>2945</v>
+      </c>
     </row>
     <row r="396" spans="1:8" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A396" s="2" t="s">
@@ -19374,7 +19562,9 @@
       <c r="G396" s="2">
         <v>4</v>
       </c>
-      <c r="H396" s="2"/>
+      <c r="H396" s="2" t="s">
+        <v>2945</v>
+      </c>
     </row>
     <row r="397" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A397" s="2" t="s">
@@ -19398,7 +19588,9 @@
       <c r="G397" s="2">
         <v>4</v>
       </c>
-      <c r="H397" s="2"/>
+      <c r="H397" s="2" t="s">
+        <v>2945</v>
+      </c>
     </row>
     <row r="398" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A398" s="2" t="s">
@@ -19422,7 +19614,9 @@
       <c r="G398" s="2">
         <v>4</v>
       </c>
-      <c r="H398" s="2"/>
+      <c r="H398" s="2" t="s">
+        <v>2946</v>
+      </c>
     </row>
     <row r="399" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A399" s="2" t="s">
@@ -19446,7 +19640,9 @@
       <c r="G399" s="2">
         <v>4</v>
       </c>
-      <c r="H399" s="2"/>
+      <c r="H399" s="2" t="s">
+        <v>2945</v>
+      </c>
     </row>
     <row r="400" spans="1:8" ht="29" x14ac:dyDescent="0.35">
       <c r="A400" s="2" t="s">
@@ -19470,7 +19666,9 @@
       <c r="G400" s="2">
         <v>4</v>
       </c>
-      <c r="H400" s="2"/>
+      <c r="H400" s="2" t="s">
+        <v>2946</v>
+      </c>
     </row>
     <row r="401" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A401" s="2" t="s">
@@ -19494,7 +19692,9 @@
       <c r="G401" s="2">
         <v>4</v>
       </c>
-      <c r="H401" s="2"/>
+      <c r="H401" s="2" t="s">
+        <v>2946</v>
+      </c>
     </row>
     <row r="402" spans="1:8" ht="58" x14ac:dyDescent="0.35">
       <c r="A402" s="2" t="s">
@@ -19518,7 +19718,9 @@
       <c r="G402" s="2">
         <v>5</v>
       </c>
-      <c r="H402" s="2"/>
+      <c r="H402" s="2" t="s">
+        <v>2946</v>
+      </c>
     </row>
     <row r="403" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A403" s="2" t="s">
@@ -19542,7 +19744,9 @@
       <c r="G403" s="2">
         <v>5</v>
       </c>
-      <c r="H403" s="2"/>
+      <c r="H403" s="2" t="s">
+        <v>2945</v>
+      </c>
     </row>
     <row r="404" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A404" s="2" t="s">
@@ -19566,7 +19770,9 @@
       <c r="G404" s="2">
         <v>5</v>
       </c>
-      <c r="H404" s="2"/>
+      <c r="H404" s="2" t="s">
+        <v>2945</v>
+      </c>
     </row>
     <row r="405" spans="1:8" ht="58" x14ac:dyDescent="0.35">
       <c r="A405" s="2" t="s">
@@ -19590,7 +19796,9 @@
       <c r="G405" s="2">
         <v>5</v>
       </c>
-      <c r="H405" s="2"/>
+      <c r="H405" s="2" t="s">
+        <v>2946</v>
+      </c>
     </row>
     <row r="406" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A406" s="2" t="s">
@@ -19614,7 +19822,9 @@
       <c r="G406" s="2">
         <v>5</v>
       </c>
-      <c r="H406" s="2"/>
+      <c r="H406" s="2" t="s">
+        <v>2945</v>
+      </c>
     </row>
     <row r="407" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A407" s="2" t="s">
@@ -19638,7 +19848,9 @@
       <c r="G407" s="2">
         <v>5</v>
       </c>
-      <c r="H407" s="2"/>
+      <c r="H407" s="2" t="s">
+        <v>2945</v>
+      </c>
     </row>
     <row r="408" spans="1:8" ht="29" x14ac:dyDescent="0.35">
       <c r="A408" s="2" t="s">
@@ -19662,7 +19874,9 @@
       <c r="G408" s="2">
         <v>5</v>
       </c>
-      <c r="H408" s="2"/>
+      <c r="H408" s="2" t="s">
+        <v>2946</v>
+      </c>
     </row>
     <row r="409" spans="1:8" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A409" s="2" t="s">
@@ -19686,7 +19900,9 @@
       <c r="G409" s="2">
         <v>5</v>
       </c>
-      <c r="H409" s="2"/>
+      <c r="H409" s="2" t="s">
+        <v>2946</v>
+      </c>
     </row>
     <row r="410" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A410" s="2" t="s">
@@ -19710,7 +19926,9 @@
       <c r="G410" s="2">
         <v>5</v>
       </c>
-      <c r="H410" s="2"/>
+      <c r="H410" s="2" t="s">
+        <v>2946</v>
+      </c>
     </row>
     <row r="411" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A411" s="2" t="s">
@@ -19734,7 +19952,9 @@
       <c r="G411" s="2">
         <v>5</v>
       </c>
-      <c r="H411" s="2"/>
+      <c r="H411" s="2" t="s">
+        <v>2946</v>
+      </c>
     </row>
     <row r="412" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A412" s="2" t="s">
@@ -19758,7 +19978,9 @@
       <c r="G412" s="2">
         <v>5</v>
       </c>
-      <c r="H412" s="2"/>
+      <c r="H412" s="2" t="s">
+        <v>2945</v>
+      </c>
     </row>
     <row r="413" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A413" s="2" t="s">
@@ -19782,7 +20004,9 @@
       <c r="G413" s="2">
         <v>5</v>
       </c>
-      <c r="H413" s="2"/>
+      <c r="H413" s="2" t="s">
+        <v>2946</v>
+      </c>
     </row>
     <row r="414" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A414" s="2" t="s">
@@ -19806,7 +20030,9 @@
       <c r="G414" s="2">
         <v>5</v>
       </c>
-      <c r="H414" s="2"/>
+      <c r="H414" s="2" t="s">
+        <v>2946</v>
+      </c>
     </row>
     <row r="415" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A415" s="2" t="s">
@@ -19830,7 +20056,9 @@
       <c r="G415" s="2">
         <v>5</v>
       </c>
-      <c r="H415" s="2"/>
+      <c r="H415" s="2" t="s">
+        <v>2945</v>
+      </c>
     </row>
     <row r="416" spans="1:8" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A416" s="2" t="s">
@@ -19854,7 +20082,9 @@
       <c r="G416" s="2">
         <v>5</v>
       </c>
-      <c r="H416" s="2"/>
+      <c r="H416" s="2" t="s">
+        <v>2946</v>
+      </c>
     </row>
     <row r="417" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A417" s="2" t="s">
@@ -19878,7 +20108,9 @@
       <c r="G417" s="2">
         <v>5</v>
       </c>
-      <c r="H417" s="2"/>
+      <c r="H417" s="2" t="s">
+        <v>2945</v>
+      </c>
     </row>
     <row r="418" spans="1:8" ht="29" x14ac:dyDescent="0.35">
       <c r="A418" s="2" t="s">
@@ -19902,7 +20134,9 @@
       <c r="G418" s="2">
         <v>5</v>
       </c>
-      <c r="H418" s="2"/>
+      <c r="H418" s="2" t="s">
+        <v>2945</v>
+      </c>
     </row>
     <row r="419" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A419" s="2" t="s">
@@ -19926,7 +20160,9 @@
       <c r="G419" s="2">
         <v>5</v>
       </c>
-      <c r="H419" s="2"/>
+      <c r="H419" s="2" t="s">
+        <v>2945</v>
+      </c>
     </row>
     <row r="420" spans="1:8" ht="29" x14ac:dyDescent="0.35">
       <c r="A420" s="2" t="s">
@@ -19950,7 +20186,9 @@
       <c r="G420" s="2">
         <v>5</v>
       </c>
-      <c r="H420" s="2"/>
+      <c r="H420" s="2" t="s">
+        <v>2945</v>
+      </c>
     </row>
     <row r="421" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A421" s="2" t="s">
@@ -19974,7 +20212,9 @@
       <c r="G421" s="2">
         <v>5</v>
       </c>
-      <c r="H421" s="2"/>
+      <c r="H421" s="2" t="s">
+        <v>2945</v>
+      </c>
     </row>
     <row r="422" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A422" s="2" t="s">
@@ -19998,7 +20238,9 @@
       <c r="G422" s="2">
         <v>5</v>
       </c>
-      <c r="H422" s="2"/>
+      <c r="H422" s="2" t="s">
+        <v>2946</v>
+      </c>
     </row>
     <row r="423" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A423" s="2" t="s">
@@ -20022,7 +20264,9 @@
       <c r="G423" s="2">
         <v>5</v>
       </c>
-      <c r="H423" s="2"/>
+      <c r="H423" s="2" t="s">
+        <v>2946</v>
+      </c>
     </row>
     <row r="424" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A424" s="2" t="s">
@@ -20046,7 +20290,9 @@
       <c r="G424" s="2">
         <v>5</v>
       </c>
-      <c r="H424" s="2"/>
+      <c r="H424" s="2" t="s">
+        <v>2945</v>
+      </c>
     </row>
     <row r="425" spans="1:8" ht="87" x14ac:dyDescent="0.35">
       <c r="A425" s="2" t="s">
@@ -20070,7 +20316,9 @@
       <c r="G425" s="2">
         <v>5</v>
       </c>
-      <c r="H425" s="2"/>
+      <c r="H425" s="2" t="s">
+        <v>2946</v>
+      </c>
     </row>
     <row r="426" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A426" s="2" t="s">
@@ -20094,7 +20342,9 @@
       <c r="G426" s="2">
         <v>5</v>
       </c>
-      <c r="H426" s="2"/>
+      <c r="H426" s="2" t="s">
+        <v>2945</v>
+      </c>
     </row>
     <row r="427" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A427" s="2" t="s">
@@ -20118,7 +20368,9 @@
       <c r="G427" s="2">
         <v>5</v>
       </c>
-      <c r="H427" s="2"/>
+      <c r="H427" s="2" t="s">
+        <v>2946</v>
+      </c>
     </row>
     <row r="428" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A428" s="2" t="s">
@@ -20142,7 +20394,9 @@
       <c r="G428" s="2">
         <v>5</v>
       </c>
-      <c r="H428" s="2"/>
+      <c r="H428" s="2" t="s">
+        <v>2946</v>
+      </c>
     </row>
     <row r="429" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A429" s="2" t="s">
@@ -20166,7 +20420,9 @@
       <c r="G429" s="2">
         <v>5</v>
       </c>
-      <c r="H429" s="2"/>
+      <c r="H429" s="2" t="s">
+        <v>2945</v>
+      </c>
     </row>
     <row r="430" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A430" s="2" t="s">
@@ -20190,7 +20446,9 @@
       <c r="G430" s="2">
         <v>5</v>
       </c>
-      <c r="H430" s="2"/>
+      <c r="H430" s="2">
+        <v>0</v>
+      </c>
     </row>
     <row r="431" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A431" s="2" t="s">
@@ -20214,7 +20472,9 @@
       <c r="G431" s="2">
         <v>5</v>
       </c>
-      <c r="H431" s="2"/>
+      <c r="H431" s="2" t="s">
+        <v>2945</v>
+      </c>
     </row>
     <row r="432" spans="1:8" ht="58" x14ac:dyDescent="0.35">
       <c r="A432" s="2" t="s">
@@ -20238,7 +20498,9 @@
       <c r="G432" s="2">
         <v>5</v>
       </c>
-      <c r="H432" s="2"/>
+      <c r="H432" s="2" t="s">
+        <v>2946</v>
+      </c>
     </row>
     <row r="433" spans="1:8" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A433" s="2" t="s">
@@ -20262,7 +20524,9 @@
       <c r="G433" s="2">
         <v>5</v>
       </c>
-      <c r="H433" s="2"/>
+      <c r="H433" s="2" t="s">
+        <v>2946</v>
+      </c>
     </row>
     <row r="434" spans="1:8" ht="29" x14ac:dyDescent="0.35">
       <c r="A434" s="2" t="s">
@@ -20286,7 +20550,9 @@
       <c r="G434" s="2">
         <v>5</v>
       </c>
-      <c r="H434" s="2"/>
+      <c r="H434" s="2" t="s">
+        <v>2945</v>
+      </c>
     </row>
     <row r="435" spans="1:8" ht="29" x14ac:dyDescent="0.35">
       <c r="A435" s="2" t="s">
@@ -20310,7 +20576,9 @@
       <c r="G435" s="2">
         <v>5</v>
       </c>
-      <c r="H435" s="2"/>
+      <c r="H435" s="2" t="s">
+        <v>2946</v>
+      </c>
     </row>
     <row r="436" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A436" s="2" t="s">
@@ -20334,7 +20602,9 @@
       <c r="G436" s="2">
         <v>5</v>
       </c>
-      <c r="H436" s="2"/>
+      <c r="H436" s="2" t="s">
+        <v>2946</v>
+      </c>
     </row>
     <row r="437" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A437" s="2" t="s">
@@ -20358,7 +20628,9 @@
       <c r="G437" s="2">
         <v>5</v>
       </c>
-      <c r="H437" s="2"/>
+      <c r="H437" s="2" t="s">
+        <v>2945</v>
+      </c>
     </row>
     <row r="438" spans="1:8" ht="72.5" x14ac:dyDescent="0.35">
       <c r="A438" s="2" t="s">
@@ -20382,7 +20654,9 @@
       <c r="G438" s="2">
         <v>5</v>
       </c>
-      <c r="H438" s="2"/>
+      <c r="H438" s="2" t="s">
+        <v>2945</v>
+      </c>
     </row>
     <row r="439" spans="1:8" ht="29" x14ac:dyDescent="0.35">
       <c r="A439" s="2" t="s">
@@ -20406,7 +20680,9 @@
       <c r="G439" s="2">
         <v>5</v>
       </c>
-      <c r="H439" s="2"/>
+      <c r="H439" s="2" t="s">
+        <v>2946</v>
+      </c>
     </row>
     <row r="440" spans="1:8" ht="29" x14ac:dyDescent="0.35">
       <c r="A440" s="2" t="s">
@@ -20430,7 +20706,9 @@
       <c r="G440" s="2">
         <v>5</v>
       </c>
-      <c r="H440" s="2"/>
+      <c r="H440" s="2" t="s">
+        <v>2945</v>
+      </c>
     </row>
     <row r="441" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A441" s="2" t="s">
@@ -20454,7 +20732,9 @@
       <c r="G441" s="2">
         <v>5</v>
       </c>
-      <c r="H441" s="2"/>
+      <c r="H441" s="2" t="s">
+        <v>2945</v>
+      </c>
     </row>
     <row r="442" spans="1:8" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A442" s="2" t="s">
@@ -20478,7 +20758,9 @@
       <c r="G442" s="2">
         <v>5</v>
       </c>
-      <c r="H442" s="2"/>
+      <c r="H442" s="2" t="s">
+        <v>2945</v>
+      </c>
     </row>
     <row r="443" spans="1:8" ht="29" x14ac:dyDescent="0.35">
       <c r="A443" s="2" t="s">
@@ -20502,7 +20784,9 @@
       <c r="G443" s="2">
         <v>5</v>
       </c>
-      <c r="H443" s="2"/>
+      <c r="H443" s="2" t="s">
+        <v>2946</v>
+      </c>
     </row>
     <row r="444" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A444" s="2" t="s">
@@ -20526,7 +20810,9 @@
       <c r="G444" s="2">
         <v>5</v>
       </c>
-      <c r="H444" s="2"/>
+      <c r="H444" s="2" t="s">
+        <v>2946</v>
+      </c>
     </row>
     <row r="445" spans="1:8" ht="29" x14ac:dyDescent="0.35">
       <c r="A445" s="2" t="s">
@@ -20550,7 +20836,9 @@
       <c r="G445" s="2">
         <v>5</v>
       </c>
-      <c r="H445" s="2"/>
+      <c r="H445" s="2" t="s">
+        <v>2945</v>
+      </c>
     </row>
     <row r="446" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A446" s="2" t="s">
@@ -20574,7 +20862,9 @@
       <c r="G446" s="2">
         <v>5</v>
       </c>
-      <c r="H446" s="2"/>
+      <c r="H446" s="2" t="s">
+        <v>2945</v>
+      </c>
     </row>
     <row r="447" spans="1:8" ht="58" x14ac:dyDescent="0.35">
       <c r="A447" s="2" t="s">
@@ -20598,7 +20888,9 @@
       <c r="G447" s="2">
         <v>5</v>
       </c>
-      <c r="H447" s="2"/>
+      <c r="H447" s="2" t="s">
+        <v>2946</v>
+      </c>
     </row>
     <row r="448" spans="1:8" ht="29" x14ac:dyDescent="0.35">
       <c r="A448" s="2" t="s">
@@ -20622,7 +20914,9 @@
       <c r="G448" s="2">
         <v>5</v>
       </c>
-      <c r="H448" s="2"/>
+      <c r="H448" s="2" t="s">
+        <v>2945</v>
+      </c>
     </row>
     <row r="449" spans="1:8" ht="29" x14ac:dyDescent="0.35">
       <c r="A449" s="2" t="s">
@@ -20646,7 +20940,9 @@
       <c r="G449" s="2">
         <v>5</v>
       </c>
-      <c r="H449" s="2"/>
+      <c r="H449" s="2" t="s">
+        <v>2946</v>
+      </c>
     </row>
     <row r="450" spans="1:8" ht="29" x14ac:dyDescent="0.35">
       <c r="A450" s="2" t="s">
@@ -20670,7 +20966,9 @@
       <c r="G450" s="2">
         <v>5</v>
       </c>
-      <c r="H450" s="2"/>
+      <c r="H450" s="2" t="s">
+        <v>2946</v>
+      </c>
     </row>
     <row r="451" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A451" s="2" t="s">
@@ -20694,7 +20992,9 @@
       <c r="G451" s="2">
         <v>5</v>
       </c>
-      <c r="H451" s="2"/>
+      <c r="H451" s="2">
+        <v>0</v>
+      </c>
     </row>
     <row r="452" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A452" s="2" t="s">
@@ -20718,7 +21018,9 @@
       <c r="G452" s="2">
         <v>5</v>
       </c>
-      <c r="H452" s="2"/>
+      <c r="H452" s="2" t="s">
+        <v>2946</v>
+      </c>
     </row>
     <row r="453" spans="1:8" ht="29" x14ac:dyDescent="0.35">
       <c r="A453" s="2" t="s">
@@ -20742,7 +21044,9 @@
       <c r="G453" s="2">
         <v>5</v>
       </c>
-      <c r="H453" s="2"/>
+      <c r="H453" s="2" t="s">
+        <v>2945</v>
+      </c>
     </row>
     <row r="454" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A454" s="2" t="s">
@@ -20766,7 +21070,9 @@
       <c r="G454" s="2">
         <v>5</v>
       </c>
-      <c r="H454" s="2"/>
+      <c r="H454" s="2" t="s">
+        <v>2946</v>
+      </c>
     </row>
     <row r="455" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A455" s="2" t="s">
@@ -20790,7 +21096,9 @@
       <c r="G455" s="2">
         <v>5</v>
       </c>
-      <c r="H455" s="2"/>
+      <c r="H455" s="2" t="s">
+        <v>2945</v>
+      </c>
     </row>
     <row r="456" spans="1:8" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A456" s="2" t="s">
@@ -20814,7 +21122,9 @@
       <c r="G456" s="2">
         <v>5</v>
       </c>
-      <c r="H456" s="2"/>
+      <c r="H456" s="2" t="s">
+        <v>2946</v>
+      </c>
     </row>
     <row r="457" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A457" s="2" t="s">
@@ -20838,7 +21148,9 @@
       <c r="G457" s="2">
         <v>5</v>
       </c>
-      <c r="H457" s="2"/>
+      <c r="H457" s="2" t="s">
+        <v>2945</v>
+      </c>
     </row>
     <row r="458" spans="1:8" ht="58" x14ac:dyDescent="0.35">
       <c r="A458" s="2" t="s">
@@ -20862,7 +21174,9 @@
       <c r="G458" s="2">
         <v>5</v>
       </c>
-      <c r="H458" s="2"/>
+      <c r="H458" s="2" t="s">
+        <v>2946</v>
+      </c>
     </row>
     <row r="459" spans="1:8" ht="72.5" x14ac:dyDescent="0.35">
       <c r="A459" s="2" t="s">
@@ -20886,7 +21200,9 @@
       <c r="G459" s="2">
         <v>5</v>
       </c>
-      <c r="H459" s="2"/>
+      <c r="H459" s="2" t="s">
+        <v>2946</v>
+      </c>
     </row>
     <row r="460" spans="1:8" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A460" s="2" t="s">
@@ -20910,7 +21226,9 @@
       <c r="G460" s="2">
         <v>5</v>
       </c>
-      <c r="H460" s="2"/>
+      <c r="H460" s="2" t="s">
+        <v>2946</v>
+      </c>
     </row>
     <row r="461" spans="1:8" ht="29" x14ac:dyDescent="0.35">
       <c r="A461" s="2" t="s">
@@ -20934,7 +21252,9 @@
       <c r="G461" s="2">
         <v>5</v>
       </c>
-      <c r="H461" s="2"/>
+      <c r="H461" s="2" t="s">
+        <v>2946</v>
+      </c>
     </row>
     <row r="462" spans="1:8" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A462" s="2" t="s">
@@ -20958,7 +21278,9 @@
       <c r="G462" s="2">
         <v>5</v>
       </c>
-      <c r="H462" s="2"/>
+      <c r="H462" s="2" t="s">
+        <v>2946</v>
+      </c>
     </row>
     <row r="463" spans="1:8" ht="29" x14ac:dyDescent="0.35">
       <c r="A463" s="2" t="s">
@@ -20982,7 +21304,9 @@
       <c r="G463" s="2">
         <v>5</v>
       </c>
-      <c r="H463" s="2"/>
+      <c r="H463" s="2" t="s">
+        <v>2946</v>
+      </c>
     </row>
     <row r="464" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A464" s="2" t="s">
@@ -21006,7 +21330,9 @@
       <c r="G464" s="2">
         <v>5</v>
       </c>
-      <c r="H464" s="2"/>
+      <c r="H464" s="2" t="s">
+        <v>2945</v>
+      </c>
     </row>
     <row r="465" spans="1:8" ht="29" x14ac:dyDescent="0.35">
       <c r="A465" s="2" t="s">
@@ -21030,7 +21356,9 @@
       <c r="G465" s="2">
         <v>5</v>
       </c>
-      <c r="H465" s="2"/>
+      <c r="H465" s="2" t="s">
+        <v>2945</v>
+      </c>
     </row>
     <row r="466" spans="1:8" ht="29" x14ac:dyDescent="0.35">
       <c r="A466" s="2" t="s">
@@ -21054,7 +21382,9 @@
       <c r="G466" s="2">
         <v>5</v>
       </c>
-      <c r="H466" s="2"/>
+      <c r="H466" s="2" t="s">
+        <v>2946</v>
+      </c>
     </row>
     <row r="467" spans="1:8" ht="29" x14ac:dyDescent="0.35">
       <c r="A467" s="2" t="s">
@@ -21078,7 +21408,9 @@
       <c r="G467" s="2">
         <v>5</v>
       </c>
-      <c r="H467" s="2"/>
+      <c r="H467" s="2" t="s">
+        <v>2945</v>
+      </c>
     </row>
     <row r="468" spans="1:8" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A468" s="2" t="s">
@@ -21102,7 +21434,9 @@
       <c r="G468" s="2">
         <v>5</v>
       </c>
-      <c r="H468" s="2"/>
+      <c r="H468" s="2" t="s">
+        <v>2946</v>
+      </c>
     </row>
     <row r="469" spans="1:8" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A469" s="2" t="s">
@@ -21126,7 +21460,9 @@
       <c r="G469" s="2">
         <v>5</v>
       </c>
-      <c r="H469" s="2"/>
+      <c r="H469" s="2" t="s">
+        <v>2946</v>
+      </c>
     </row>
     <row r="470" spans="1:8" ht="58" x14ac:dyDescent="0.35">
       <c r="A470" s="2" t="s">
@@ -21150,7 +21486,9 @@
       <c r="G470" s="2">
         <v>5</v>
       </c>
-      <c r="H470" s="2"/>
+      <c r="H470" s="2" t="s">
+        <v>2946</v>
+      </c>
     </row>
     <row r="471" spans="1:8" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A471" s="2" t="s">
@@ -21174,7 +21512,9 @@
       <c r="G471" s="2">
         <v>5</v>
       </c>
-      <c r="H471" s="2"/>
+      <c r="H471" s="2" t="s">
+        <v>2946</v>
+      </c>
     </row>
     <row r="472" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A472" s="2" t="s">
@@ -21198,7 +21538,9 @@
       <c r="G472" s="2">
         <v>5</v>
       </c>
-      <c r="H472" s="2"/>
+      <c r="H472" s="2">
+        <v>0</v>
+      </c>
     </row>
     <row r="473" spans="1:8" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A473" s="2" t="s">
@@ -21222,7 +21564,9 @@
       <c r="G473" s="2">
         <v>5</v>
       </c>
-      <c r="H473" s="2"/>
+      <c r="H473" s="2" t="s">
+        <v>2946</v>
+      </c>
     </row>
     <row r="474" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A474" s="2" t="s">
@@ -21246,7 +21590,9 @@
       <c r="G474" s="2">
         <v>5</v>
       </c>
-      <c r="H474" s="2"/>
+      <c r="H474" s="2" t="s">
+        <v>2945</v>
+      </c>
     </row>
     <row r="475" spans="1:8" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A475" s="2" t="s">
@@ -21270,7 +21616,9 @@
       <c r="G475" s="2">
         <v>5</v>
       </c>
-      <c r="H475" s="2"/>
+      <c r="H475" s="2" t="s">
+        <v>2946</v>
+      </c>
     </row>
     <row r="476" spans="1:8" ht="29" x14ac:dyDescent="0.35">
       <c r="A476" s="2" t="s">
@@ -21294,7 +21642,9 @@
       <c r="G476" s="2">
         <v>5</v>
       </c>
-      <c r="H476" s="2"/>
+      <c r="H476" s="2" t="s">
+        <v>2946</v>
+      </c>
     </row>
     <row r="477" spans="1:8" ht="29" x14ac:dyDescent="0.35">
       <c r="A477" s="2" t="s">
@@ -21318,7 +21668,9 @@
       <c r="G477" s="2">
         <v>5</v>
       </c>
-      <c r="H477" s="2"/>
+      <c r="H477" s="2" t="s">
+        <v>2946</v>
+      </c>
     </row>
     <row r="478" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A478" s="2" t="s">
@@ -21342,7 +21694,9 @@
       <c r="G478" s="2">
         <v>5</v>
       </c>
-      <c r="H478" s="2"/>
+      <c r="H478" s="2" t="s">
+        <v>2946</v>
+      </c>
     </row>
     <row r="479" spans="1:8" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A479" s="2" t="s">
@@ -21366,7 +21720,9 @@
       <c r="G479" s="2">
         <v>5</v>
       </c>
-      <c r="H479" s="2"/>
+      <c r="H479" s="2" t="s">
+        <v>2946</v>
+      </c>
     </row>
     <row r="480" spans="1:8" ht="29" x14ac:dyDescent="0.35">
       <c r="A480" s="2" t="s">
@@ -21390,7 +21746,9 @@
       <c r="G480" s="2">
         <v>5</v>
       </c>
-      <c r="H480" s="2"/>
+      <c r="H480" s="2" t="s">
+        <v>2946</v>
+      </c>
     </row>
     <row r="481" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A481" s="2" t="s">
@@ -21414,7 +21772,9 @@
       <c r="G481" s="2">
         <v>5</v>
       </c>
-      <c r="H481" s="2"/>
+      <c r="H481" s="2" t="s">
+        <v>2946</v>
+      </c>
     </row>
     <row r="482" spans="1:8" ht="29" x14ac:dyDescent="0.35">
       <c r="A482" s="2" t="s">
@@ -21438,7 +21798,9 @@
       <c r="G482" s="2">
         <v>5</v>
       </c>
-      <c r="H482" s="2"/>
+      <c r="H482" s="2" t="s">
+        <v>2946</v>
+      </c>
     </row>
     <row r="483" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A483" s="2" t="s">
@@ -21462,7 +21824,9 @@
       <c r="G483" s="2">
         <v>5</v>
       </c>
-      <c r="H483" s="2"/>
+      <c r="H483" s="2" t="s">
+        <v>2946</v>
+      </c>
     </row>
     <row r="484" spans="1:8" ht="29" x14ac:dyDescent="0.35">
       <c r="A484" s="2" t="s">
@@ -21486,7 +21850,9 @@
       <c r="G484" s="2">
         <v>5</v>
       </c>
-      <c r="H484" s="2"/>
+      <c r="H484" s="2" t="s">
+        <v>2946</v>
+      </c>
     </row>
     <row r="485" spans="1:8" ht="29" x14ac:dyDescent="0.35">
       <c r="A485" s="2" t="s">
@@ -21510,7 +21876,9 @@
       <c r="G485" s="2">
         <v>5</v>
       </c>
-      <c r="H485" s="2"/>
+      <c r="H485" s="2" t="s">
+        <v>2946</v>
+      </c>
     </row>
     <row r="486" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A486" s="2" t="s">
@@ -21534,7 +21902,9 @@
       <c r="G486" s="2">
         <v>5</v>
       </c>
-      <c r="H486" s="2"/>
+      <c r="H486" s="2" t="s">
+        <v>2945</v>
+      </c>
     </row>
     <row r="487" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A487" s="2" t="s">
@@ -21558,7 +21928,9 @@
       <c r="G487" s="2">
         <v>5</v>
       </c>
-      <c r="H487" s="2"/>
+      <c r="H487" s="2" t="s">
+        <v>2945</v>
+      </c>
     </row>
     <row r="488" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A488" s="2" t="s">
@@ -21582,7 +21954,9 @@
       <c r="G488" s="2">
         <v>5</v>
       </c>
-      <c r="H488" s="2"/>
+      <c r="H488" s="2" t="s">
+        <v>2945</v>
+      </c>
     </row>
     <row r="489" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A489" s="2" t="s">
@@ -21606,7 +21980,9 @@
       <c r="G489" s="2">
         <v>5</v>
       </c>
-      <c r="H489" s="2"/>
+      <c r="H489" s="2" t="s">
+        <v>2945</v>
+      </c>
     </row>
     <row r="490" spans="1:8" ht="29" x14ac:dyDescent="0.35">
       <c r="A490" s="2" t="s">
@@ -21630,7 +22006,9 @@
       <c r="G490" s="2">
         <v>5</v>
       </c>
-      <c r="H490" s="2"/>
+      <c r="H490" s="2">
+        <v>0</v>
+      </c>
     </row>
     <row r="491" spans="1:8" ht="29" x14ac:dyDescent="0.35">
       <c r="A491" s="2" t="s">
@@ -21654,7 +22032,9 @@
       <c r="G491" s="2">
         <v>5</v>
       </c>
-      <c r="H491" s="2"/>
+      <c r="H491" s="2" t="s">
+        <v>2946</v>
+      </c>
     </row>
     <row r="492" spans="1:8" ht="29" x14ac:dyDescent="0.35">
       <c r="A492" s="2" t="s">
@@ -21678,7 +22058,9 @@
       <c r="G492" s="2">
         <v>5</v>
       </c>
-      <c r="H492" s="2"/>
+      <c r="H492" s="2" t="s">
+        <v>2946</v>
+      </c>
     </row>
     <row r="493" spans="1:8" ht="58" x14ac:dyDescent="0.35">
       <c r="A493" s="2" t="s">
@@ -21702,7 +22084,9 @@
       <c r="G493" s="2">
         <v>5</v>
       </c>
-      <c r="H493" s="2"/>
+      <c r="H493" s="2" t="s">
+        <v>2946</v>
+      </c>
     </row>
     <row r="494" spans="1:8" ht="58" x14ac:dyDescent="0.35">
       <c r="A494" s="2" t="s">
@@ -21726,7 +22110,9 @@
       <c r="G494" s="2">
         <v>5</v>
       </c>
-      <c r="H494" s="2"/>
+      <c r="H494" s="2" t="s">
+        <v>2945</v>
+      </c>
     </row>
     <row r="495" spans="1:8" ht="29" x14ac:dyDescent="0.35">
       <c r="A495" s="2" t="s">
@@ -21750,7 +22136,9 @@
       <c r="G495" s="2">
         <v>5</v>
       </c>
-      <c r="H495" s="2"/>
+      <c r="H495" s="2" t="s">
+        <v>2945</v>
+      </c>
     </row>
     <row r="496" spans="1:8" ht="58" x14ac:dyDescent="0.35">
       <c r="A496" s="2" t="s">
@@ -21774,7 +22162,9 @@
       <c r="G496" s="2">
         <v>5</v>
       </c>
-      <c r="H496" s="2"/>
+      <c r="H496" s="2" t="s">
+        <v>2946</v>
+      </c>
     </row>
     <row r="497" spans="1:8" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A497" s="2" t="s">
@@ -21798,7 +22188,9 @@
       <c r="G497" s="2">
         <v>5</v>
       </c>
-      <c r="H497" s="2"/>
+      <c r="H497" s="2" t="s">
+        <v>2946</v>
+      </c>
     </row>
     <row r="498" spans="1:8" ht="29" x14ac:dyDescent="0.35">
       <c r="A498" s="2" t="s">
@@ -21822,7 +22214,9 @@
       <c r="G498" s="2">
         <v>5</v>
       </c>
-      <c r="H498" s="2"/>
+      <c r="H498" s="2" t="s">
+        <v>2945</v>
+      </c>
     </row>
     <row r="499" spans="1:8" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A499" s="2" t="s">
@@ -21846,7 +22240,9 @@
       <c r="G499" s="2">
         <v>5</v>
       </c>
-      <c r="H499" s="2"/>
+      <c r="H499" s="2" t="s">
+        <v>2945</v>
+      </c>
     </row>
     <row r="500" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A500" s="2" t="s">
@@ -21870,7 +22266,9 @@
       <c r="G500" s="2">
         <v>5</v>
       </c>
-      <c r="H500" s="2"/>
+      <c r="H500" s="2" t="s">
+        <v>2946</v>
+      </c>
     </row>
     <row r="501" spans="1:8" ht="29" x14ac:dyDescent="0.35">
       <c r="A501" s="2" t="s">
@@ -21894,7 +22292,9 @@
       <c r="G501" s="2">
         <v>5</v>
       </c>
-      <c r="H501" s="2"/>
+      <c r="H501" s="2" t="s">
+        <v>2946</v>
+      </c>
     </row>
     <row r="502" spans="1:8" ht="29" x14ac:dyDescent="0.35">
       <c r="A502" s="2" t="s">
@@ -21918,7 +22318,9 @@
       <c r="G502" s="2">
         <v>6</v>
       </c>
-      <c r="H502" s="2"/>
+      <c r="H502" s="2" t="s">
+        <v>2945</v>
+      </c>
     </row>
     <row r="503" spans="1:8" ht="87" x14ac:dyDescent="0.35">
       <c r="A503" s="2" t="s">
@@ -21942,7 +22344,9 @@
       <c r="G503" s="2">
         <v>6</v>
       </c>
-      <c r="H503" s="2"/>
+      <c r="H503" s="2" t="s">
+        <v>2946</v>
+      </c>
     </row>
     <row r="504" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A504" s="2" t="s">
@@ -21966,7 +22370,9 @@
       <c r="G504" s="2">
         <v>6</v>
       </c>
-      <c r="H504" s="2"/>
+      <c r="H504" s="2" t="s">
+        <v>2945</v>
+      </c>
     </row>
     <row r="505" spans="1:8" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A505" s="2" t="s">
@@ -21990,7 +22396,9 @@
       <c r="G505" s="2">
         <v>6</v>
       </c>
-      <c r="H505" s="2"/>
+      <c r="H505" s="2" t="s">
+        <v>2946</v>
+      </c>
     </row>
     <row r="506" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A506" s="2" t="s">
@@ -22014,7 +22422,9 @@
       <c r="G506" s="2">
         <v>6</v>
       </c>
-      <c r="H506" s="2"/>
+      <c r="H506" s="2" t="s">
+        <v>2946</v>
+      </c>
     </row>
     <row r="507" spans="1:8" ht="29" x14ac:dyDescent="0.35">
       <c r="A507" s="2" t="s">
@@ -22038,7 +22448,9 @@
       <c r="G507" s="2">
         <v>6</v>
       </c>
-      <c r="H507" s="2"/>
+      <c r="H507" s="2" t="s">
+        <v>2946</v>
+      </c>
     </row>
     <row r="508" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A508" s="2" t="s">
@@ -22062,7 +22474,9 @@
       <c r="G508" s="2">
         <v>6</v>
       </c>
-      <c r="H508" s="2"/>
+      <c r="H508" s="2" t="s">
+        <v>2946</v>
+      </c>
     </row>
     <row r="509" spans="1:8" ht="29" x14ac:dyDescent="0.35">
       <c r="A509" s="2" t="s">
@@ -22086,7 +22500,9 @@
       <c r="G509" s="2">
         <v>6</v>
       </c>
-      <c r="H509" s="2"/>
+      <c r="H509" s="2" t="s">
+        <v>2946</v>
+      </c>
     </row>
     <row r="510" spans="1:8" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A510" s="2" t="s">
@@ -22110,7 +22526,9 @@
       <c r="G510" s="2">
         <v>6</v>
       </c>
-      <c r="H510" s="2"/>
+      <c r="H510" s="2" t="s">
+        <v>2946</v>
+      </c>
     </row>
     <row r="511" spans="1:8" ht="29" x14ac:dyDescent="0.35">
       <c r="A511" s="2" t="s">
@@ -22134,7 +22552,9 @@
       <c r="G511" s="2">
         <v>6</v>
       </c>
-      <c r="H511" s="2"/>
+      <c r="H511" s="2" t="s">
+        <v>2946</v>
+      </c>
     </row>
     <row r="512" spans="1:8" ht="29" x14ac:dyDescent="0.35">
       <c r="A512" s="2" t="s">
@@ -22158,7 +22578,9 @@
       <c r="G512" s="2">
         <v>6</v>
       </c>
-      <c r="H512" s="2"/>
+      <c r="H512" s="2" t="s">
+        <v>2945</v>
+      </c>
     </row>
     <row r="513" spans="1:8" ht="29" x14ac:dyDescent="0.35">
       <c r="A513" s="2" t="s">
@@ -22182,7 +22604,9 @@
       <c r="G513" s="2">
         <v>6</v>
       </c>
-      <c r="H513" s="2"/>
+      <c r="H513" s="2" t="s">
+        <v>2945</v>
+      </c>
     </row>
     <row r="514" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A514" s="2" t="s">
@@ -22206,7 +22630,9 @@
       <c r="G514" s="2">
         <v>6</v>
       </c>
-      <c r="H514" s="2"/>
+      <c r="H514" s="2" t="s">
+        <v>2945</v>
+      </c>
     </row>
     <row r="515" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A515" s="2" t="s">
@@ -22230,7 +22656,9 @@
       <c r="G515" s="2">
         <v>6</v>
       </c>
-      <c r="H515" s="2"/>
+      <c r="H515" s="2" t="s">
+        <v>2945</v>
+      </c>
     </row>
     <row r="516" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A516" s="2" t="s">
@@ -22254,7 +22682,9 @@
       <c r="G516" s="2">
         <v>6</v>
       </c>
-      <c r="H516" s="2"/>
+      <c r="H516" s="2" t="s">
+        <v>2945</v>
+      </c>
     </row>
     <row r="517" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A517" s="2" t="s">
@@ -22278,7 +22708,9 @@
       <c r="G517" s="2">
         <v>6</v>
       </c>
-      <c r="H517" s="2"/>
+      <c r="H517" s="2" t="s">
+        <v>2946</v>
+      </c>
     </row>
     <row r="518" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A518" s="2" t="s">
@@ -22302,7 +22734,9 @@
       <c r="G518" s="2">
         <v>6</v>
       </c>
-      <c r="H518" s="2"/>
+      <c r="H518" s="2" t="s">
+        <v>2945</v>
+      </c>
     </row>
     <row r="519" spans="1:8" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A519" s="2" t="s">
@@ -22314,7 +22748,7 @@
       <c r="C519" s="2" t="s">
         <v>1557</v>
       </c>
-      <c r="D519" s="3" t="s">
+      <c r="D519" s="4" t="s">
         <v>1558</v>
       </c>
       <c r="E519" s="2" t="s">
@@ -22326,7 +22760,9 @@
       <c r="G519" s="2">
         <v>6</v>
       </c>
-      <c r="H519" s="2"/>
+      <c r="H519" s="2" t="s">
+        <v>2946</v>
+      </c>
     </row>
     <row r="520" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A520" s="2" t="s">
@@ -22350,7 +22786,9 @@
       <c r="G520" s="2">
         <v>6</v>
       </c>
-      <c r="H520" s="2"/>
+      <c r="H520" s="2" t="s">
+        <v>2945</v>
+      </c>
     </row>
     <row r="521" spans="1:8" ht="87" x14ac:dyDescent="0.35">
       <c r="A521" s="2" t="s">
@@ -22374,7 +22812,9 @@
       <c r="G521" s="2">
         <v>6</v>
       </c>
-      <c r="H521" s="2"/>
+      <c r="H521" s="2" t="s">
+        <v>2946</v>
+      </c>
     </row>
     <row r="522" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A522" s="2" t="s">
@@ -22398,7 +22838,9 @@
       <c r="G522" s="2">
         <v>6</v>
       </c>
-      <c r="H522" s="2"/>
+      <c r="H522" s="2" t="s">
+        <v>2945</v>
+      </c>
     </row>
     <row r="523" spans="1:8" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A523" s="2" t="s">
@@ -22422,7 +22864,9 @@
       <c r="G523" s="2">
         <v>6</v>
       </c>
-      <c r="H523" s="2"/>
+      <c r="H523" s="2" t="s">
+        <v>2946</v>
+      </c>
     </row>
     <row r="524" spans="1:8" ht="29" x14ac:dyDescent="0.35">
       <c r="A524" s="2" t="s">
@@ -22446,7 +22890,9 @@
       <c r="G524" s="2">
         <v>6</v>
       </c>
-      <c r="H524" s="2"/>
+      <c r="H524" s="2" t="s">
+        <v>2946</v>
+      </c>
     </row>
     <row r="525" spans="1:8" ht="87" x14ac:dyDescent="0.35">
       <c r="A525" s="2" t="s">
@@ -22470,7 +22916,9 @@
       <c r="G525" s="2">
         <v>6</v>
       </c>
-      <c r="H525" s="2"/>
+      <c r="H525" s="2" t="s">
+        <v>2946</v>
+      </c>
     </row>
     <row r="526" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A526" s="2" t="s">
@@ -22494,7 +22942,9 @@
       <c r="G526" s="2">
         <v>6</v>
       </c>
-      <c r="H526" s="2"/>
+      <c r="H526" s="2" t="s">
+        <v>2946</v>
+      </c>
     </row>
     <row r="527" spans="1:8" ht="29" x14ac:dyDescent="0.35">
       <c r="A527" s="2" t="s">
@@ -22518,7 +22968,9 @@
       <c r="G527" s="2">
         <v>6</v>
       </c>
-      <c r="H527" s="2"/>
+      <c r="H527" s="2" t="s">
+        <v>2946</v>
+      </c>
     </row>
     <row r="528" spans="1:8" ht="58" x14ac:dyDescent="0.35">
       <c r="A528" s="2" t="s">
@@ -22542,7 +22994,9 @@
       <c r="G528" s="2">
         <v>6</v>
       </c>
-      <c r="H528" s="2"/>
+      <c r="H528" s="2" t="s">
+        <v>2946</v>
+      </c>
     </row>
     <row r="529" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A529" s="2" t="s">
@@ -22566,7 +23020,9 @@
       <c r="G529" s="2">
         <v>6</v>
       </c>
-      <c r="H529" s="2"/>
+      <c r="H529" s="2" t="s">
+        <v>2945</v>
+      </c>
     </row>
     <row r="530" spans="1:8" ht="29" x14ac:dyDescent="0.35">
       <c r="A530" s="2" t="s">
@@ -22590,7 +23046,9 @@
       <c r="G530" s="2">
         <v>6</v>
       </c>
-      <c r="H530" s="2"/>
+      <c r="H530" s="2" t="s">
+        <v>2946</v>
+      </c>
     </row>
     <row r="531" spans="1:8" ht="72.5" x14ac:dyDescent="0.35">
       <c r="A531" s="2" t="s">
@@ -22614,7 +23072,9 @@
       <c r="G531" s="2">
         <v>6</v>
       </c>
-      <c r="H531" s="2"/>
+      <c r="H531" s="2" t="s">
+        <v>2945</v>
+      </c>
     </row>
     <row r="532" spans="1:8" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A532" s="2" t="s">
@@ -22638,7 +23098,9 @@
       <c r="G532" s="2">
         <v>6</v>
       </c>
-      <c r="H532" s="2"/>
+      <c r="H532" s="2" t="s">
+        <v>2946</v>
+      </c>
     </row>
     <row r="533" spans="1:8" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A533" s="2" t="s">
@@ -22662,7 +23124,9 @@
       <c r="G533" s="2">
         <v>6</v>
       </c>
-      <c r="H533" s="2"/>
+      <c r="H533" s="2" t="s">
+        <v>2946</v>
+      </c>
     </row>
     <row r="534" spans="1:8" ht="87" x14ac:dyDescent="0.35">
       <c r="A534" s="2" t="s">
@@ -22686,7 +23150,9 @@
       <c r="G534" s="2">
         <v>6</v>
       </c>
-      <c r="H534" s="2"/>
+      <c r="H534" s="2" t="s">
+        <v>2946</v>
+      </c>
     </row>
     <row r="535" spans="1:8" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A535" s="2" t="s">
@@ -22710,7 +23176,9 @@
       <c r="G535" s="2">
         <v>6</v>
       </c>
-      <c r="H535" s="2"/>
+      <c r="H535" s="2" t="s">
+        <v>2946</v>
+      </c>
     </row>
     <row r="536" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A536" s="2" t="s">
@@ -22734,7 +23202,9 @@
       <c r="G536" s="2">
         <v>6</v>
       </c>
-      <c r="H536" s="2"/>
+      <c r="H536" s="2">
+        <v>0</v>
+      </c>
     </row>
     <row r="537" spans="1:8" ht="29" x14ac:dyDescent="0.35">
       <c r="A537" s="2" t="s">
@@ -22758,7 +23228,9 @@
       <c r="G537" s="2">
         <v>6</v>
       </c>
-      <c r="H537" s="2"/>
+      <c r="H537" s="2" t="s">
+        <v>2945</v>
+      </c>
     </row>
     <row r="538" spans="1:8" ht="58" x14ac:dyDescent="0.35">
       <c r="A538" s="2" t="s">
@@ -22782,7 +23254,9 @@
       <c r="G538" s="2">
         <v>6</v>
       </c>
-      <c r="H538" s="2"/>
+      <c r="H538" s="2" t="s">
+        <v>2946</v>
+      </c>
     </row>
     <row r="539" spans="1:8" ht="58" x14ac:dyDescent="0.35">
       <c r="A539" s="2" t="s">
@@ -22806,7 +23280,9 @@
       <c r="G539" s="2">
         <v>6</v>
       </c>
-      <c r="H539" s="2"/>
+      <c r="H539" s="2" t="s">
+        <v>2946</v>
+      </c>
     </row>
     <row r="540" spans="1:8" ht="72.5" x14ac:dyDescent="0.35">
       <c r="A540" s="2" t="s">
@@ -22830,7 +23306,9 @@
       <c r="G540" s="2">
         <v>6</v>
       </c>
-      <c r="H540" s="2"/>
+      <c r="H540" s="2" t="s">
+        <v>2946</v>
+      </c>
     </row>
     <row r="541" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A541" s="2" t="s">
@@ -22854,7 +23332,9 @@
       <c r="G541" s="2">
         <v>6</v>
       </c>
-      <c r="H541" s="2"/>
+      <c r="H541" s="2" t="s">
+        <v>2945</v>
+      </c>
     </row>
     <row r="542" spans="1:8" ht="29" x14ac:dyDescent="0.35">
       <c r="A542" s="2" t="s">
@@ -22878,7 +23358,9 @@
       <c r="G542" s="2">
         <v>6</v>
       </c>
-      <c r="H542" s="2"/>
+      <c r="H542" s="2" t="s">
+        <v>2946</v>
+      </c>
     </row>
     <row r="543" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A543" s="2" t="s">
@@ -22902,7 +23384,9 @@
       <c r="G543" s="2">
         <v>6</v>
       </c>
-      <c r="H543" s="2"/>
+      <c r="H543" s="2" t="s">
+        <v>2945</v>
+      </c>
     </row>
     <row r="544" spans="1:8" ht="29" x14ac:dyDescent="0.35">
       <c r="A544" s="2" t="s">
@@ -22926,7 +23410,9 @@
       <c r="G544" s="2">
         <v>6</v>
       </c>
-      <c r="H544" s="2"/>
+      <c r="H544" s="2" t="s">
+        <v>2945</v>
+      </c>
     </row>
     <row r="545" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A545" s="2" t="s">
@@ -22950,7 +23436,9 @@
       <c r="G545" s="2">
         <v>6</v>
       </c>
-      <c r="H545" s="2"/>
+      <c r="H545" s="2" t="s">
+        <v>2945</v>
+      </c>
     </row>
     <row r="546" spans="1:8" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A546" s="2" t="s">
@@ -22974,7 +23462,9 @@
       <c r="G546" s="2">
         <v>6</v>
       </c>
-      <c r="H546" s="2"/>
+      <c r="H546" s="2" t="s">
+        <v>2946</v>
+      </c>
     </row>
     <row r="547" spans="1:8" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A547" s="2" t="s">
@@ -22998,7 +23488,9 @@
       <c r="G547" s="2">
         <v>6</v>
       </c>
-      <c r="H547" s="2"/>
+      <c r="H547" s="2" t="s">
+        <v>2946</v>
+      </c>
     </row>
     <row r="548" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A548" s="2" t="s">
@@ -23022,7 +23514,9 @@
       <c r="G548" s="2">
         <v>6</v>
       </c>
-      <c r="H548" s="2"/>
+      <c r="H548" s="2" t="s">
+        <v>2945</v>
+      </c>
     </row>
     <row r="549" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A549" s="2" t="s">
@@ -23046,7 +23540,9 @@
       <c r="G549" s="2">
         <v>6</v>
       </c>
-      <c r="H549" s="2"/>
+      <c r="H549" s="2" t="s">
+        <v>2945</v>
+      </c>
     </row>
     <row r="550" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A550" s="2" t="s">
@@ -23070,7 +23566,9 @@
       <c r="G550" s="2">
         <v>6</v>
       </c>
-      <c r="H550" s="2"/>
+      <c r="H550" s="2">
+        <v>0</v>
+      </c>
     </row>
     <row r="551" spans="1:8" ht="29" x14ac:dyDescent="0.35">
       <c r="A551" s="2" t="s">
@@ -23094,7 +23592,9 @@
       <c r="G551" s="2">
         <v>6</v>
       </c>
-      <c r="H551" s="2"/>
+      <c r="H551" s="2" t="s">
+        <v>2946</v>
+      </c>
     </row>
     <row r="552" spans="1:8" ht="29" x14ac:dyDescent="0.35">
       <c r="A552" s="2" t="s">
@@ -23118,7 +23618,9 @@
       <c r="G552" s="2">
         <v>6</v>
       </c>
-      <c r="H552" s="2"/>
+      <c r="H552" s="2" t="s">
+        <v>2946</v>
+      </c>
     </row>
     <row r="553" spans="1:8" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A553" s="2" t="s">
@@ -23142,7 +23644,9 @@
       <c r="G553" s="2">
         <v>6</v>
       </c>
-      <c r="H553" s="2"/>
+      <c r="H553" s="2" t="s">
+        <v>2946</v>
+      </c>
     </row>
     <row r="554" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A554" s="2" t="s">
@@ -23166,7 +23670,9 @@
       <c r="G554" s="2">
         <v>6</v>
       </c>
-      <c r="H554" s="2"/>
+      <c r="H554" s="2" t="s">
+        <v>2946</v>
+      </c>
     </row>
     <row r="555" spans="1:8" ht="87" x14ac:dyDescent="0.35">
       <c r="A555" s="2" t="s">
@@ -23190,7 +23696,9 @@
       <c r="G555" s="2">
         <v>6</v>
       </c>
-      <c r="H555" s="2"/>
+      <c r="H555" s="2" t="s">
+        <v>2946</v>
+      </c>
     </row>
     <row r="556" spans="1:8" ht="29" x14ac:dyDescent="0.35">
       <c r="A556" s="2" t="s">
@@ -23214,7 +23722,9 @@
       <c r="G556" s="2">
         <v>6</v>
       </c>
-      <c r="H556" s="2"/>
+      <c r="H556" s="2" t="s">
+        <v>2946</v>
+      </c>
     </row>
     <row r="557" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A557" s="2" t="s">
@@ -23238,7 +23748,9 @@
       <c r="G557" s="2">
         <v>6</v>
       </c>
-      <c r="H557" s="2"/>
+      <c r="H557" s="2" t="s">
+        <v>2945</v>
+      </c>
     </row>
     <row r="558" spans="1:8" ht="29" x14ac:dyDescent="0.35">
       <c r="A558" s="2" t="s">
@@ -23262,7 +23774,9 @@
       <c r="G558" s="2">
         <v>6</v>
       </c>
-      <c r="H558" s="2"/>
+      <c r="H558" s="2" t="s">
+        <v>2946</v>
+      </c>
     </row>
     <row r="559" spans="1:8" ht="29" x14ac:dyDescent="0.35">
       <c r="A559" s="2" t="s">
@@ -23286,7 +23800,9 @@
       <c r="G559" s="2">
         <v>6</v>
       </c>
-      <c r="H559" s="2"/>
+      <c r="H559" s="2" t="s">
+        <v>2945</v>
+      </c>
     </row>
     <row r="560" spans="1:8" ht="29" x14ac:dyDescent="0.35">
       <c r="A560" s="2" t="s">
@@ -23310,7 +23826,9 @@
       <c r="G560" s="2">
         <v>6</v>
       </c>
-      <c r="H560" s="2"/>
+      <c r="H560" s="2">
+        <v>0</v>
+      </c>
     </row>
     <row r="561" spans="1:8" ht="29" x14ac:dyDescent="0.35">
       <c r="A561" s="2" t="s">
@@ -23334,7 +23852,9 @@
       <c r="G561" s="2">
         <v>6</v>
       </c>
-      <c r="H561" s="2"/>
+      <c r="H561" s="2" t="s">
+        <v>2946</v>
+      </c>
     </row>
     <row r="562" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A562" s="2" t="s">
@@ -23358,7 +23878,9 @@
       <c r="G562" s="2">
         <v>6</v>
       </c>
-      <c r="H562" s="2"/>
+      <c r="H562" s="2" t="s">
+        <v>2945</v>
+      </c>
     </row>
     <row r="563" spans="1:8" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A563" s="2" t="s">
@@ -23382,7 +23904,9 @@
       <c r="G563" s="2">
         <v>6</v>
       </c>
-      <c r="H563" s="2"/>
+      <c r="H563" s="2" t="s">
+        <v>2945</v>
+      </c>
     </row>
     <row r="564" spans="1:8" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A564" s="2" t="s">
@@ -23406,7 +23930,9 @@
       <c r="G564" s="2">
         <v>6</v>
       </c>
-      <c r="H564" s="2"/>
+      <c r="H564" s="2" t="s">
+        <v>2946</v>
+      </c>
     </row>
     <row r="565" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A565" s="2" t="s">
@@ -23430,7 +23956,9 @@
       <c r="G565" s="2">
         <v>6</v>
       </c>
-      <c r="H565" s="2"/>
+      <c r="H565" s="2" t="s">
+        <v>2946</v>
+      </c>
     </row>
     <row r="566" spans="1:8" ht="29" x14ac:dyDescent="0.35">
       <c r="A566" s="2" t="s">
@@ -23454,7 +23982,9 @@
       <c r="G566" s="2">
         <v>6</v>
       </c>
-      <c r="H566" s="2"/>
+      <c r="H566" s="2" t="s">
+        <v>2946</v>
+      </c>
     </row>
     <row r="567" spans="1:8" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A567" s="2" t="s">
@@ -23478,7 +24008,9 @@
       <c r="G567" s="2">
         <v>6</v>
       </c>
-      <c r="H567" s="2"/>
+      <c r="H567" s="2" t="s">
+        <v>2946</v>
+      </c>
     </row>
     <row r="568" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A568" s="2" t="s">
@@ -23502,7 +24034,9 @@
       <c r="G568" s="2">
         <v>6</v>
       </c>
-      <c r="H568" s="2"/>
+      <c r="H568" s="2" t="s">
+        <v>2946</v>
+      </c>
     </row>
     <row r="569" spans="1:8" ht="58" x14ac:dyDescent="0.35">
       <c r="A569" s="2" t="s">
@@ -23526,7 +24060,9 @@
       <c r="G569" s="2">
         <v>6</v>
       </c>
-      <c r="H569" s="2"/>
+      <c r="H569" s="2" t="s">
+        <v>2946</v>
+      </c>
     </row>
     <row r="570" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A570" s="2" t="s">
@@ -23550,7 +24086,9 @@
       <c r="G570" s="2">
         <v>6</v>
       </c>
-      <c r="H570" s="2"/>
+      <c r="H570" s="2" t="s">
+        <v>2945</v>
+      </c>
     </row>
     <row r="571" spans="1:8" ht="29" x14ac:dyDescent="0.35">
       <c r="A571" s="2" t="s">
@@ -23574,7 +24112,9 @@
       <c r="G571" s="2">
         <v>6</v>
       </c>
-      <c r="H571" s="2"/>
+      <c r="H571" s="2" t="s">
+        <v>2946</v>
+      </c>
     </row>
     <row r="572" spans="1:8" ht="29" x14ac:dyDescent="0.35">
       <c r="A572" s="2" t="s">
@@ -23598,7 +24138,9 @@
       <c r="G572" s="2">
         <v>6</v>
       </c>
-      <c r="H572" s="2"/>
+      <c r="H572" s="2" t="s">
+        <v>2946</v>
+      </c>
     </row>
     <row r="573" spans="1:8" ht="72.5" x14ac:dyDescent="0.35">
       <c r="A573" s="2" t="s">
@@ -23622,7 +24164,9 @@
       <c r="G573" s="2">
         <v>6</v>
       </c>
-      <c r="H573" s="2"/>
+      <c r="H573" s="2" t="s">
+        <v>2946</v>
+      </c>
     </row>
     <row r="574" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A574" s="2" t="s">
@@ -23646,7 +24190,9 @@
       <c r="G574" s="2">
         <v>6</v>
       </c>
-      <c r="H574" s="2"/>
+      <c r="H574" s="2" t="s">
+        <v>2945</v>
+      </c>
     </row>
     <row r="575" spans="1:8" ht="87" x14ac:dyDescent="0.35">
       <c r="A575" s="2" t="s">
@@ -23670,7 +24216,9 @@
       <c r="G575" s="2">
         <v>6</v>
       </c>
-      <c r="H575" s="2"/>
+      <c r="H575" s="2" t="s">
+        <v>2946</v>
+      </c>
     </row>
     <row r="576" spans="1:8" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A576" s="2" t="s">
@@ -23694,7 +24242,9 @@
       <c r="G576" s="2">
         <v>6</v>
       </c>
-      <c r="H576" s="2"/>
+      <c r="H576" s="2" t="s">
+        <v>2946</v>
+      </c>
     </row>
     <row r="577" spans="1:8" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A577" s="2" t="s">
@@ -23718,7 +24268,9 @@
       <c r="G577" s="2">
         <v>6</v>
       </c>
-      <c r="H577" s="2"/>
+      <c r="H577" s="2">
+        <v>0</v>
+      </c>
     </row>
     <row r="578" spans="1:8" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A578" s="2" t="s">
@@ -23742,7 +24294,9 @@
       <c r="G578" s="2">
         <v>6</v>
       </c>
-      <c r="H578" s="2"/>
+      <c r="H578" s="2" t="s">
+        <v>2945</v>
+      </c>
     </row>
     <row r="579" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A579" s="2" t="s">
@@ -23766,7 +24320,9 @@
       <c r="G579" s="2">
         <v>6</v>
       </c>
-      <c r="H579" s="2"/>
+      <c r="H579" s="2" t="s">
+        <v>2946</v>
+      </c>
     </row>
     <row r="580" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A580" s="2" t="s">
@@ -23790,7 +24346,9 @@
       <c r="G580" s="2">
         <v>6</v>
       </c>
-      <c r="H580" s="2"/>
+      <c r="H580" s="2" t="s">
+        <v>2945</v>
+      </c>
     </row>
     <row r="581" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A581" s="2" t="s">
@@ -23814,9 +24372,11 @@
       <c r="G581" s="2">
         <v>6</v>
       </c>
-      <c r="H581" s="2"/>
-    </row>
-    <row r="582" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="H581" s="2" t="s">
+        <v>2946</v>
+      </c>
+    </row>
+    <row r="582" spans="1:8" ht="29" x14ac:dyDescent="0.35">
       <c r="A582" s="2" t="s">
         <v>1736</v>
       </c>
@@ -23838,7 +24398,9 @@
       <c r="G582" s="2">
         <v>6</v>
       </c>
-      <c r="H582" s="2"/>
+      <c r="H582" s="2" t="s">
+        <v>2946</v>
+      </c>
     </row>
     <row r="583" spans="1:8" ht="29" x14ac:dyDescent="0.35">
       <c r="A583" s="2" t="s">
@@ -23862,7 +24424,9 @@
       <c r="G583" s="2">
         <v>6</v>
       </c>
-      <c r="H583" s="2"/>
+      <c r="H583" s="2" t="s">
+        <v>2946</v>
+      </c>
     </row>
     <row r="584" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A584" s="2" t="s">
@@ -23886,7 +24450,9 @@
       <c r="G584" s="2">
         <v>6</v>
       </c>
-      <c r="H584" s="2"/>
+      <c r="H584" s="2" t="s">
+        <v>2945</v>
+      </c>
     </row>
     <row r="585" spans="1:8" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A585" s="2" t="s">
@@ -23910,7 +24476,9 @@
       <c r="G585" s="2">
         <v>6</v>
       </c>
-      <c r="H585" s="2"/>
+      <c r="H585" s="2" t="s">
+        <v>2945</v>
+      </c>
     </row>
     <row r="586" spans="1:8" ht="29" x14ac:dyDescent="0.35">
       <c r="A586" s="2" t="s">
@@ -23934,7 +24502,9 @@
       <c r="G586" s="2">
         <v>6</v>
       </c>
-      <c r="H586" s="2"/>
+      <c r="H586" s="2" t="s">
+        <v>2946</v>
+      </c>
     </row>
     <row r="587" spans="1:8" ht="72.5" x14ac:dyDescent="0.35">
       <c r="A587" s="2" t="s">
@@ -23958,7 +24528,9 @@
       <c r="G587" s="2">
         <v>6</v>
       </c>
-      <c r="H587" s="2"/>
+      <c r="H587" s="2" t="s">
+        <v>2946</v>
+      </c>
     </row>
     <row r="588" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A588" s="2" t="s">
@@ -23982,7 +24554,9 @@
       <c r="G588" s="2">
         <v>6</v>
       </c>
-      <c r="H588" s="2"/>
+      <c r="H588" s="2" t="s">
+        <v>2945</v>
+      </c>
     </row>
     <row r="589" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A589" s="2" t="s">
@@ -24006,7 +24580,9 @@
       <c r="G589" s="2">
         <v>6</v>
       </c>
-      <c r="H589" s="2"/>
+      <c r="H589" s="2">
+        <v>0</v>
+      </c>
     </row>
     <row r="590" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A590" s="2" t="s">
@@ -24030,7 +24606,9 @@
       <c r="G590" s="2">
         <v>6</v>
       </c>
-      <c r="H590" s="2"/>
+      <c r="H590" s="2" t="s">
+        <v>2945</v>
+      </c>
     </row>
     <row r="591" spans="1:8" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A591" s="2" t="s">
@@ -24054,7 +24632,9 @@
       <c r="G591" s="2">
         <v>6</v>
       </c>
-      <c r="H591" s="2"/>
+      <c r="H591" s="2" t="s">
+        <v>2946</v>
+      </c>
     </row>
     <row r="592" spans="1:8" ht="29" x14ac:dyDescent="0.35">
       <c r="A592" s="2" t="s">
@@ -24078,7 +24658,9 @@
       <c r="G592" s="2">
         <v>6</v>
       </c>
-      <c r="H592" s="2"/>
+      <c r="H592" s="2" t="s">
+        <v>2945</v>
+      </c>
     </row>
     <row r="593" spans="1:8" ht="29" x14ac:dyDescent="0.35">
       <c r="A593" s="2" t="s">
@@ -24102,7 +24684,9 @@
       <c r="G593" s="2">
         <v>6</v>
       </c>
-      <c r="H593" s="2"/>
+      <c r="H593" s="2" t="s">
+        <v>2946</v>
+      </c>
     </row>
     <row r="594" spans="1:8" ht="29" x14ac:dyDescent="0.35">
       <c r="A594" s="2" t="s">
@@ -24126,7 +24710,9 @@
       <c r="G594" s="2">
         <v>6</v>
       </c>
-      <c r="H594" s="2"/>
+      <c r="H594" s="2" t="s">
+        <v>2946</v>
+      </c>
     </row>
     <row r="595" spans="1:8" ht="29" x14ac:dyDescent="0.35">
       <c r="A595" s="2" t="s">
@@ -24150,7 +24736,9 @@
       <c r="G595" s="2">
         <v>6</v>
       </c>
-      <c r="H595" s="2"/>
+      <c r="H595" s="2" t="s">
+        <v>2946</v>
+      </c>
     </row>
     <row r="596" spans="1:8" ht="29" x14ac:dyDescent="0.35">
       <c r="A596" s="2" t="s">
@@ -24174,7 +24762,9 @@
       <c r="G596" s="2">
         <v>6</v>
       </c>
-      <c r="H596" s="2"/>
+      <c r="H596" s="2" t="s">
+        <v>2946</v>
+      </c>
     </row>
     <row r="597" spans="1:8" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A597" s="2" t="s">
@@ -24198,7 +24788,9 @@
       <c r="G597" s="2">
         <v>6</v>
       </c>
-      <c r="H597" s="2"/>
+      <c r="H597" s="2" t="s">
+        <v>2946</v>
+      </c>
     </row>
     <row r="598" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A598" s="2" t="s">
@@ -24222,7 +24814,9 @@
       <c r="G598" s="2">
         <v>6</v>
       </c>
-      <c r="H598" s="2"/>
+      <c r="H598" s="2" t="s">
+        <v>2945</v>
+      </c>
     </row>
     <row r="599" spans="1:8" ht="58" x14ac:dyDescent="0.35">
       <c r="A599" s="2" t="s">
@@ -24246,7 +24840,9 @@
       <c r="G599" s="2">
         <v>6</v>
       </c>
-      <c r="H599" s="2"/>
+      <c r="H599" s="2" t="s">
+        <v>2946</v>
+      </c>
     </row>
     <row r="600" spans="1:8" ht="87" x14ac:dyDescent="0.35">
       <c r="A600" s="2" t="s">
@@ -24270,7 +24866,9 @@
       <c r="G600" s="2">
         <v>6</v>
       </c>
-      <c r="H600" s="2"/>
+      <c r="H600" s="2" t="s">
+        <v>2946</v>
+      </c>
     </row>
     <row r="601" spans="1:8" ht="29" x14ac:dyDescent="0.35">
       <c r="A601" s="2" t="s">
@@ -24294,7 +24892,9 @@
       <c r="G601" s="2">
         <v>6</v>
       </c>
-      <c r="H601" s="2"/>
+      <c r="H601" s="2" t="s">
+        <v>2945</v>
+      </c>
     </row>
     <row r="602" spans="1:8" ht="29" x14ac:dyDescent="0.35">
       <c r="A602" s="2" t="s">
@@ -24318,7 +24918,9 @@
       <c r="G602" s="2">
         <v>7</v>
       </c>
-      <c r="H602" s="2"/>
+      <c r="H602" s="2" t="s">
+        <v>2945</v>
+      </c>
     </row>
     <row r="603" spans="1:8" ht="29" x14ac:dyDescent="0.35">
       <c r="A603" s="2" t="s">
@@ -24342,7 +24944,9 @@
       <c r="G603" s="2">
         <v>7</v>
       </c>
-      <c r="H603" s="2"/>
+      <c r="H603" s="2" t="s">
+        <v>2945</v>
+      </c>
     </row>
     <row r="604" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A604" s="2" t="s">
@@ -24366,7 +24970,9 @@
       <c r="G604" s="2">
         <v>7</v>
       </c>
-      <c r="H604" s="2"/>
+      <c r="H604" s="2" t="s">
+        <v>2945</v>
+      </c>
     </row>
     <row r="605" spans="1:8" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A605" s="2" t="s">
@@ -24390,7 +24996,9 @@
       <c r="G605" s="2">
         <v>7</v>
       </c>
-      <c r="H605" s="2"/>
+      <c r="H605" s="2" t="s">
+        <v>2945</v>
+      </c>
     </row>
     <row r="606" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A606" s="2" t="s">
@@ -24414,7 +25022,9 @@
       <c r="G606" s="2">
         <v>7</v>
       </c>
-      <c r="H606" s="2"/>
+      <c r="H606" s="2" t="s">
+        <v>2945</v>
+      </c>
     </row>
     <row r="607" spans="1:8" ht="87" x14ac:dyDescent="0.35">
       <c r="A607" s="2" t="s">
@@ -24438,7 +25048,9 @@
       <c r="G607" s="2">
         <v>7</v>
       </c>
-      <c r="H607" s="2"/>
+      <c r="H607" s="2" t="s">
+        <v>2945</v>
+      </c>
     </row>
     <row r="608" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A608" s="2" t="s">
@@ -24462,7 +25074,9 @@
       <c r="G608" s="2">
         <v>7</v>
       </c>
-      <c r="H608" s="2"/>
+      <c r="H608" s="2" t="s">
+        <v>2945</v>
+      </c>
     </row>
     <row r="609" spans="1:8" ht="29" x14ac:dyDescent="0.35">
       <c r="A609" s="2" t="s">
@@ -24486,7 +25100,9 @@
       <c r="G609" s="2">
         <v>7</v>
       </c>
-      <c r="H609" s="2"/>
+      <c r="H609" s="2" t="s">
+        <v>2945</v>
+      </c>
     </row>
     <row r="610" spans="1:8" ht="87" x14ac:dyDescent="0.35">
       <c r="A610" s="2" t="s">
@@ -24510,7 +25126,9 @@
       <c r="G610" s="2">
         <v>7</v>
       </c>
-      <c r="H610" s="2"/>
+      <c r="H610" s="2" t="s">
+        <v>2946</v>
+      </c>
     </row>
     <row r="611" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A611" s="2" t="s">
@@ -24534,7 +25152,9 @@
       <c r="G611" s="2">
         <v>7</v>
       </c>
-      <c r="H611" s="2"/>
+      <c r="H611" s="2" t="s">
+        <v>2946</v>
+      </c>
     </row>
     <row r="612" spans="1:8" ht="72.5" x14ac:dyDescent="0.35">
       <c r="A612" s="2" t="s">
@@ -24558,7 +25178,9 @@
       <c r="G612" s="2">
         <v>7</v>
       </c>
-      <c r="H612" s="2"/>
+      <c r="H612" s="2" t="s">
+        <v>2946</v>
+      </c>
     </row>
     <row r="613" spans="1:8" ht="29" x14ac:dyDescent="0.35">
       <c r="A613" s="2" t="s">
@@ -24582,7 +25204,9 @@
       <c r="G613" s="2">
         <v>7</v>
       </c>
-      <c r="H613" s="2"/>
+      <c r="H613" s="2" t="s">
+        <v>2946</v>
+      </c>
     </row>
     <row r="614" spans="1:8" ht="72.5" x14ac:dyDescent="0.35">
       <c r="A614" s="2" t="s">
@@ -24606,7 +25230,9 @@
       <c r="G614" s="2">
         <v>7</v>
       </c>
-      <c r="H614" s="2"/>
+      <c r="H614" s="2" t="s">
+        <v>2946</v>
+      </c>
     </row>
     <row r="615" spans="1:8" ht="29" x14ac:dyDescent="0.35">
       <c r="A615" s="2" t="s">
@@ -24630,7 +25256,9 @@
       <c r="G615" s="2">
         <v>7</v>
       </c>
-      <c r="H615" s="2"/>
+      <c r="H615" s="2" t="s">
+        <v>2946</v>
+      </c>
     </row>
     <row r="616" spans="1:8" ht="72.5" x14ac:dyDescent="0.35">
       <c r="A616" s="2" t="s">
@@ -24654,7 +25282,9 @@
       <c r="G616" s="2">
         <v>7</v>
       </c>
-      <c r="H616" s="2"/>
+      <c r="H616" s="2" t="s">
+        <v>2946</v>
+      </c>
     </row>
     <row r="617" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A617" s="2" t="s">
@@ -24678,7 +25308,9 @@
       <c r="G617" s="2">
         <v>7</v>
       </c>
-      <c r="H617" s="2"/>
+      <c r="H617" s="2" t="s">
+        <v>2945</v>
+      </c>
     </row>
     <row r="618" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A618" s="2" t="s">
@@ -24702,7 +25334,9 @@
       <c r="G618" s="2">
         <v>7</v>
       </c>
-      <c r="H618" s="2"/>
+      <c r="H618" s="2" t="s">
+        <v>2945</v>
+      </c>
     </row>
     <row r="619" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A619" s="2" t="s">
@@ -24726,7 +25360,9 @@
       <c r="G619" s="2">
         <v>7</v>
       </c>
-      <c r="H619" s="2"/>
+      <c r="H619" s="2" t="s">
+        <v>2945</v>
+      </c>
     </row>
     <row r="620" spans="1:8" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A620" s="2" t="s">
@@ -24750,7 +25386,9 @@
       <c r="G620" s="2">
         <v>7</v>
       </c>
-      <c r="H620" s="2"/>
+      <c r="H620" s="2" t="s">
+        <v>2946</v>
+      </c>
     </row>
     <row r="621" spans="1:8" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A621" s="2" t="s">
@@ -24774,7 +25412,9 @@
       <c r="G621" s="2">
         <v>7</v>
       </c>
-      <c r="H621" s="2"/>
+      <c r="H621" s="2" t="s">
+        <v>2946</v>
+      </c>
     </row>
     <row r="622" spans="1:8" ht="29" x14ac:dyDescent="0.35">
       <c r="A622" s="2" t="s">
@@ -24798,7 +25438,9 @@
       <c r="G622" s="2">
         <v>7</v>
       </c>
-      <c r="H622" s="2"/>
+      <c r="H622" s="2">
+        <v>0</v>
+      </c>
     </row>
     <row r="623" spans="1:8" ht="29" x14ac:dyDescent="0.35">
       <c r="A623" s="2" t="s">
@@ -24822,7 +25464,9 @@
       <c r="G623" s="2">
         <v>7</v>
       </c>
-      <c r="H623" s="2"/>
+      <c r="H623" s="2" t="s">
+        <v>2946</v>
+      </c>
     </row>
     <row r="624" spans="1:8" ht="29" x14ac:dyDescent="0.35">
       <c r="A624" s="2" t="s">
@@ -24846,7 +25490,9 @@
       <c r="G624" s="2">
         <v>7</v>
       </c>
-      <c r="H624" s="2"/>
+      <c r="H624" s="2" t="s">
+        <v>2946</v>
+      </c>
     </row>
     <row r="625" spans="1:8" ht="29" x14ac:dyDescent="0.35">
       <c r="A625" s="2" t="s">
@@ -24870,7 +25516,9 @@
       <c r="G625" s="2">
         <v>7</v>
       </c>
-      <c r="H625" s="2"/>
+      <c r="H625" s="2" t="s">
+        <v>2946</v>
+      </c>
     </row>
     <row r="626" spans="1:8" ht="29" x14ac:dyDescent="0.35">
       <c r="A626" s="2" t="s">
@@ -24894,7 +25542,9 @@
       <c r="G626" s="2">
         <v>7</v>
       </c>
-      <c r="H626" s="2"/>
+      <c r="H626" s="2" t="s">
+        <v>2946</v>
+      </c>
     </row>
     <row r="627" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A627" s="2" t="s">
@@ -24918,7 +25568,9 @@
       <c r="G627" s="2">
         <v>7</v>
       </c>
-      <c r="H627" s="2"/>
+      <c r="H627" s="2" t="s">
+        <v>2945</v>
+      </c>
     </row>
     <row r="628" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A628" s="2" t="s">
@@ -24942,7 +25594,9 @@
       <c r="G628" s="2">
         <v>7</v>
       </c>
-      <c r="H628" s="2"/>
+      <c r="H628" s="2">
+        <v>0</v>
+      </c>
     </row>
     <row r="629" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A629" s="2" t="s">
@@ -24966,7 +25620,9 @@
       <c r="G629" s="2">
         <v>7</v>
       </c>
-      <c r="H629" s="2"/>
+      <c r="H629" s="2" t="s">
+        <v>2946</v>
+      </c>
     </row>
     <row r="630" spans="1:8" ht="58" x14ac:dyDescent="0.35">
       <c r="A630" s="2" t="s">
@@ -24990,7 +25646,9 @@
       <c r="G630" s="2">
         <v>7</v>
       </c>
-      <c r="H630" s="2"/>
+      <c r="H630" s="2" t="s">
+        <v>2946</v>
+      </c>
     </row>
     <row r="631" spans="1:8" ht="29" x14ac:dyDescent="0.35">
       <c r="A631" s="2" t="s">
@@ -25014,7 +25672,9 @@
       <c r="G631" s="2">
         <v>7</v>
       </c>
-      <c r="H631" s="2"/>
+      <c r="H631" s="2" t="s">
+        <v>2945</v>
+      </c>
     </row>
     <row r="632" spans="1:8" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A632" s="2" t="s">
@@ -25038,7 +25698,9 @@
       <c r="G632" s="2">
         <v>7</v>
       </c>
-      <c r="H632" s="2"/>
+      <c r="H632" s="2" t="s">
+        <v>2946</v>
+      </c>
     </row>
     <row r="633" spans="1:8" ht="29" x14ac:dyDescent="0.35">
       <c r="A633" s="2" t="s">
@@ -25062,7 +25724,9 @@
       <c r="G633" s="2">
         <v>7</v>
       </c>
-      <c r="H633" s="2"/>
+      <c r="H633" s="2" t="s">
+        <v>2946</v>
+      </c>
     </row>
     <row r="634" spans="1:8" ht="29" x14ac:dyDescent="0.35">
       <c r="A634" s="2" t="s">
@@ -25086,7 +25750,9 @@
       <c r="G634" s="2">
         <v>7</v>
       </c>
-      <c r="H634" s="2"/>
+      <c r="H634" s="2" t="s">
+        <v>2946</v>
+      </c>
     </row>
     <row r="635" spans="1:8" ht="29" x14ac:dyDescent="0.35">
       <c r="A635" s="2" t="s">
@@ -25110,7 +25776,9 @@
       <c r="G635" s="2">
         <v>7</v>
       </c>
-      <c r="H635" s="2"/>
+      <c r="H635" s="2" t="s">
+        <v>2946</v>
+      </c>
     </row>
     <row r="636" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A636" s="2" t="s">
@@ -25134,7 +25802,9 @@
       <c r="G636" s="2">
         <v>7</v>
       </c>
-      <c r="H636" s="2"/>
+      <c r="H636" s="2" t="s">
+        <v>2945</v>
+      </c>
     </row>
     <row r="637" spans="1:8" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A637" s="2" t="s">
@@ -25158,7 +25828,9 @@
       <c r="G637" s="2">
         <v>7</v>
       </c>
-      <c r="H637" s="2"/>
+      <c r="H637" s="2" t="s">
+        <v>2946</v>
+      </c>
     </row>
     <row r="638" spans="1:8" ht="29" x14ac:dyDescent="0.35">
       <c r="A638" s="2" t="s">
@@ -25182,7 +25854,9 @@
       <c r="G638" s="2">
         <v>7</v>
       </c>
-      <c r="H638" s="2"/>
+      <c r="H638" s="2" t="s">
+        <v>2946</v>
+      </c>
     </row>
     <row r="639" spans="1:8" ht="29" x14ac:dyDescent="0.35">
       <c r="A639" s="2" t="s">
@@ -25206,7 +25880,9 @@
       <c r="G639" s="2">
         <v>7</v>
       </c>
-      <c r="H639" s="2"/>
+      <c r="H639" s="2" t="s">
+        <v>2946</v>
+      </c>
     </row>
     <row r="640" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A640" s="2" t="s">
@@ -25230,7 +25906,9 @@
       <c r="G640" s="2">
         <v>7</v>
       </c>
-      <c r="H640" s="2"/>
+      <c r="H640" s="2" t="s">
+        <v>2946</v>
+      </c>
     </row>
     <row r="641" spans="1:8" ht="29" x14ac:dyDescent="0.35">
       <c r="A641" s="2" t="s">
@@ -25254,7 +25932,9 @@
       <c r="G641" s="2">
         <v>7</v>
       </c>
-      <c r="H641" s="2"/>
+      <c r="H641" s="2" t="s">
+        <v>2946</v>
+      </c>
     </row>
     <row r="642" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A642" s="2" t="s">
@@ -25278,7 +25958,9 @@
       <c r="G642" s="2">
         <v>7</v>
       </c>
-      <c r="H642" s="2"/>
+      <c r="H642" s="2" t="s">
+        <v>2946</v>
+      </c>
     </row>
     <row r="643" spans="1:8" ht="58" x14ac:dyDescent="0.35">
       <c r="A643" s="2" t="s">
@@ -25302,7 +25984,9 @@
       <c r="G643" s="2">
         <v>7</v>
       </c>
-      <c r="H643" s="2"/>
+      <c r="H643" s="2" t="s">
+        <v>2946</v>
+      </c>
     </row>
     <row r="644" spans="1:8" ht="58" x14ac:dyDescent="0.35">
       <c r="A644" s="2" t="s">
@@ -25326,7 +26010,9 @@
       <c r="G644" s="2">
         <v>7</v>
       </c>
-      <c r="H644" s="2"/>
+      <c r="H644" s="2" t="s">
+        <v>2946</v>
+      </c>
     </row>
     <row r="645" spans="1:8" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A645" s="2" t="s">
@@ -25350,7 +26036,9 @@
       <c r="G645" s="2">
         <v>7</v>
       </c>
-      <c r="H645" s="2"/>
+      <c r="H645" s="2" t="s">
+        <v>2946</v>
+      </c>
     </row>
     <row r="646" spans="1:8" ht="72.5" x14ac:dyDescent="0.35">
       <c r="A646" s="2" t="s">
@@ -25374,7 +26062,9 @@
       <c r="G646" s="2">
         <v>7</v>
       </c>
-      <c r="H646" s="2"/>
+      <c r="H646" s="2" t="s">
+        <v>2946</v>
+      </c>
     </row>
     <row r="647" spans="1:8" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A647" s="2" t="s">
@@ -25398,7 +26088,9 @@
       <c r="G647" s="2">
         <v>7</v>
       </c>
-      <c r="H647" s="2"/>
+      <c r="H647" s="2" t="s">
+        <v>2946</v>
+      </c>
     </row>
     <row r="648" spans="1:8" ht="87" x14ac:dyDescent="0.35">
       <c r="A648" s="2" t="s">
@@ -25422,7 +26114,9 @@
       <c r="G648" s="2">
         <v>7</v>
       </c>
-      <c r="H648" s="2"/>
+      <c r="H648" s="2" t="s">
+        <v>2946</v>
+      </c>
     </row>
     <row r="649" spans="1:8" ht="58" x14ac:dyDescent="0.35">
       <c r="A649" s="2" t="s">
@@ -25446,7 +26140,9 @@
       <c r="G649" s="2">
         <v>7</v>
       </c>
-      <c r="H649" s="2"/>
+      <c r="H649" s="2" t="s">
+        <v>2946</v>
+      </c>
     </row>
     <row r="650" spans="1:8" ht="29" x14ac:dyDescent="0.35">
       <c r="A650" s="2" t="s">
@@ -25470,7 +26166,9 @@
       <c r="G650" s="2">
         <v>7</v>
       </c>
-      <c r="H650" s="2"/>
+      <c r="H650" s="2" t="s">
+        <v>2945</v>
+      </c>
     </row>
     <row r="651" spans="1:8" ht="29" x14ac:dyDescent="0.35">
       <c r="A651" s="2" t="s">
@@ -25494,7 +26192,9 @@
       <c r="G651" s="2">
         <v>7</v>
       </c>
-      <c r="H651" s="2"/>
+      <c r="H651" s="2">
+        <v>0</v>
+      </c>
     </row>
     <row r="652" spans="1:8" ht="29" x14ac:dyDescent="0.35">
       <c r="A652" s="2" t="s">
@@ -25518,7 +26218,9 @@
       <c r="G652" s="2">
         <v>7</v>
       </c>
-      <c r="H652" s="2"/>
+      <c r="H652" s="2" t="s">
+        <v>2946</v>
+      </c>
     </row>
     <row r="653" spans="1:8" ht="87" x14ac:dyDescent="0.35">
       <c r="A653" s="2" t="s">
@@ -25542,7 +26244,9 @@
       <c r="G653" s="2">
         <v>7</v>
       </c>
-      <c r="H653" s="2"/>
+      <c r="H653" s="2" t="s">
+        <v>2946</v>
+      </c>
     </row>
     <row r="654" spans="1:8" ht="58" x14ac:dyDescent="0.35">
       <c r="A654" s="2" t="s">
@@ -25566,7 +26270,9 @@
       <c r="G654" s="2">
         <v>7</v>
       </c>
-      <c r="H654" s="2"/>
+      <c r="H654" s="2" t="s">
+        <v>2945</v>
+      </c>
     </row>
     <row r="655" spans="1:8" ht="29" x14ac:dyDescent="0.35">
       <c r="A655" s="2" t="s">
@@ -25590,7 +26296,9 @@
       <c r="G655" s="2">
         <v>7</v>
       </c>
-      <c r="H655" s="2"/>
+      <c r="H655" s="2">
+        <v>0</v>
+      </c>
     </row>
     <row r="656" spans="1:8" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A656" s="2" t="s">
@@ -25614,7 +26322,9 @@
       <c r="G656" s="2">
         <v>7</v>
       </c>
-      <c r="H656" s="2"/>
+      <c r="H656" s="2" t="s">
+        <v>2945</v>
+      </c>
     </row>
     <row r="657" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A657" s="2" t="s">
@@ -25638,7 +26348,9 @@
       <c r="G657" s="2">
         <v>7</v>
       </c>
-      <c r="H657" s="2"/>
+      <c r="H657" s="2" t="s">
+        <v>2945</v>
+      </c>
     </row>
     <row r="658" spans="1:8" ht="29" x14ac:dyDescent="0.35">
       <c r="A658" s="2" t="s">
@@ -25662,7 +26374,9 @@
       <c r="G658" s="2">
         <v>7</v>
       </c>
-      <c r="H658" s="2"/>
+      <c r="H658" s="2" t="s">
+        <v>2945</v>
+      </c>
     </row>
     <row r="659" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A659" s="2" t="s">
@@ -25686,7 +26400,9 @@
       <c r="G659" s="2">
         <v>7</v>
       </c>
-      <c r="H659" s="2"/>
+      <c r="H659" s="2" t="s">
+        <v>2945</v>
+      </c>
     </row>
     <row r="660" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A660" s="2" t="s">
@@ -25710,7 +26426,9 @@
       <c r="G660" s="2">
         <v>7</v>
       </c>
-      <c r="H660" s="2"/>
+      <c r="H660" s="2" t="s">
+        <v>2945</v>
+      </c>
     </row>
     <row r="661" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A661" s="2" t="s">
@@ -25734,7 +26452,9 @@
       <c r="G661" s="2">
         <v>7</v>
       </c>
-      <c r="H661" s="2"/>
+      <c r="H661" s="2" t="s">
+        <v>2945</v>
+      </c>
     </row>
     <row r="662" spans="1:8" ht="29" x14ac:dyDescent="0.35">
       <c r="A662" s="2" t="s">
@@ -25758,7 +26478,9 @@
       <c r="G662" s="2">
         <v>7</v>
       </c>
-      <c r="H662" s="2"/>
+      <c r="H662" s="2" t="s">
+        <v>2946</v>
+      </c>
     </row>
     <row r="663" spans="1:8" ht="29" x14ac:dyDescent="0.35">
       <c r="A663" s="2" t="s">
@@ -25782,7 +26504,9 @@
       <c r="G663" s="2">
         <v>7</v>
       </c>
-      <c r="H663" s="2"/>
+      <c r="H663" s="2" t="s">
+        <v>2946</v>
+      </c>
     </row>
     <row r="664" spans="1:8" ht="29" x14ac:dyDescent="0.35">
       <c r="A664" s="2" t="s">
@@ -25806,7 +26530,9 @@
       <c r="G664" s="2">
         <v>7</v>
       </c>
-      <c r="H664" s="2"/>
+      <c r="H664" s="2" t="s">
+        <v>2945</v>
+      </c>
     </row>
     <row r="665" spans="1:8" ht="29" x14ac:dyDescent="0.35">
       <c r="A665" s="2" t="s">
@@ -25830,7 +26556,9 @@
       <c r="G665" s="2">
         <v>7</v>
       </c>
-      <c r="H665" s="2"/>
+      <c r="H665" s="2" t="s">
+        <v>2945</v>
+      </c>
     </row>
     <row r="666" spans="1:8" ht="87" x14ac:dyDescent="0.35">
       <c r="A666" s="2" t="s">
@@ -25854,7 +26582,9 @@
       <c r="G666" s="2">
         <v>7</v>
       </c>
-      <c r="H666" s="2"/>
+      <c r="H666" s="2" t="s">
+        <v>2946</v>
+      </c>
     </row>
     <row r="667" spans="1:8" ht="29" x14ac:dyDescent="0.35">
       <c r="A667" s="2" t="s">
@@ -25878,7 +26608,9 @@
       <c r="G667" s="2">
         <v>7</v>
       </c>
-      <c r="H667" s="2"/>
+      <c r="H667" s="2" t="s">
+        <v>2946</v>
+      </c>
     </row>
     <row r="668" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A668" s="2" t="s">
@@ -25902,7 +26634,9 @@
       <c r="G668" s="2">
         <v>7</v>
       </c>
-      <c r="H668" s="2"/>
+      <c r="H668" s="2" t="s">
+        <v>2946</v>
+      </c>
     </row>
     <row r="669" spans="1:8" ht="72.5" x14ac:dyDescent="0.35">
       <c r="A669" s="2" t="s">
@@ -25926,7 +26660,9 @@
       <c r="G669" s="2">
         <v>7</v>
       </c>
-      <c r="H669" s="2"/>
+      <c r="H669" s="2" t="s">
+        <v>2946</v>
+      </c>
     </row>
     <row r="670" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A670" s="2" t="s">
@@ -25950,7 +26686,9 @@
       <c r="G670" s="2">
         <v>7</v>
       </c>
-      <c r="H670" s="2"/>
+      <c r="H670" s="2" t="s">
+        <v>2945</v>
+      </c>
     </row>
     <row r="671" spans="1:8" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A671" s="2" t="s">
@@ -25974,7 +26712,9 @@
       <c r="G671" s="2">
         <v>7</v>
       </c>
-      <c r="H671" s="2"/>
+      <c r="H671" s="2" t="s">
+        <v>2945</v>
+      </c>
     </row>
     <row r="672" spans="1:8" ht="58" x14ac:dyDescent="0.35">
       <c r="A672" s="2" t="s">
@@ -25998,7 +26738,9 @@
       <c r="G672" s="2">
         <v>7</v>
       </c>
-      <c r="H672" s="2"/>
+      <c r="H672" s="2" t="s">
+        <v>2946</v>
+      </c>
     </row>
     <row r="673" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A673" s="2" t="s">
@@ -26022,7 +26764,9 @@
       <c r="G673" s="2">
         <v>7</v>
       </c>
-      <c r="H673" s="2"/>
+      <c r="H673" s="2" t="s">
+        <v>2946</v>
+      </c>
     </row>
     <row r="674" spans="1:8" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A674" s="2" t="s">
@@ -26046,7 +26790,9 @@
       <c r="G674" s="2">
         <v>7</v>
       </c>
-      <c r="H674" s="2"/>
+      <c r="H674" s="2" t="s">
+        <v>2946</v>
+      </c>
     </row>
     <row r="675" spans="1:8" ht="29" x14ac:dyDescent="0.35">
       <c r="A675" s="2" t="s">
@@ -26070,7 +26816,9 @@
       <c r="G675" s="2">
         <v>7</v>
       </c>
-      <c r="H675" s="2"/>
+      <c r="H675" s="2">
+        <v>0</v>
+      </c>
     </row>
     <row r="676" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A676" s="2" t="s">
@@ -26094,7 +26842,9 @@
       <c r="G676" s="2">
         <v>7</v>
       </c>
-      <c r="H676" s="2"/>
+      <c r="H676" s="2" t="s">
+        <v>2945</v>
+      </c>
     </row>
     <row r="677" spans="1:8" ht="29" x14ac:dyDescent="0.35">
       <c r="A677" s="2" t="s">
@@ -26118,7 +26868,9 @@
       <c r="G677" s="2">
         <v>7</v>
       </c>
-      <c r="H677" s="2"/>
+      <c r="H677" s="2" t="s">
+        <v>2946</v>
+      </c>
     </row>
     <row r="678" spans="1:8" ht="58" x14ac:dyDescent="0.35">
       <c r="A678" s="2" t="s">
@@ -26142,7 +26894,9 @@
       <c r="G678" s="2">
         <v>7</v>
       </c>
-      <c r="H678" s="2"/>
+      <c r="H678" s="2" t="s">
+        <v>2946</v>
+      </c>
     </row>
     <row r="679" spans="1:8" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A679" s="2" t="s">
@@ -26166,7 +26920,9 @@
       <c r="G679" s="2">
         <v>7</v>
       </c>
-      <c r="H679" s="2"/>
+      <c r="H679" s="2" t="s">
+        <v>2946</v>
+      </c>
     </row>
     <row r="680" spans="1:8" ht="29" x14ac:dyDescent="0.35">
       <c r="A680" s="2" t="s">
@@ -26190,7 +26946,9 @@
       <c r="G680" s="2">
         <v>7</v>
       </c>
-      <c r="H680" s="2"/>
+      <c r="H680" s="2" t="s">
+        <v>2946</v>
+      </c>
     </row>
     <row r="681" spans="1:8" ht="29" x14ac:dyDescent="0.35">
       <c r="A681" s="2" t="s">
@@ -26214,7 +26972,9 @@
       <c r="G681" s="2">
         <v>7</v>
       </c>
-      <c r="H681" s="2"/>
+      <c r="H681" s="2" t="s">
+        <v>2945</v>
+      </c>
     </row>
     <row r="682" spans="1:8" ht="87" x14ac:dyDescent="0.35">
       <c r="A682" s="2" t="s">
@@ -26238,7 +26998,9 @@
       <c r="G682" s="2">
         <v>7</v>
       </c>
-      <c r="H682" s="2"/>
+      <c r="H682" s="2" t="s">
+        <v>2945</v>
+      </c>
     </row>
     <row r="683" spans="1:8" ht="58" x14ac:dyDescent="0.35">
       <c r="A683" s="2" t="s">
@@ -26262,7 +27024,9 @@
       <c r="G683" s="2">
         <v>7</v>
       </c>
-      <c r="H683" s="2"/>
+      <c r="H683" s="2" t="s">
+        <v>2946</v>
+      </c>
     </row>
     <row r="684" spans="1:8" ht="29" x14ac:dyDescent="0.35">
       <c r="A684" s="2" t="s">
@@ -26286,7 +27050,9 @@
       <c r="G684" s="2">
         <v>7</v>
       </c>
-      <c r="H684" s="2"/>
+      <c r="H684" s="2" t="s">
+        <v>2946</v>
+      </c>
     </row>
     <row r="685" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A685" s="2" t="s">
@@ -26310,7 +27076,9 @@
       <c r="G685" s="2">
         <v>7</v>
       </c>
-      <c r="H685" s="2"/>
+      <c r="H685" s="2" t="s">
+        <v>2945</v>
+      </c>
     </row>
     <row r="686" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A686" s="2" t="s">
@@ -26334,7 +27102,9 @@
       <c r="G686" s="2">
         <v>7</v>
       </c>
-      <c r="H686" s="2"/>
+      <c r="H686" s="2" t="s">
+        <v>2946</v>
+      </c>
     </row>
     <row r="687" spans="1:8" ht="29" x14ac:dyDescent="0.35">
       <c r="A687" s="2" t="s">
@@ -26358,7 +27128,9 @@
       <c r="G687" s="2">
         <v>7</v>
       </c>
-      <c r="H687" s="2"/>
+      <c r="H687" s="2" t="s">
+        <v>2946</v>
+      </c>
     </row>
     <row r="688" spans="1:8" ht="29" x14ac:dyDescent="0.35">
       <c r="A688" s="2" t="s">
@@ -26382,7 +27154,9 @@
       <c r="G688" s="2">
         <v>7</v>
       </c>
-      <c r="H688" s="2"/>
+      <c r="H688" s="2" t="s">
+        <v>2946</v>
+      </c>
     </row>
     <row r="689" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A689" s="2" t="s">
@@ -26406,7 +27180,9 @@
       <c r="G689" s="2">
         <v>7</v>
       </c>
-      <c r="H689" s="2"/>
+      <c r="H689" s="2" t="s">
+        <v>2946</v>
+      </c>
     </row>
     <row r="690" spans="1:8" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A690" s="2" t="s">
@@ -26430,7 +27206,9 @@
       <c r="G690" s="2">
         <v>7</v>
       </c>
-      <c r="H690" s="2"/>
+      <c r="H690" s="2" t="s">
+        <v>2946</v>
+      </c>
     </row>
     <row r="691" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A691" s="2" t="s">
@@ -26454,7 +27232,9 @@
       <c r="G691" s="2">
         <v>7</v>
       </c>
-      <c r="H691" s="2"/>
+      <c r="H691" s="2" t="s">
+        <v>2945</v>
+      </c>
     </row>
     <row r="692" spans="1:8" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A692" s="2" t="s">
@@ -26478,7 +27258,9 @@
       <c r="G692" s="2">
         <v>7</v>
       </c>
-      <c r="H692" s="2"/>
+      <c r="H692" s="2" t="s">
+        <v>2946</v>
+      </c>
     </row>
     <row r="693" spans="1:8" ht="29" x14ac:dyDescent="0.35">
       <c r="A693" s="2" t="s">
@@ -26502,7 +27284,9 @@
       <c r="G693" s="2">
         <v>7</v>
       </c>
-      <c r="H693" s="2"/>
+      <c r="H693" s="2" t="s">
+        <v>2945</v>
+      </c>
     </row>
     <row r="694" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A694" s="2" t="s">
@@ -26526,7 +27310,9 @@
       <c r="G694" s="2">
         <v>7</v>
       </c>
-      <c r="H694" s="2"/>
+      <c r="H694" s="2" t="s">
+        <v>2945</v>
+      </c>
     </row>
     <row r="695" spans="1:8" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A695" s="2" t="s">
@@ -26550,7 +27336,9 @@
       <c r="G695" s="2">
         <v>7</v>
       </c>
-      <c r="H695" s="2"/>
+      <c r="H695" s="2" t="s">
+        <v>2946</v>
+      </c>
     </row>
     <row r="696" spans="1:8" ht="87" x14ac:dyDescent="0.35">
       <c r="A696" s="2" t="s">
@@ -26574,7 +27362,9 @@
       <c r="G696" s="2">
         <v>7</v>
       </c>
-      <c r="H696" s="2"/>
+      <c r="H696" s="2">
+        <v>0</v>
+      </c>
     </row>
     <row r="697" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A697" s="2" t="s">
@@ -26598,7 +27388,9 @@
       <c r="G697" s="2">
         <v>7</v>
       </c>
-      <c r="H697" s="2"/>
+      <c r="H697" s="2" t="s">
+        <v>2945</v>
+      </c>
     </row>
     <row r="698" spans="1:8" ht="29" x14ac:dyDescent="0.35">
       <c r="A698" s="2" t="s">
@@ -26622,7 +27414,9 @@
       <c r="G698" s="2">
         <v>7</v>
       </c>
-      <c r="H698" s="2"/>
+      <c r="H698" s="2" t="s">
+        <v>2946</v>
+      </c>
     </row>
     <row r="699" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A699" s="2" t="s">
@@ -26646,7 +27440,9 @@
       <c r="G699" s="2">
         <v>7</v>
       </c>
-      <c r="H699" s="2"/>
+      <c r="H699" s="2">
+        <v>0</v>
+      </c>
     </row>
     <row r="700" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A700" s="2" t="s">
@@ -26670,7 +27466,9 @@
       <c r="G700" s="2">
         <v>7</v>
       </c>
-      <c r="H700" s="2"/>
+      <c r="H700" s="2" t="s">
+        <v>2946</v>
+      </c>
     </row>
     <row r="701" spans="1:8" ht="58" x14ac:dyDescent="0.35">
       <c r="A701" s="2" t="s">
@@ -26694,7 +27492,9 @@
       <c r="G701" s="2">
         <v>7</v>
       </c>
-      <c r="H701" s="2"/>
+      <c r="H701" s="2" t="s">
+        <v>2946</v>
+      </c>
     </row>
     <row r="702" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A702" s="2" t="s">
@@ -26718,7 +27518,9 @@
       <c r="G702" s="2">
         <v>8</v>
       </c>
-      <c r="H702" s="2"/>
+      <c r="H702" s="2" t="s">
+        <v>2945</v>
+      </c>
     </row>
     <row r="703" spans="1:8" ht="87" x14ac:dyDescent="0.35">
       <c r="A703" s="2" t="s">
@@ -26742,7 +27544,9 @@
       <c r="G703" s="2">
         <v>8</v>
       </c>
-      <c r="H703" s="2"/>
+      <c r="H703" s="2">
+        <v>0</v>
+      </c>
     </row>
     <row r="704" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A704" s="2" t="s">
@@ -26766,7 +27570,9 @@
       <c r="G704" s="2">
         <v>8</v>
       </c>
-      <c r="H704" s="2"/>
+      <c r="H704" s="2" t="s">
+        <v>2945</v>
+      </c>
     </row>
     <row r="705" spans="1:8" ht="29" x14ac:dyDescent="0.35">
       <c r="A705" s="2" t="s">
@@ -26790,7 +27596,9 @@
       <c r="G705" s="2">
         <v>8</v>
       </c>
-      <c r="H705" s="2"/>
+      <c r="H705" s="2" t="s">
+        <v>2946</v>
+      </c>
     </row>
     <row r="706" spans="1:8" ht="29" x14ac:dyDescent="0.35">
       <c r="A706" s="2" t="s">
@@ -26814,7 +27622,9 @@
       <c r="G706" s="2">
         <v>8</v>
       </c>
-      <c r="H706" s="2"/>
+      <c r="H706" s="2" t="s">
+        <v>2946</v>
+      </c>
     </row>
     <row r="707" spans="1:8" ht="29" x14ac:dyDescent="0.35">
       <c r="A707" s="2" t="s">
@@ -26838,7 +27648,9 @@
       <c r="G707" s="2">
         <v>8</v>
       </c>
-      <c r="H707" s="2"/>
+      <c r="H707" s="2" t="s">
+        <v>2946</v>
+      </c>
     </row>
     <row r="708" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A708" s="2" t="s">
@@ -26862,7 +27674,9 @@
       <c r="G708" s="2">
         <v>8</v>
       </c>
-      <c r="H708" s="2"/>
+      <c r="H708" s="2" t="s">
+        <v>2945</v>
+      </c>
     </row>
     <row r="709" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A709" s="2" t="s">
@@ -26886,7 +27700,9 @@
       <c r="G709" s="2">
         <v>8</v>
       </c>
-      <c r="H709" s="2"/>
+      <c r="H709" s="2" t="s">
+        <v>2945</v>
+      </c>
     </row>
     <row r="710" spans="1:8" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A710" s="2" t="s">
@@ -26910,7 +27726,9 @@
       <c r="G710" s="2">
         <v>8</v>
       </c>
-      <c r="H710" s="2"/>
+      <c r="H710" s="2" t="s">
+        <v>2946</v>
+      </c>
     </row>
     <row r="711" spans="1:8" ht="29" x14ac:dyDescent="0.35">
       <c r="A711" s="2" t="s">
@@ -26934,7 +27752,9 @@
       <c r="G711" s="2">
         <v>8</v>
       </c>
-      <c r="H711" s="2"/>
+      <c r="H711" s="2" t="s">
+        <v>2946</v>
+      </c>
     </row>
     <row r="712" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A712" s="2" t="s">
@@ -26958,7 +27778,9 @@
       <c r="G712" s="2">
         <v>8</v>
       </c>
-      <c r="H712" s="2"/>
+      <c r="H712" s="2">
+        <v>0</v>
+      </c>
     </row>
     <row r="713" spans="1:8" ht="58" x14ac:dyDescent="0.35">
       <c r="A713" s="2" t="s">
@@ -26982,7 +27804,9 @@
       <c r="G713" s="2">
         <v>8</v>
       </c>
-      <c r="H713" s="2"/>
+      <c r="H713" s="2" t="s">
+        <v>2946</v>
+      </c>
     </row>
     <row r="714" spans="1:8" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A714" s="2" t="s">
@@ -27006,7 +27830,9 @@
       <c r="G714" s="2">
         <v>8</v>
       </c>
-      <c r="H714" s="2"/>
+      <c r="H714" s="2" t="s">
+        <v>2945</v>
+      </c>
     </row>
     <row r="715" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A715" s="2" t="s">
@@ -27030,7 +27856,9 @@
       <c r="G715" s="2">
         <v>8</v>
       </c>
-      <c r="H715" s="2"/>
+      <c r="H715" s="2" t="s">
+        <v>2945</v>
+      </c>
     </row>
     <row r="716" spans="1:8" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A716" s="2" t="s">
@@ -27054,7 +27882,9 @@
       <c r="G716" s="2">
         <v>8</v>
       </c>
-      <c r="H716" s="2"/>
+      <c r="H716" s="2" t="s">
+        <v>2946</v>
+      </c>
     </row>
     <row r="717" spans="1:8" ht="72.5" x14ac:dyDescent="0.35">
       <c r="A717" s="2" t="s">
@@ -27078,7 +27908,9 @@
       <c r="G717" s="2">
         <v>8</v>
       </c>
-      <c r="H717" s="2"/>
+      <c r="H717" s="2" t="s">
+        <v>2946</v>
+      </c>
     </row>
     <row r="718" spans="1:8" ht="58" x14ac:dyDescent="0.35">
       <c r="A718" s="2" t="s">
@@ -27102,7 +27934,9 @@
       <c r="G718" s="2">
         <v>8</v>
       </c>
-      <c r="H718" s="2"/>
+      <c r="H718" s="2" t="s">
+        <v>2945</v>
+      </c>
     </row>
     <row r="719" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A719" s="2" t="s">
@@ -27126,7 +27960,9 @@
       <c r="G719" s="2">
         <v>8</v>
       </c>
-      <c r="H719" s="2"/>
+      <c r="H719" s="2" t="s">
+        <v>2945</v>
+      </c>
     </row>
     <row r="720" spans="1:8" ht="29" x14ac:dyDescent="0.35">
       <c r="A720" s="2" t="s">
@@ -27150,7 +27986,9 @@
       <c r="G720" s="2">
         <v>8</v>
       </c>
-      <c r="H720" s="2"/>
+      <c r="H720" s="2" t="s">
+        <v>2946</v>
+      </c>
     </row>
     <row r="721" spans="1:8" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A721" s="2" t="s">
@@ -27174,7 +28012,9 @@
       <c r="G721" s="2">
         <v>8</v>
       </c>
-      <c r="H721" s="2"/>
+      <c r="H721" s="2" t="s">
+        <v>2946</v>
+      </c>
     </row>
     <row r="722" spans="1:8" ht="58" x14ac:dyDescent="0.35">
       <c r="A722" s="2" t="s">
@@ -27198,7 +28038,9 @@
       <c r="G722" s="2">
         <v>8</v>
       </c>
-      <c r="H722" s="2"/>
+      <c r="H722" s="2" t="s">
+        <v>2945</v>
+      </c>
     </row>
     <row r="723" spans="1:8" ht="72.5" x14ac:dyDescent="0.35">
       <c r="A723" s="2" t="s">
@@ -27222,7 +28064,9 @@
       <c r="G723" s="2">
         <v>8</v>
       </c>
-      <c r="H723" s="2"/>
+      <c r="H723" s="2" t="s">
+        <v>2946</v>
+      </c>
     </row>
     <row r="724" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A724" s="2" t="s">
@@ -27246,7 +28090,9 @@
       <c r="G724" s="2">
         <v>8</v>
       </c>
-      <c r="H724" s="2"/>
+      <c r="H724" s="2" t="s">
+        <v>2945</v>
+      </c>
     </row>
     <row r="725" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A725" s="2" t="s">
@@ -27270,7 +28116,9 @@
       <c r="G725" s="2">
         <v>8</v>
       </c>
-      <c r="H725" s="2"/>
+      <c r="H725" s="2" t="s">
+        <v>2945</v>
+      </c>
     </row>
     <row r="726" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A726" s="2" t="s">
@@ -27294,7 +28142,9 @@
       <c r="G726" s="2">
         <v>8</v>
       </c>
-      <c r="H726" s="2"/>
+      <c r="H726" s="2" t="s">
+        <v>2945</v>
+      </c>
     </row>
     <row r="727" spans="1:8" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A727" s="2" t="s">
@@ -27318,7 +28168,9 @@
       <c r="G727" s="2">
         <v>8</v>
       </c>
-      <c r="H727" s="2"/>
+      <c r="H727" s="2" t="s">
+        <v>2946</v>
+      </c>
     </row>
     <row r="728" spans="1:8" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A728" s="2" t="s">
@@ -27342,7 +28194,9 @@
       <c r="G728" s="2">
         <v>8</v>
       </c>
-      <c r="H728" s="2"/>
+      <c r="H728" s="2" t="s">
+        <v>2945</v>
+      </c>
     </row>
     <row r="729" spans="1:8" ht="29" x14ac:dyDescent="0.35">
       <c r="A729" s="2" t="s">
@@ -27366,7 +28220,9 @@
       <c r="G729" s="2">
         <v>8</v>
       </c>
-      <c r="H729" s="2"/>
+      <c r="H729" s="2" t="s">
+        <v>2946</v>
+      </c>
     </row>
     <row r="730" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A730" s="2" t="s">
@@ -27390,7 +28246,9 @@
       <c r="G730" s="2">
         <v>8</v>
       </c>
-      <c r="H730" s="2"/>
+      <c r="H730" s="2" t="s">
+        <v>2946</v>
+      </c>
     </row>
     <row r="731" spans="1:8" ht="58" x14ac:dyDescent="0.35">
       <c r="A731" s="2" t="s">
@@ -27414,7 +28272,9 @@
       <c r="G731" s="2">
         <v>8</v>
       </c>
-      <c r="H731" s="2"/>
+      <c r="H731" s="2" t="s">
+        <v>2946</v>
+      </c>
     </row>
     <row r="732" spans="1:8" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A732" s="2" t="s">
@@ -27438,7 +28298,9 @@
       <c r="G732" s="2">
         <v>8</v>
       </c>
-      <c r="H732" s="2"/>
+      <c r="H732" s="2" t="s">
+        <v>2946</v>
+      </c>
     </row>
     <row r="733" spans="1:8" ht="29" x14ac:dyDescent="0.35">
       <c r="A733" s="2" t="s">
@@ -27462,7 +28324,9 @@
       <c r="G733" s="2">
         <v>8</v>
       </c>
-      <c r="H733" s="2"/>
+      <c r="H733" s="2" t="s">
+        <v>2946</v>
+      </c>
     </row>
     <row r="734" spans="1:8" ht="58" x14ac:dyDescent="0.35">
       <c r="A734" s="2" t="s">
@@ -27486,7 +28350,9 @@
       <c r="G734" s="2">
         <v>8</v>
       </c>
-      <c r="H734" s="2"/>
+      <c r="H734" s="2" t="s">
+        <v>2945</v>
+      </c>
     </row>
     <row r="735" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A735" s="2" t="s">
@@ -27510,7 +28376,9 @@
       <c r="G735" s="2">
         <v>8</v>
       </c>
-      <c r="H735" s="2"/>
+      <c r="H735" s="2" t="s">
+        <v>2945</v>
+      </c>
     </row>
     <row r="736" spans="1:8" ht="29" x14ac:dyDescent="0.35">
       <c r="A736" s="2" t="s">
@@ -27534,7 +28402,9 @@
       <c r="G736" s="2">
         <v>8</v>
       </c>
-      <c r="H736" s="2"/>
+      <c r="H736" s="2" t="s">
+        <v>2945</v>
+      </c>
     </row>
     <row r="737" spans="1:8" ht="29" x14ac:dyDescent="0.35">
       <c r="A737" s="2" t="s">
@@ -27558,7 +28428,9 @@
       <c r="G737" s="2">
         <v>8</v>
       </c>
-      <c r="H737" s="2"/>
+      <c r="H737" s="2">
+        <v>0</v>
+      </c>
     </row>
     <row r="738" spans="1:8" ht="29" x14ac:dyDescent="0.35">
       <c r="A738" s="2" t="s">
@@ -27582,7 +28454,9 @@
       <c r="G738" s="2">
         <v>8</v>
       </c>
-      <c r="H738" s="2"/>
+      <c r="H738" s="2" t="s">
+        <v>2946</v>
+      </c>
     </row>
     <row r="739" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A739" s="2" t="s">
@@ -27606,7 +28480,9 @@
       <c r="G739" s="2">
         <v>8</v>
       </c>
-      <c r="H739" s="2"/>
+      <c r="H739" s="2">
+        <v>0</v>
+      </c>
     </row>
     <row r="740" spans="1:8" ht="29" x14ac:dyDescent="0.35">
       <c r="A740" s="2" t="s">
@@ -27630,7 +28506,9 @@
       <c r="G740" s="2">
         <v>8</v>
       </c>
-      <c r="H740" s="2"/>
+      <c r="H740" s="2">
+        <v>0</v>
+      </c>
     </row>
     <row r="741" spans="1:8" ht="87" x14ac:dyDescent="0.35">
       <c r="A741" s="2" t="s">
@@ -27654,7 +28532,9 @@
       <c r="G741" s="2">
         <v>8</v>
       </c>
-      <c r="H741" s="2"/>
+      <c r="H741" s="2" t="s">
+        <v>2946</v>
+      </c>
     </row>
     <row r="742" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A742" s="2" t="s">
@@ -27678,7 +28558,9 @@
       <c r="G742" s="2">
         <v>8</v>
       </c>
-      <c r="H742" s="2"/>
+      <c r="H742" s="2" t="s">
+        <v>2946</v>
+      </c>
     </row>
     <row r="743" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A743" s="2" t="s">
@@ -27702,7 +28584,9 @@
       <c r="G743" s="2">
         <v>8</v>
       </c>
-      <c r="H743" s="2"/>
+      <c r="H743" s="2" t="s">
+        <v>2945</v>
+      </c>
     </row>
     <row r="744" spans="1:8" ht="29" x14ac:dyDescent="0.35">
       <c r="A744" s="2" t="s">
@@ -27726,7 +28610,9 @@
       <c r="G744" s="2">
         <v>8</v>
       </c>
-      <c r="H744" s="2"/>
+      <c r="H744" s="2" t="s">
+        <v>2946</v>
+      </c>
     </row>
     <row r="745" spans="1:8" ht="87" x14ac:dyDescent="0.35">
       <c r="A745" s="2" t="s">
@@ -27750,7 +28636,9 @@
       <c r="G745" s="2">
         <v>8</v>
       </c>
-      <c r="H745" s="2"/>
+      <c r="H745" s="2" t="s">
+        <v>2946</v>
+      </c>
     </row>
     <row r="746" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A746" s="2" t="s">
@@ -27774,7 +28662,9 @@
       <c r="G746" s="2">
         <v>8</v>
       </c>
-      <c r="H746" s="2"/>
+      <c r="H746" s="2" t="s">
+        <v>2945</v>
+      </c>
     </row>
     <row r="747" spans="1:8" ht="29" x14ac:dyDescent="0.35">
       <c r="A747" s="2" t="s">
@@ -27798,7 +28688,9 @@
       <c r="G747" s="2">
         <v>8</v>
       </c>
-      <c r="H747" s="2"/>
+      <c r="H747" s="2" t="s">
+        <v>2946</v>
+      </c>
     </row>
     <row r="748" spans="1:8" ht="29" x14ac:dyDescent="0.35">
       <c r="A748" s="2" t="s">
@@ -27822,7 +28714,9 @@
       <c r="G748" s="2">
         <v>8</v>
       </c>
-      <c r="H748" s="2"/>
+      <c r="H748" s="2" t="s">
+        <v>2946</v>
+      </c>
     </row>
     <row r="749" spans="1:8" ht="29" x14ac:dyDescent="0.35">
       <c r="A749" s="2" t="s">
@@ -27846,7 +28740,9 @@
       <c r="G749" s="2">
         <v>8</v>
       </c>
-      <c r="H749" s="2"/>
+      <c r="H749" s="2" t="s">
+        <v>2946</v>
+      </c>
     </row>
     <row r="750" spans="1:8" ht="29" x14ac:dyDescent="0.35">
       <c r="A750" s="2" t="s">
@@ -27870,7 +28766,9 @@
       <c r="G750" s="2">
         <v>8</v>
       </c>
-      <c r="H750" s="2"/>
+      <c r="H750" s="2" t="s">
+        <v>2946</v>
+      </c>
     </row>
     <row r="751" spans="1:8" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A751" s="2" t="s">
@@ -27894,7 +28792,9 @@
       <c r="G751" s="2">
         <v>8</v>
       </c>
-      <c r="H751" s="2"/>
+      <c r="H751" s="2" t="s">
+        <v>2946</v>
+      </c>
     </row>
     <row r="752" spans="1:8" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A752" s="2" t="s">
@@ -27918,7 +28818,9 @@
       <c r="G752" s="2">
         <v>8</v>
       </c>
-      <c r="H752" s="2"/>
+      <c r="H752" s="2" t="s">
+        <v>2946</v>
+      </c>
     </row>
     <row r="753" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A753" s="2" t="s">
@@ -27942,7 +28844,9 @@
       <c r="G753" s="2">
         <v>8</v>
       </c>
-      <c r="H753" s="2"/>
+      <c r="H753" s="2" t="s">
+        <v>2946</v>
+      </c>
     </row>
     <row r="754" spans="1:8" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A754" s="2" t="s">
@@ -27966,7 +28870,9 @@
       <c r="G754" s="2">
         <v>8</v>
       </c>
-      <c r="H754" s="2"/>
+      <c r="H754" s="2" t="s">
+        <v>2946</v>
+      </c>
     </row>
     <row r="755" spans="1:8" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A755" s="2" t="s">
@@ -27990,7 +28896,9 @@
       <c r="G755" s="2">
         <v>8</v>
       </c>
-      <c r="H755" s="2"/>
+      <c r="H755" s="2" t="s">
+        <v>2945</v>
+      </c>
     </row>
     <row r="756" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A756" s="2" t="s">
@@ -28014,7 +28922,9 @@
       <c r="G756" s="2">
         <v>8</v>
       </c>
-      <c r="H756" s="2"/>
+      <c r="H756" s="2" t="s">
+        <v>2946</v>
+      </c>
     </row>
     <row r="757" spans="1:8" ht="29" x14ac:dyDescent="0.35">
       <c r="A757" s="2" t="s">
@@ -28038,7 +28948,9 @@
       <c r="G757" s="2">
         <v>8</v>
       </c>
-      <c r="H757" s="2"/>
+      <c r="H757" s="2" t="s">
+        <v>2945</v>
+      </c>
     </row>
     <row r="758" spans="1:8" ht="29" x14ac:dyDescent="0.35">
       <c r="A758" s="2" t="s">
@@ -28062,7 +28974,9 @@
       <c r="G758" s="2">
         <v>8</v>
       </c>
-      <c r="H758" s="2"/>
+      <c r="H758" s="2" t="s">
+        <v>2945</v>
+      </c>
     </row>
     <row r="759" spans="1:8" ht="29" x14ac:dyDescent="0.35">
       <c r="A759" s="2" t="s">
@@ -28086,7 +29000,9 @@
       <c r="G759" s="2">
         <v>8</v>
       </c>
-      <c r="H759" s="2"/>
+      <c r="H759" s="2" t="s">
+        <v>2946</v>
+      </c>
     </row>
     <row r="760" spans="1:8" ht="29" x14ac:dyDescent="0.35">
       <c r="A760" s="2" t="s">
@@ -28110,7 +29026,9 @@
       <c r="G760" s="2">
         <v>8</v>
       </c>
-      <c r="H760" s="2"/>
+      <c r="H760" s="2">
+        <v>0</v>
+      </c>
     </row>
     <row r="761" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A761" s="2" t="s">
@@ -28134,7 +29052,9 @@
       <c r="G761" s="2">
         <v>8</v>
       </c>
-      <c r="H761" s="2"/>
+      <c r="H761" s="2" t="s">
+        <v>2945</v>
+      </c>
     </row>
     <row r="762" spans="1:8" ht="58" x14ac:dyDescent="0.35">
       <c r="A762" s="2" t="s">
@@ -28158,7 +29078,9 @@
       <c r="G762" s="2">
         <v>8</v>
       </c>
-      <c r="H762" s="2"/>
+      <c r="H762" s="2" t="s">
+        <v>2946</v>
+      </c>
     </row>
     <row r="763" spans="1:8" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A763" s="2" t="s">
@@ -28182,7 +29104,9 @@
       <c r="G763" s="2">
         <v>8</v>
       </c>
-      <c r="H763" s="2"/>
+      <c r="H763" s="2" t="s">
+        <v>2946</v>
+      </c>
     </row>
     <row r="764" spans="1:8" ht="29" x14ac:dyDescent="0.35">
       <c r="A764" s="2" t="s">
@@ -28206,7 +29130,9 @@
       <c r="G764" s="2">
         <v>8</v>
       </c>
-      <c r="H764" s="2"/>
+      <c r="H764" s="2" t="s">
+        <v>2945</v>
+      </c>
     </row>
     <row r="765" spans="1:8" ht="29" x14ac:dyDescent="0.35">
       <c r="A765" s="2" t="s">
@@ -28230,7 +29156,9 @@
       <c r="G765" s="2">
         <v>8</v>
       </c>
-      <c r="H765" s="2"/>
+      <c r="H765" s="2" t="s">
+        <v>2946</v>
+      </c>
     </row>
     <row r="766" spans="1:8" ht="29" x14ac:dyDescent="0.35">
       <c r="A766" s="2" t="s">
@@ -28254,7 +29182,9 @@
       <c r="G766" s="2">
         <v>8</v>
       </c>
-      <c r="H766" s="2"/>
+      <c r="H766" s="2" t="s">
+        <v>2945</v>
+      </c>
     </row>
     <row r="767" spans="1:8" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A767" s="2" t="s">
@@ -28278,7 +29208,9 @@
       <c r="G767" s="2">
         <v>8</v>
       </c>
-      <c r="H767" s="2"/>
+      <c r="H767" s="2" t="s">
+        <v>2945</v>
+      </c>
     </row>
     <row r="768" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A768" s="2" t="s">
@@ -28302,7 +29234,9 @@
       <c r="G768" s="2">
         <v>8</v>
       </c>
-      <c r="H768" s="2"/>
+      <c r="H768" s="2" t="s">
+        <v>2945</v>
+      </c>
     </row>
     <row r="769" spans="1:8" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A769" s="2" t="s">
@@ -28326,7 +29260,9 @@
       <c r="G769" s="2">
         <v>8</v>
       </c>
-      <c r="H769" s="2"/>
+      <c r="H769" s="2" t="s">
+        <v>2946</v>
+      </c>
     </row>
     <row r="770" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A770" s="2" t="s">
@@ -28350,7 +29286,9 @@
       <c r="G770" s="2">
         <v>8</v>
       </c>
-      <c r="H770" s="2"/>
+      <c r="H770" s="2" t="s">
+        <v>2945</v>
+      </c>
     </row>
     <row r="771" spans="1:8" ht="29" x14ac:dyDescent="0.35">
       <c r="A771" s="2" t="s">
@@ -28374,7 +29312,9 @@
       <c r="G771" s="2">
         <v>8</v>
       </c>
-      <c r="H771" s="2"/>
+      <c r="H771" s="2" t="s">
+        <v>2945</v>
+      </c>
     </row>
     <row r="772" spans="1:8" ht="29" x14ac:dyDescent="0.35">
       <c r="A772" s="2" t="s">
@@ -28398,7 +29338,9 @@
       <c r="G772" s="2">
         <v>8</v>
       </c>
-      <c r="H772" s="2"/>
+      <c r="H772" s="2" t="s">
+        <v>2946</v>
+      </c>
     </row>
     <row r="773" spans="1:8" ht="58" x14ac:dyDescent="0.35">
       <c r="A773" s="2" t="s">
@@ -28422,7 +29364,9 @@
       <c r="G773" s="2">
         <v>8</v>
       </c>
-      <c r="H773" s="2"/>
+      <c r="H773" s="2" t="s">
+        <v>2946</v>
+      </c>
     </row>
     <row r="774" spans="1:8" ht="29" x14ac:dyDescent="0.35">
       <c r="A774" s="2" t="s">
@@ -28446,7 +29390,9 @@
       <c r="G774" s="2">
         <v>8</v>
       </c>
-      <c r="H774" s="2"/>
+      <c r="H774" s="2" t="s">
+        <v>2946</v>
+      </c>
     </row>
     <row r="775" spans="1:8" ht="87" x14ac:dyDescent="0.35">
       <c r="A775" s="2" t="s">
@@ -28470,7 +29416,9 @@
       <c r="G775" s="2">
         <v>8</v>
       </c>
-      <c r="H775" s="2"/>
+      <c r="H775" s="2" t="s">
+        <v>2946</v>
+      </c>
     </row>
     <row r="776" spans="1:8" ht="29" x14ac:dyDescent="0.35">
       <c r="A776" s="2" t="s">
@@ -28494,7 +29442,9 @@
       <c r="G776" s="2">
         <v>8</v>
       </c>
-      <c r="H776" s="2"/>
+      <c r="H776" s="2" t="s">
+        <v>2946</v>
+      </c>
     </row>
     <row r="777" spans="1:8" ht="58" x14ac:dyDescent="0.35">
       <c r="A777" s="2" t="s">
@@ -28518,7 +29468,9 @@
       <c r="G777" s="2">
         <v>8</v>
       </c>
-      <c r="H777" s="2"/>
+      <c r="H777" s="2" t="s">
+        <v>2946</v>
+      </c>
     </row>
     <row r="778" spans="1:8" ht="29" x14ac:dyDescent="0.35">
       <c r="A778" s="2" t="s">
@@ -28542,7 +29494,9 @@
       <c r="G778" s="2">
         <v>8</v>
       </c>
-      <c r="H778" s="2"/>
+      <c r="H778" s="2" t="s">
+        <v>2946</v>
+      </c>
     </row>
     <row r="779" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A779" s="2" t="s">
@@ -28566,7 +29520,9 @@
       <c r="G779" s="2">
         <v>8</v>
       </c>
-      <c r="H779" s="2"/>
+      <c r="H779" s="2" t="s">
+        <v>2946</v>
+      </c>
     </row>
     <row r="780" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A780" s="2" t="s">
@@ -28590,7 +29546,9 @@
       <c r="G780" s="2">
         <v>8</v>
       </c>
-      <c r="H780" s="2"/>
+      <c r="H780" s="2" t="s">
+        <v>2945</v>
+      </c>
     </row>
     <row r="781" spans="1:8" ht="58" x14ac:dyDescent="0.35">
       <c r="A781" s="2" t="s">
@@ -28614,7 +29572,9 @@
       <c r="G781" s="2">
         <v>8</v>
       </c>
-      <c r="H781" s="2"/>
+      <c r="H781" s="2" t="s">
+        <v>2946</v>
+      </c>
     </row>
     <row r="782" spans="1:8" ht="58" x14ac:dyDescent="0.35">
       <c r="A782" s="2" t="s">
@@ -28638,7 +29598,9 @@
       <c r="G782" s="2">
         <v>8</v>
       </c>
-      <c r="H782" s="2"/>
+      <c r="H782" s="2" t="s">
+        <v>2946</v>
+      </c>
     </row>
     <row r="783" spans="1:8" ht="29" x14ac:dyDescent="0.35">
       <c r="A783" s="2" t="s">
@@ -28662,7 +29624,9 @@
       <c r="G783" s="2">
         <v>8</v>
       </c>
-      <c r="H783" s="2"/>
+      <c r="H783" s="2">
+        <v>0</v>
+      </c>
     </row>
     <row r="784" spans="1:8" ht="87" x14ac:dyDescent="0.35">
       <c r="A784" s="2" t="s">
@@ -28686,7 +29650,9 @@
       <c r="G784" s="2">
         <v>8</v>
       </c>
-      <c r="H784" s="2"/>
+      <c r="H784" s="2" t="s">
+        <v>2946</v>
+      </c>
     </row>
     <row r="785" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A785" s="2" t="s">
@@ -28710,7 +29676,9 @@
       <c r="G785" s="2">
         <v>8</v>
       </c>
-      <c r="H785" s="2"/>
+      <c r="H785" s="2" t="s">
+        <v>2945</v>
+      </c>
     </row>
     <row r="786" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A786" s="2" t="s">
@@ -28734,7 +29702,9 @@
       <c r="G786" s="2">
         <v>8</v>
       </c>
-      <c r="H786" s="2"/>
+      <c r="H786" s="2" t="s">
+        <v>2946</v>
+      </c>
     </row>
     <row r="787" spans="1:8" ht="87" x14ac:dyDescent="0.35">
       <c r="A787" s="2" t="s">
@@ -28758,7 +29728,9 @@
       <c r="G787" s="2">
         <v>8</v>
       </c>
-      <c r="H787" s="2"/>
+      <c r="H787" s="2" t="s">
+        <v>2946</v>
+      </c>
     </row>
     <row r="788" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A788" s="2" t="s">
@@ -28782,7 +29754,9 @@
       <c r="G788" s="2">
         <v>8</v>
       </c>
-      <c r="H788" s="2"/>
+      <c r="H788" s="2" t="s">
+        <v>2945</v>
+      </c>
     </row>
     <row r="789" spans="1:8" ht="29" x14ac:dyDescent="0.35">
       <c r="A789" s="2" t="s">
@@ -28806,7 +29780,9 @@
       <c r="G789" s="2">
         <v>8</v>
       </c>
-      <c r="H789" s="2"/>
+      <c r="H789" s="2" t="s">
+        <v>2946</v>
+      </c>
     </row>
     <row r="790" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A790" s="2" t="s">
@@ -28830,7 +29806,9 @@
       <c r="G790" s="2">
         <v>8</v>
       </c>
-      <c r="H790" s="2"/>
+      <c r="H790" s="2" t="s">
+        <v>2945</v>
+      </c>
     </row>
     <row r="791" spans="1:8" ht="58" x14ac:dyDescent="0.35">
       <c r="A791" s="2" t="s">
@@ -28854,7 +29832,9 @@
       <c r="G791" s="2">
         <v>8</v>
       </c>
-      <c r="H791" s="2"/>
+      <c r="H791" s="2" t="s">
+        <v>2946</v>
+      </c>
     </row>
     <row r="792" spans="1:8" ht="58" x14ac:dyDescent="0.35">
       <c r="A792" s="2" t="s">
@@ -28878,7 +29858,9 @@
       <c r="G792" s="2">
         <v>8</v>
       </c>
-      <c r="H792" s="2"/>
+      <c r="H792" s="2" t="s">
+        <v>2946</v>
+      </c>
     </row>
     <row r="793" spans="1:8" ht="29" x14ac:dyDescent="0.35">
       <c r="A793" s="2" t="s">
@@ -28902,7 +29884,9 @@
       <c r="G793" s="2">
         <v>8</v>
       </c>
-      <c r="H793" s="2"/>
+      <c r="H793" s="2" t="s">
+        <v>2946</v>
+      </c>
     </row>
     <row r="794" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A794" s="2" t="s">
@@ -28926,7 +29910,9 @@
       <c r="G794" s="2">
         <v>8</v>
       </c>
-      <c r="H794" s="2"/>
+      <c r="H794" s="2" t="s">
+        <v>2945</v>
+      </c>
     </row>
     <row r="795" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A795" s="2" t="s">
@@ -28950,7 +29936,9 @@
       <c r="G795" s="2">
         <v>8</v>
       </c>
-      <c r="H795" s="2"/>
+      <c r="H795" s="2" t="s">
+        <v>2945</v>
+      </c>
     </row>
     <row r="796" spans="1:8" ht="29" x14ac:dyDescent="0.35">
       <c r="A796" s="2" t="s">
@@ -28974,7 +29962,9 @@
       <c r="G796" s="2">
         <v>8</v>
       </c>
-      <c r="H796" s="2"/>
+      <c r="H796" s="2">
+        <v>0</v>
+      </c>
     </row>
     <row r="797" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A797" s="2" t="s">
@@ -28998,7 +29988,9 @@
       <c r="G797" s="2">
         <v>8</v>
       </c>
-      <c r="H797" s="2"/>
+      <c r="H797" s="2" t="s">
+        <v>2946</v>
+      </c>
     </row>
     <row r="798" spans="1:8" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A798" s="2" t="s">
@@ -29022,7 +30014,9 @@
       <c r="G798" s="2">
         <v>8</v>
       </c>
-      <c r="H798" s="2"/>
+      <c r="H798" s="2">
+        <v>0</v>
+      </c>
     </row>
     <row r="799" spans="1:8" ht="29" x14ac:dyDescent="0.35">
       <c r="A799" s="2" t="s">
@@ -29046,7 +30040,9 @@
       <c r="G799" s="2">
         <v>8</v>
       </c>
-      <c r="H799" s="2"/>
+      <c r="H799" s="2" t="s">
+        <v>2946</v>
+      </c>
     </row>
     <row r="800" spans="1:8" ht="29" x14ac:dyDescent="0.35">
       <c r="A800" s="2" t="s">
@@ -29070,7 +30066,9 @@
       <c r="G800" s="2">
         <v>8</v>
       </c>
-      <c r="H800" s="2"/>
+      <c r="H800" s="2" t="s">
+        <v>2946</v>
+      </c>
     </row>
     <row r="801" spans="1:8" ht="29" x14ac:dyDescent="0.35">
       <c r="A801" s="2" t="s">
@@ -29094,7 +30092,9 @@
       <c r="G801" s="2">
         <v>8</v>
       </c>
-      <c r="H801" s="2"/>
+      <c r="H801" s="2" t="s">
+        <v>2945</v>
+      </c>
     </row>
     <row r="802" spans="1:8" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A802" s="2" t="s">
@@ -29118,7 +30118,9 @@
       <c r="G802" s="2">
         <v>9</v>
       </c>
-      <c r="H802" s="2"/>
+      <c r="H802" s="2" t="s">
+        <v>2946</v>
+      </c>
     </row>
     <row r="803" spans="1:8" ht="29" x14ac:dyDescent="0.35">
       <c r="A803" s="2" t="s">
@@ -29142,7 +30144,9 @@
       <c r="G803" s="2">
         <v>9</v>
       </c>
-      <c r="H803" s="2"/>
+      <c r="H803" s="2" t="s">
+        <v>2946</v>
+      </c>
     </row>
     <row r="804" spans="1:8" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A804" s="2" t="s">
@@ -29166,7 +30170,9 @@
       <c r="G804" s="2">
         <v>9</v>
       </c>
-      <c r="H804" s="2"/>
+      <c r="H804" s="2" t="s">
+        <v>2946</v>
+      </c>
     </row>
     <row r="805" spans="1:8" ht="58" x14ac:dyDescent="0.35">
       <c r="A805" s="2" t="s">
@@ -29190,7 +30196,9 @@
       <c r="G805" s="2">
         <v>9</v>
       </c>
-      <c r="H805" s="2"/>
+      <c r="H805" s="2">
+        <v>0</v>
+      </c>
     </row>
     <row r="806" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A806" s="2" t="s">
@@ -29214,7 +30222,9 @@
       <c r="G806" s="2">
         <v>9</v>
       </c>
-      <c r="H806" s="2"/>
+      <c r="H806" s="2" t="s">
+        <v>2946</v>
+      </c>
     </row>
     <row r="807" spans="1:8" ht="58" x14ac:dyDescent="0.35">
       <c r="A807" s="2" t="s">
@@ -29238,7 +30248,9 @@
       <c r="G807" s="2">
         <v>9</v>
       </c>
-      <c r="H807" s="2"/>
+      <c r="H807" s="2" t="s">
+        <v>2946</v>
+      </c>
     </row>
     <row r="808" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A808" s="2" t="s">
@@ -29262,7 +30274,9 @@
       <c r="G808" s="2">
         <v>9</v>
       </c>
-      <c r="H808" s="2"/>
+      <c r="H808" s="2" t="s">
+        <v>2946</v>
+      </c>
     </row>
     <row r="809" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A809" s="2" t="s">
@@ -29286,7 +30300,9 @@
       <c r="G809" s="2">
         <v>9</v>
       </c>
-      <c r="H809" s="2"/>
+      <c r="H809" s="2" t="s">
+        <v>2946</v>
+      </c>
     </row>
     <row r="810" spans="1:8" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A810" s="2" t="s">
@@ -29310,7 +30326,9 @@
       <c r="G810" s="2">
         <v>9</v>
       </c>
-      <c r="H810" s="2"/>
+      <c r="H810" s="2" t="s">
+        <v>2946</v>
+      </c>
     </row>
     <row r="811" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A811" s="2" t="s">
@@ -29334,7 +30352,9 @@
       <c r="G811" s="2">
         <v>9</v>
       </c>
-      <c r="H811" s="2"/>
+      <c r="H811" s="2" t="s">
+        <v>2945</v>
+      </c>
     </row>
     <row r="812" spans="1:8" ht="87" x14ac:dyDescent="0.35">
       <c r="A812" s="2" t="s">
@@ -29358,7 +30378,9 @@
       <c r="G812" s="2">
         <v>9</v>
       </c>
-      <c r="H812" s="2"/>
+      <c r="H812" s="2" t="s">
+        <v>2946</v>
+      </c>
     </row>
     <row r="813" spans="1:8" ht="58" x14ac:dyDescent="0.35">
       <c r="A813" s="2" t="s">
@@ -29382,7 +30404,9 @@
       <c r="G813" s="2">
         <v>9</v>
       </c>
-      <c r="H813" s="2"/>
+      <c r="H813" s="2" t="s">
+        <v>2946</v>
+      </c>
     </row>
     <row r="814" spans="1:8" ht="29" x14ac:dyDescent="0.35">
       <c r="A814" s="2" t="s">
@@ -29406,7 +30430,9 @@
       <c r="G814" s="2">
         <v>9</v>
       </c>
-      <c r="H814" s="2"/>
+      <c r="H814" s="2" t="s">
+        <v>2946</v>
+      </c>
     </row>
     <row r="815" spans="1:8" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A815" s="2" t="s">
@@ -29430,7 +30456,9 @@
       <c r="G815" s="2">
         <v>9</v>
       </c>
-      <c r="H815" s="2"/>
+      <c r="H815" s="2" t="s">
+        <v>2945</v>
+      </c>
     </row>
     <row r="816" spans="1:8" ht="72.5" x14ac:dyDescent="0.35">
       <c r="A816" s="2" t="s">
@@ -29454,7 +30482,9 @@
       <c r="G816" s="2">
         <v>9</v>
       </c>
-      <c r="H816" s="2"/>
+      <c r="H816" s="2" t="s">
+        <v>2946</v>
+      </c>
     </row>
     <row r="817" spans="1:8" ht="29" x14ac:dyDescent="0.35">
       <c r="A817" s="2" t="s">
@@ -29478,7 +30508,9 @@
       <c r="G817" s="2">
         <v>9</v>
       </c>
-      <c r="H817" s="2"/>
+      <c r="H817" s="2" t="s">
+        <v>2945</v>
+      </c>
     </row>
     <row r="818" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A818" s="2" t="s">
@@ -29502,7 +30534,9 @@
       <c r="G818" s="2">
         <v>9</v>
       </c>
-      <c r="H818" s="2"/>
+      <c r="H818" s="2" t="s">
+        <v>2945</v>
+      </c>
     </row>
     <row r="819" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A819" s="2" t="s">
@@ -29526,7 +30560,9 @@
       <c r="G819" s="2">
         <v>9</v>
       </c>
-      <c r="H819" s="2"/>
+      <c r="H819" s="2" t="s">
+        <v>2945</v>
+      </c>
     </row>
     <row r="820" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A820" s="2" t="s">
@@ -29550,7 +30586,9 @@
       <c r="G820" s="2">
         <v>9</v>
       </c>
-      <c r="H820" s="2"/>
+      <c r="H820" s="2" t="s">
+        <v>2946</v>
+      </c>
     </row>
     <row r="821" spans="1:8" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A821" s="2" t="s">
@@ -29574,7 +30612,9 @@
       <c r="G821" s="2">
         <v>9</v>
       </c>
-      <c r="H821" s="2"/>
+      <c r="H821" s="2" t="s">
+        <v>2945</v>
+      </c>
     </row>
     <row r="822" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A822" s="2" t="s">
@@ -29598,7 +30638,9 @@
       <c r="G822" s="2">
         <v>9</v>
       </c>
-      <c r="H822" s="2"/>
+      <c r="H822" s="2" t="s">
+        <v>2945</v>
+      </c>
     </row>
     <row r="823" spans="1:8" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A823" s="2" t="s">
@@ -29622,7 +30664,9 @@
       <c r="G823" s="2">
         <v>9</v>
       </c>
-      <c r="H823" s="2"/>
+      <c r="H823" s="2" t="s">
+        <v>2945</v>
+      </c>
     </row>
     <row r="824" spans="1:8" ht="29" x14ac:dyDescent="0.35">
       <c r="A824" s="2" t="s">
@@ -29646,7 +30690,9 @@
       <c r="G824" s="2">
         <v>9</v>
       </c>
-      <c r="H824" s="2"/>
+      <c r="H824" s="2">
+        <v>0</v>
+      </c>
     </row>
     <row r="825" spans="1:8" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A825" s="2" t="s">
@@ -29670,7 +30716,9 @@
       <c r="G825" s="2">
         <v>9</v>
       </c>
-      <c r="H825" s="2"/>
+      <c r="H825" s="2" t="s">
+        <v>2946</v>
+      </c>
     </row>
     <row r="826" spans="1:8" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A826" s="2" t="s">
@@ -29694,7 +30742,9 @@
       <c r="G826" s="2">
         <v>9</v>
       </c>
-      <c r="H826" s="2"/>
+      <c r="H826" s="2" t="s">
+        <v>2946</v>
+      </c>
     </row>
     <row r="827" spans="1:8" ht="29" x14ac:dyDescent="0.35">
       <c r="A827" s="2" t="s">
@@ -29718,7 +30768,9 @@
       <c r="G827" s="2">
         <v>9</v>
       </c>
-      <c r="H827" s="2"/>
+      <c r="H827" s="2" t="s">
+        <v>2946</v>
+      </c>
     </row>
     <row r="828" spans="1:8" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A828" s="2" t="s">
@@ -29742,7 +30794,9 @@
       <c r="G828" s="2">
         <v>9</v>
       </c>
-      <c r="H828" s="2"/>
+      <c r="H828" s="2" t="s">
+        <v>2945</v>
+      </c>
     </row>
     <row r="829" spans="1:8" ht="29" x14ac:dyDescent="0.35">
       <c r="A829" s="2" t="s">
@@ -29766,7 +30820,9 @@
       <c r="G829" s="2">
         <v>9</v>
       </c>
-      <c r="H829" s="2"/>
+      <c r="H829" s="2" t="s">
+        <v>2945</v>
+      </c>
     </row>
     <row r="830" spans="1:8" ht="29" x14ac:dyDescent="0.35">
       <c r="A830" s="2" t="s">
@@ -29790,7 +30846,9 @@
       <c r="G830" s="2">
         <v>9</v>
       </c>
-      <c r="H830" s="2"/>
+      <c r="H830" s="2" t="s">
+        <v>2946</v>
+      </c>
     </row>
     <row r="831" spans="1:8" ht="72.5" x14ac:dyDescent="0.35">
       <c r="A831" s="2" t="s">
@@ -29814,7 +30872,9 @@
       <c r="G831" s="2">
         <v>9</v>
       </c>
-      <c r="H831" s="2"/>
+      <c r="H831" s="2" t="s">
+        <v>2946</v>
+      </c>
     </row>
     <row r="832" spans="1:8" ht="29" x14ac:dyDescent="0.35">
       <c r="A832" s="2" t="s">
@@ -29838,7 +30898,9 @@
       <c r="G832" s="2">
         <v>9</v>
       </c>
-      <c r="H832" s="2"/>
+      <c r="H832" s="2" t="s">
+        <v>2946</v>
+      </c>
     </row>
     <row r="833" spans="1:8" ht="29" x14ac:dyDescent="0.35">
       <c r="A833" s="2" t="s">
@@ -29862,7 +30924,9 @@
       <c r="G833" s="2">
         <v>9</v>
       </c>
-      <c r="H833" s="2"/>
+      <c r="H833" s="2" t="s">
+        <v>2946</v>
+      </c>
     </row>
     <row r="834" spans="1:8" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A834" s="2" t="s">
@@ -29886,7 +30950,9 @@
       <c r="G834" s="2">
         <v>9</v>
       </c>
-      <c r="H834" s="2"/>
+      <c r="H834" s="2" t="s">
+        <v>2946</v>
+      </c>
     </row>
     <row r="835" spans="1:8" ht="29" x14ac:dyDescent="0.35">
       <c r="A835" s="2" t="s">
@@ -29910,7 +30976,9 @@
       <c r="G835" s="2">
         <v>9</v>
       </c>
-      <c r="H835" s="2"/>
+      <c r="H835" s="2" t="s">
+        <v>2946</v>
+      </c>
     </row>
     <row r="836" spans="1:8" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A836" s="2" t="s">
@@ -29934,7 +31002,9 @@
       <c r="G836" s="2">
         <v>9</v>
       </c>
-      <c r="H836" s="2"/>
+      <c r="H836" s="2" t="s">
+        <v>2946</v>
+      </c>
     </row>
     <row r="837" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A837" s="2" t="s">
@@ -29958,7 +31028,9 @@
       <c r="G837" s="2">
         <v>9</v>
       </c>
-      <c r="H837" s="2"/>
+      <c r="H837" s="2">
+        <v>0</v>
+      </c>
     </row>
     <row r="838" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A838" s="2" t="s">
@@ -29982,7 +31054,9 @@
       <c r="G838" s="2">
         <v>9</v>
       </c>
-      <c r="H838" s="2"/>
+      <c r="H838" s="2" t="s">
+        <v>2945</v>
+      </c>
     </row>
     <row r="839" spans="1:8" ht="29" x14ac:dyDescent="0.35">
       <c r="A839" s="2" t="s">
@@ -30006,7 +31080,9 @@
       <c r="G839" s="2">
         <v>9</v>
       </c>
-      <c r="H839" s="2"/>
+      <c r="H839" s="2" t="s">
+        <v>2945</v>
+      </c>
     </row>
     <row r="840" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A840" s="2" t="s">
@@ -30030,7 +31106,9 @@
       <c r="G840" s="2">
         <v>9</v>
       </c>
-      <c r="H840" s="2"/>
+      <c r="H840" s="2" t="s">
+        <v>2945</v>
+      </c>
     </row>
     <row r="841" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A841" s="2" t="s">
@@ -30054,7 +31132,9 @@
       <c r="G841" s="2">
         <v>9</v>
       </c>
-      <c r="H841" s="2"/>
+      <c r="H841" s="2" t="s">
+        <v>2945</v>
+      </c>
     </row>
     <row r="842" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A842" s="2" t="s">
@@ -30078,7 +31158,9 @@
       <c r="G842" s="2">
         <v>9</v>
       </c>
-      <c r="H842" s="2"/>
+      <c r="H842" s="2" t="s">
+        <v>2946</v>
+      </c>
     </row>
     <row r="843" spans="1:8" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A843" s="2" t="s">
@@ -30102,7 +31184,9 @@
       <c r="G843" s="2">
         <v>9</v>
       </c>
-      <c r="H843" s="2"/>
+      <c r="H843" s="2" t="s">
+        <v>2946</v>
+      </c>
     </row>
     <row r="844" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A844" s="2" t="s">
@@ -30126,7 +31210,9 @@
       <c r="G844" s="2">
         <v>9</v>
       </c>
-      <c r="H844" s="2"/>
+      <c r="H844" s="2" t="s">
+        <v>2946</v>
+      </c>
     </row>
     <row r="845" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A845" s="2" t="s">
@@ -30150,7 +31236,9 @@
       <c r="G845" s="2">
         <v>9</v>
       </c>
-      <c r="H845" s="2"/>
+      <c r="H845" s="2">
+        <v>0</v>
+      </c>
     </row>
     <row r="846" spans="1:8" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A846" s="2" t="s">
@@ -30174,7 +31262,9 @@
       <c r="G846" s="2">
         <v>9</v>
       </c>
-      <c r="H846" s="2"/>
+      <c r="H846" s="2" t="s">
+        <v>2946</v>
+      </c>
     </row>
     <row r="847" spans="1:8" ht="29" x14ac:dyDescent="0.35">
       <c r="A847" s="2" t="s">
@@ -30198,7 +31288,9 @@
       <c r="G847" s="2">
         <v>9</v>
       </c>
-      <c r="H847" s="2"/>
+      <c r="H847" s="2" t="s">
+        <v>2946</v>
+      </c>
     </row>
     <row r="848" spans="1:8" ht="72.5" x14ac:dyDescent="0.35">
       <c r="A848" s="2" t="s">
@@ -30222,7 +31314,9 @@
       <c r="G848" s="2">
         <v>9</v>
       </c>
-      <c r="H848" s="2"/>
+      <c r="H848" s="2">
+        <v>0</v>
+      </c>
     </row>
     <row r="849" spans="1:8" ht="29" x14ac:dyDescent="0.35">
       <c r="A849" s="2" t="s">
@@ -30246,7 +31340,9 @@
       <c r="G849" s="2">
         <v>9</v>
       </c>
-      <c r="H849" s="2"/>
+      <c r="H849" s="2" t="s">
+        <v>2945</v>
+      </c>
     </row>
     <row r="850" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A850" s="2" t="s">
@@ -30270,7 +31366,9 @@
       <c r="G850" s="2">
         <v>9</v>
       </c>
-      <c r="H850" s="2"/>
+      <c r="H850" s="2" t="s">
+        <v>2946</v>
+      </c>
     </row>
     <row r="851" spans="1:8" ht="58" x14ac:dyDescent="0.35">
       <c r="A851" s="2" t="s">
@@ -30294,7 +31392,9 @@
       <c r="G851" s="2">
         <v>9</v>
       </c>
-      <c r="H851" s="2"/>
+      <c r="H851" s="2" t="s">
+        <v>2946</v>
+      </c>
     </row>
     <row r="852" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A852" s="2" t="s">
@@ -30318,7 +31418,9 @@
       <c r="G852" s="2">
         <v>9</v>
       </c>
-      <c r="H852" s="2"/>
+      <c r="H852" s="2">
+        <v>0</v>
+      </c>
     </row>
     <row r="853" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A853" s="2" t="s">
@@ -30342,7 +31444,9 @@
       <c r="G853" s="2">
         <v>9</v>
       </c>
-      <c r="H853" s="2"/>
+      <c r="H853" s="2" t="s">
+        <v>2945</v>
+      </c>
     </row>
     <row r="854" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A854" s="2" t="s">
@@ -30366,7 +31470,9 @@
       <c r="G854" s="2">
         <v>9</v>
       </c>
-      <c r="H854" s="2"/>
+      <c r="H854" s="2" t="s">
+        <v>2945</v>
+      </c>
     </row>
     <row r="855" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A855" s="2" t="s">
@@ -30390,7 +31496,9 @@
       <c r="G855" s="2">
         <v>9</v>
       </c>
-      <c r="H855" s="2"/>
+      <c r="H855" s="2" t="s">
+        <v>2945</v>
+      </c>
     </row>
     <row r="856" spans="1:8" ht="58" x14ac:dyDescent="0.35">
       <c r="A856" s="2" t="s">
@@ -30414,7 +31522,9 @@
       <c r="G856" s="2">
         <v>9</v>
       </c>
-      <c r="H856" s="2"/>
+      <c r="H856" s="2" t="s">
+        <v>2946</v>
+      </c>
     </row>
     <row r="857" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A857" s="2" t="s">
@@ -30438,7 +31548,9 @@
       <c r="G857" s="2">
         <v>9</v>
       </c>
-      <c r="H857" s="2"/>
+      <c r="H857" s="2">
+        <v>0</v>
+      </c>
     </row>
     <row r="858" spans="1:8" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A858" s="2" t="s">
@@ -30462,7 +31574,9 @@
       <c r="G858" s="2">
         <v>9</v>
       </c>
-      <c r="H858" s="2"/>
+      <c r="H858" s="2" t="s">
+        <v>2946</v>
+      </c>
     </row>
     <row r="859" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A859" s="2" t="s">
@@ -30486,7 +31600,9 @@
       <c r="G859" s="2">
         <v>9</v>
       </c>
-      <c r="H859" s="2"/>
+      <c r="H859" s="2" t="s">
+        <v>2945</v>
+      </c>
     </row>
     <row r="860" spans="1:8" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A860" s="2" t="s">
@@ -30510,7 +31626,9 @@
       <c r="G860" s="2">
         <v>9</v>
       </c>
-      <c r="H860" s="2"/>
+      <c r="H860" s="2">
+        <v>0</v>
+      </c>
     </row>
     <row r="861" spans="1:8" ht="29" x14ac:dyDescent="0.35">
       <c r="A861" s="2" t="s">
@@ -30534,7 +31652,9 @@
       <c r="G861" s="2">
         <v>9</v>
       </c>
-      <c r="H861" s="2"/>
+      <c r="H861" s="2" t="s">
+        <v>2946</v>
+      </c>
     </row>
     <row r="862" spans="1:8" ht="29" x14ac:dyDescent="0.35">
       <c r="A862" s="2" t="s">
@@ -30558,7 +31678,9 @@
       <c r="G862" s="2">
         <v>9</v>
       </c>
-      <c r="H862" s="2"/>
+      <c r="H862" s="2" t="s">
+        <v>2946</v>
+      </c>
     </row>
     <row r="863" spans="1:8" ht="29" x14ac:dyDescent="0.35">
       <c r="A863" s="2" t="s">
@@ -30582,7 +31704,9 @@
       <c r="G863" s="2">
         <v>9</v>
       </c>
-      <c r="H863" s="2"/>
+      <c r="H863" s="2" t="s">
+        <v>2946</v>
+      </c>
     </row>
     <row r="864" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A864" s="2" t="s">
@@ -30606,7 +31730,9 @@
       <c r="G864" s="2">
         <v>9</v>
       </c>
-      <c r="H864" s="2"/>
+      <c r="H864" s="2" t="s">
+        <v>2945</v>
+      </c>
     </row>
     <row r="865" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A865" s="2" t="s">
@@ -30630,7 +31756,9 @@
       <c r="G865" s="2">
         <v>9</v>
       </c>
-      <c r="H865" s="2"/>
+      <c r="H865" s="2" t="s">
+        <v>2945</v>
+      </c>
     </row>
     <row r="866" spans="1:8" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A866" s="2" t="s">
@@ -30654,7 +31782,9 @@
       <c r="G866" s="2">
         <v>9</v>
       </c>
-      <c r="H866" s="2"/>
+      <c r="H866" s="2" t="s">
+        <v>2946</v>
+      </c>
     </row>
     <row r="867" spans="1:8" ht="29" x14ac:dyDescent="0.35">
       <c r="A867" s="2" t="s">
@@ -30678,7 +31808,9 @@
       <c r="G867" s="2">
         <v>9</v>
       </c>
-      <c r="H867" s="2"/>
+      <c r="H867" s="2" t="s">
+        <v>2946</v>
+      </c>
     </row>
     <row r="868" spans="1:8" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A868" s="2" t="s">
@@ -30702,7 +31834,9 @@
       <c r="G868" s="2">
         <v>9</v>
       </c>
-      <c r="H868" s="2"/>
+      <c r="H868" s="2" t="s">
+        <v>2946</v>
+      </c>
     </row>
     <row r="869" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A869" s="2" t="s">
@@ -30726,7 +31860,9 @@
       <c r="G869" s="2">
         <v>9</v>
       </c>
-      <c r="H869" s="2"/>
+      <c r="H869" s="2">
+        <v>0</v>
+      </c>
     </row>
     <row r="870" spans="1:8" ht="58" x14ac:dyDescent="0.35">
       <c r="A870" s="2" t="s">
@@ -30750,7 +31886,9 @@
       <c r="G870" s="2">
         <v>9</v>
       </c>
-      <c r="H870" s="2"/>
+      <c r="H870" s="2" t="s">
+        <v>2946</v>
+      </c>
     </row>
     <row r="871" spans="1:8" ht="29" x14ac:dyDescent="0.35">
       <c r="A871" s="2" t="s">
@@ -30774,7 +31912,9 @@
       <c r="G871" s="2">
         <v>9</v>
       </c>
-      <c r="H871" s="2"/>
+      <c r="H871" s="2" t="s">
+        <v>2946</v>
+      </c>
     </row>
     <row r="872" spans="1:8" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A872" s="2" t="s">
@@ -30798,7 +31938,9 @@
       <c r="G872" s="2">
         <v>9</v>
       </c>
-      <c r="H872" s="2"/>
+      <c r="H872" s="2" t="s">
+        <v>2945</v>
+      </c>
     </row>
     <row r="873" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A873" s="2" t="s">
@@ -30822,7 +31964,9 @@
       <c r="G873" s="2">
         <v>9</v>
       </c>
-      <c r="H873" s="2"/>
+      <c r="H873" s="2" t="s">
+        <v>2945</v>
+      </c>
     </row>
     <row r="874" spans="1:8" ht="29" x14ac:dyDescent="0.35">
       <c r="A874" s="2" t="s">
@@ -30846,7 +31990,9 @@
       <c r="G874" s="2">
         <v>9</v>
       </c>
-      <c r="H874" s="2"/>
+      <c r="H874" s="2" t="s">
+        <v>2946</v>
+      </c>
     </row>
     <row r="875" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A875" s="2" t="s">
@@ -30870,7 +32016,9 @@
       <c r="G875" s="2">
         <v>9</v>
       </c>
-      <c r="H875" s="2"/>
+      <c r="H875" s="2" t="s">
+        <v>2945</v>
+      </c>
     </row>
     <row r="876" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A876" s="2" t="s">
@@ -30894,7 +32042,9 @@
       <c r="G876" s="2">
         <v>9</v>
       </c>
-      <c r="H876" s="2"/>
+      <c r="H876" s="2" t="s">
+        <v>2945</v>
+      </c>
     </row>
     <row r="877" spans="1:8" ht="87" x14ac:dyDescent="0.35">
       <c r="A877" s="2" t="s">
@@ -30918,7 +32068,9 @@
       <c r="G877" s="2">
         <v>9</v>
       </c>
-      <c r="H877" s="2"/>
+      <c r="H877" s="2" t="s">
+        <v>2946</v>
+      </c>
     </row>
     <row r="878" spans="1:8" ht="29" x14ac:dyDescent="0.35">
       <c r="A878" s="2" t="s">
@@ -30942,7 +32094,9 @@
       <c r="G878" s="2">
         <v>9</v>
       </c>
-      <c r="H878" s="2"/>
+      <c r="H878" s="2" t="s">
+        <v>2946</v>
+      </c>
     </row>
     <row r="879" spans="1:8" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A879" s="2" t="s">
@@ -30966,7 +32120,9 @@
       <c r="G879" s="2">
         <v>9</v>
       </c>
-      <c r="H879" s="2"/>
+      <c r="H879" s="2" t="s">
+        <v>2946</v>
+      </c>
     </row>
     <row r="880" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A880" s="2" t="s">
@@ -30990,7 +32146,9 @@
       <c r="G880" s="2">
         <v>9</v>
       </c>
-      <c r="H880" s="2"/>
+      <c r="H880" s="2" t="s">
+        <v>2946</v>
+      </c>
     </row>
     <row r="881" spans="1:8" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A881" s="2" t="s">
@@ -31014,7 +32172,9 @@
       <c r="G881" s="2">
         <v>9</v>
       </c>
-      <c r="H881" s="2"/>
+      <c r="H881" s="2" t="s">
+        <v>2946</v>
+      </c>
     </row>
     <row r="882" spans="1:8" ht="29" x14ac:dyDescent="0.35">
       <c r="A882" s="2" t="s">
@@ -31038,7 +32198,9 @@
       <c r="G882" s="2">
         <v>9</v>
       </c>
-      <c r="H882" s="2"/>
+      <c r="H882" s="2">
+        <v>0</v>
+      </c>
     </row>
     <row r="883" spans="1:8" ht="72.5" x14ac:dyDescent="0.35">
       <c r="A883" s="2" t="s">
@@ -31062,7 +32224,9 @@
       <c r="G883" s="2">
         <v>9</v>
       </c>
-      <c r="H883" s="2"/>
+      <c r="H883" s="2" t="s">
+        <v>2946</v>
+      </c>
     </row>
     <row r="884" spans="1:8" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A884" s="2" t="s">
@@ -31086,7 +32250,9 @@
       <c r="G884" s="2">
         <v>9</v>
       </c>
-      <c r="H884" s="2"/>
+      <c r="H884" s="2" t="s">
+        <v>2946</v>
+      </c>
     </row>
     <row r="885" spans="1:8" ht="29" x14ac:dyDescent="0.35">
       <c r="A885" s="2" t="s">
@@ -31110,7 +32276,9 @@
       <c r="G885" s="2">
         <v>9</v>
       </c>
-      <c r="H885" s="2"/>
+      <c r="H885" s="2" t="s">
+        <v>2945</v>
+      </c>
     </row>
     <row r="886" spans="1:8" ht="29" x14ac:dyDescent="0.35">
       <c r="A886" s="2" t="s">
@@ -31134,7 +32302,9 @@
       <c r="G886" s="2">
         <v>9</v>
       </c>
-      <c r="H886" s="2"/>
+      <c r="H886" s="2" t="s">
+        <v>2946</v>
+      </c>
     </row>
     <row r="887" spans="1:8" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A887" s="2" t="s">
@@ -31158,7 +32328,9 @@
       <c r="G887" s="2">
         <v>9</v>
       </c>
-      <c r="H887" s="2"/>
+      <c r="H887" s="2" t="s">
+        <v>2946</v>
+      </c>
     </row>
     <row r="888" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A888" s="2" t="s">
@@ -31182,7 +32354,9 @@
       <c r="G888" s="2">
         <v>9</v>
       </c>
-      <c r="H888" s="2"/>
+      <c r="H888" s="2" t="s">
+        <v>2945</v>
+      </c>
     </row>
     <row r="889" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A889" s="2" t="s">
@@ -31206,7 +32380,9 @@
       <c r="G889" s="2">
         <v>9</v>
       </c>
-      <c r="H889" s="2"/>
+      <c r="H889" s="2" t="s">
+        <v>2945</v>
+      </c>
     </row>
     <row r="890" spans="1:8" ht="58" x14ac:dyDescent="0.35">
       <c r="A890" s="2" t="s">
@@ -31230,7 +32406,9 @@
       <c r="G890" s="2">
         <v>9</v>
       </c>
-      <c r="H890" s="2"/>
+      <c r="H890" s="2" t="s">
+        <v>2946</v>
+      </c>
     </row>
     <row r="891" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A891" s="2" t="s">
@@ -31254,7 +32432,9 @@
       <c r="G891" s="2">
         <v>9</v>
       </c>
-      <c r="H891" s="2"/>
+      <c r="H891" s="2" t="s">
+        <v>2946</v>
+      </c>
     </row>
     <row r="892" spans="1:8" ht="87" x14ac:dyDescent="0.35">
       <c r="A892" s="2" t="s">
@@ -31278,7 +32458,9 @@
       <c r="G892" s="2">
         <v>9</v>
       </c>
-      <c r="H892" s="2"/>
+      <c r="H892" s="2" t="s">
+        <v>2946</v>
+      </c>
     </row>
     <row r="893" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A893" s="2" t="s">
@@ -31302,7 +32484,9 @@
       <c r="G893" s="2">
         <v>9</v>
       </c>
-      <c r="H893" s="2"/>
+      <c r="H893" s="2" t="s">
+        <v>2945</v>
+      </c>
     </row>
     <row r="894" spans="1:8" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A894" s="2" t="s">
@@ -31326,7 +32510,9 @@
       <c r="G894" s="2">
         <v>9</v>
       </c>
-      <c r="H894" s="2"/>
+      <c r="H894" s="2" t="s">
+        <v>2946</v>
+      </c>
     </row>
     <row r="895" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A895" s="2" t="s">
@@ -31350,7 +32536,9 @@
       <c r="G895" s="2">
         <v>9</v>
       </c>
-      <c r="H895" s="2"/>
+      <c r="H895" s="2" t="s">
+        <v>2945</v>
+      </c>
     </row>
     <row r="896" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A896" s="2" t="s">
@@ -31374,7 +32562,9 @@
       <c r="G896" s="2">
         <v>9</v>
       </c>
-      <c r="H896" s="2"/>
+      <c r="H896" s="2" t="s">
+        <v>2945</v>
+      </c>
     </row>
     <row r="897" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A897" s="2" t="s">
@@ -31398,7 +32588,9 @@
       <c r="G897" s="2">
         <v>9</v>
       </c>
-      <c r="H897" s="2"/>
+      <c r="H897" s="2" t="s">
+        <v>2946</v>
+      </c>
     </row>
     <row r="898" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A898" s="2" t="s">
@@ -31422,7 +32614,9 @@
       <c r="G898" s="2">
         <v>9</v>
       </c>
-      <c r="H898" s="2"/>
+      <c r="H898" s="2" t="s">
+        <v>2945</v>
+      </c>
     </row>
     <row r="899" spans="1:8" ht="29" x14ac:dyDescent="0.35">
       <c r="A899" s="2" t="s">
@@ -31446,7 +32640,9 @@
       <c r="G899" s="2">
         <v>9</v>
       </c>
-      <c r="H899" s="2"/>
+      <c r="H899" s="2">
+        <v>0</v>
+      </c>
     </row>
     <row r="900" spans="1:8" ht="29" x14ac:dyDescent="0.35">
       <c r="A900" s="2" t="s">
@@ -31470,7 +32666,9 @@
       <c r="G900" s="2">
         <v>9</v>
       </c>
-      <c r="H900" s="2"/>
+      <c r="H900" s="2" t="s">
+        <v>2945</v>
+      </c>
     </row>
     <row r="901" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A901" s="2" t="s">
@@ -31494,7 +32692,9 @@
       <c r="G901" s="2">
         <v>9</v>
       </c>
-      <c r="H901" s="2"/>
+      <c r="H901" s="2" t="s">
+        <v>2946</v>
+      </c>
     </row>
     <row r="902" spans="1:8" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A902" s="2" t="s">
@@ -31518,7 +32718,9 @@
       <c r="G902" s="2">
         <v>10</v>
       </c>
-      <c r="H902" s="2"/>
+      <c r="H902" s="2" t="s">
+        <v>2946</v>
+      </c>
     </row>
     <row r="903" spans="1:8" ht="72.5" x14ac:dyDescent="0.35">
       <c r="A903" s="2" t="s">
@@ -31542,7 +32744,9 @@
       <c r="G903" s="2">
         <v>10</v>
       </c>
-      <c r="H903" s="2"/>
+      <c r="H903" s="2" t="s">
+        <v>2946</v>
+      </c>
     </row>
     <row r="904" spans="1:8" ht="58" x14ac:dyDescent="0.35">
       <c r="A904" s="2" t="s">
@@ -31566,7 +32770,9 @@
       <c r="G904" s="2">
         <v>10</v>
       </c>
-      <c r="H904" s="2"/>
+      <c r="H904" s="2" t="s">
+        <v>2946</v>
+      </c>
     </row>
     <row r="905" spans="1:8" ht="29" x14ac:dyDescent="0.35">
       <c r="A905" s="2" t="s">
@@ -31590,7 +32796,9 @@
       <c r="G905" s="2">
         <v>10</v>
       </c>
-      <c r="H905" s="2"/>
+      <c r="H905" s="2" t="s">
+        <v>2946</v>
+      </c>
     </row>
     <row r="906" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A906" s="2" t="s">
@@ -31614,7 +32822,9 @@
       <c r="G906" s="2">
         <v>10</v>
       </c>
-      <c r="H906" s="2"/>
+      <c r="H906" s="2" t="s">
+        <v>2945</v>
+      </c>
     </row>
     <row r="907" spans="1:8" ht="29" x14ac:dyDescent="0.35">
       <c r="A907" s="2" t="s">
@@ -31638,7 +32848,9 @@
       <c r="G907" s="2">
         <v>10</v>
       </c>
-      <c r="H907" s="2"/>
+      <c r="H907" s="2" t="s">
+        <v>2946</v>
+      </c>
     </row>
     <row r="908" spans="1:8" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A908" s="2" t="s">
@@ -31662,7 +32874,9 @@
       <c r="G908" s="2">
         <v>10</v>
       </c>
-      <c r="H908" s="2"/>
+      <c r="H908" s="2" t="s">
+        <v>2945</v>
+      </c>
     </row>
     <row r="909" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A909" s="2" t="s">
@@ -31686,7 +32900,9 @@
       <c r="G909" s="2">
         <v>10</v>
       </c>
-      <c r="H909" s="2"/>
+      <c r="H909" s="2" t="s">
+        <v>2945</v>
+      </c>
     </row>
     <row r="910" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A910" s="2" t="s">
@@ -31710,7 +32926,9 @@
       <c r="G910" s="2">
         <v>10</v>
       </c>
-      <c r="H910" s="2"/>
+      <c r="H910" s="2" t="s">
+        <v>2945</v>
+      </c>
     </row>
     <row r="911" spans="1:8" ht="29" x14ac:dyDescent="0.35">
       <c r="A911" s="2" t="s">
@@ -31734,7 +32952,9 @@
       <c r="G911" s="2">
         <v>10</v>
       </c>
-      <c r="H911" s="2"/>
+      <c r="H911" s="2" t="s">
+        <v>2946</v>
+      </c>
     </row>
     <row r="912" spans="1:8" ht="29" x14ac:dyDescent="0.35">
       <c r="A912" s="2" t="s">
@@ -31758,7 +32978,9 @@
       <c r="G912" s="2">
         <v>10</v>
       </c>
-      <c r="H912" s="2"/>
+      <c r="H912" s="2" t="s">
+        <v>2946</v>
+      </c>
     </row>
     <row r="913" spans="1:8" ht="29" x14ac:dyDescent="0.35">
       <c r="A913" s="2" t="s">
@@ -31782,7 +33004,9 @@
       <c r="G913" s="2">
         <v>10</v>
       </c>
-      <c r="H913" s="2"/>
+      <c r="H913" s="2" t="s">
+        <v>2946</v>
+      </c>
     </row>
     <row r="914" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A914" s="2" t="s">
@@ -31806,7 +33030,9 @@
       <c r="G914" s="2">
         <v>10</v>
       </c>
-      <c r="H914" s="2"/>
+      <c r="H914" s="2" t="s">
+        <v>2945</v>
+      </c>
     </row>
     <row r="915" spans="1:8" ht="29" x14ac:dyDescent="0.35">
       <c r="A915" s="2" t="s">
@@ -31830,7 +33056,9 @@
       <c r="G915" s="2">
         <v>10</v>
       </c>
-      <c r="H915" s="2"/>
+      <c r="H915" s="2" t="s">
+        <v>2945</v>
+      </c>
     </row>
     <row r="916" spans="1:8" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A916" s="2" t="s">
@@ -31854,7 +33082,9 @@
       <c r="G916" s="2">
         <v>10</v>
       </c>
-      <c r="H916" s="2"/>
+      <c r="H916" s="2" t="s">
+        <v>2946</v>
+      </c>
     </row>
     <row r="917" spans="1:8" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A917" s="2" t="s">
@@ -31878,7 +33108,9 @@
       <c r="G917" s="2">
         <v>10</v>
       </c>
-      <c r="H917" s="2"/>
+      <c r="H917" s="2" t="s">
+        <v>2945</v>
+      </c>
     </row>
     <row r="918" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A918" s="2" t="s">
@@ -31902,7 +33134,9 @@
       <c r="G918" s="2">
         <v>10</v>
       </c>
-      <c r="H918" s="2"/>
+      <c r="H918" s="2" t="s">
+        <v>2946</v>
+      </c>
     </row>
     <row r="919" spans="1:8" ht="29" x14ac:dyDescent="0.35">
       <c r="A919" s="2" t="s">
@@ -31926,7 +33160,9 @@
       <c r="G919" s="2">
         <v>10</v>
       </c>
-      <c r="H919" s="2"/>
+      <c r="H919" s="2" t="s">
+        <v>2946</v>
+      </c>
     </row>
     <row r="920" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A920" s="2" t="s">
@@ -31950,7 +33186,9 @@
       <c r="G920" s="2">
         <v>10</v>
       </c>
-      <c r="H920" s="2"/>
+      <c r="H920" s="2" t="s">
+        <v>2945</v>
+      </c>
     </row>
     <row r="921" spans="1:8" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A921" s="2" t="s">
@@ -31974,7 +33212,9 @@
       <c r="G921" s="2">
         <v>10</v>
       </c>
-      <c r="H921" s="2"/>
+      <c r="H921" s="2" t="s">
+        <v>2945</v>
+      </c>
     </row>
     <row r="922" spans="1:8" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A922" s="2" t="s">
@@ -31998,7 +33238,9 @@
       <c r="G922" s="2">
         <v>10</v>
       </c>
-      <c r="H922" s="2"/>
+      <c r="H922" s="2" t="s">
+        <v>2946</v>
+      </c>
     </row>
     <row r="923" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A923" s="2" t="s">
@@ -32022,7 +33264,9 @@
       <c r="G923" s="2">
         <v>10</v>
       </c>
-      <c r="H923" s="2"/>
+      <c r="H923" s="2" t="s">
+        <v>2946</v>
+      </c>
     </row>
     <row r="924" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A924" s="2" t="s">
@@ -32046,7 +33290,9 @@
       <c r="G924" s="2">
         <v>10</v>
       </c>
-      <c r="H924" s="2"/>
+      <c r="H924" s="2" t="s">
+        <v>2945</v>
+      </c>
     </row>
     <row r="925" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A925" s="2" t="s">
@@ -32070,7 +33316,9 @@
       <c r="G925" s="2">
         <v>10</v>
       </c>
-      <c r="H925" s="2"/>
+      <c r="H925" s="2" t="s">
+        <v>2946</v>
+      </c>
     </row>
     <row r="926" spans="1:8" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A926" s="2" t="s">
@@ -32094,7 +33342,9 @@
       <c r="G926" s="2">
         <v>10</v>
       </c>
-      <c r="H926" s="2"/>
+      <c r="H926" s="2" t="s">
+        <v>2946</v>
+      </c>
     </row>
     <row r="927" spans="1:8" ht="29" x14ac:dyDescent="0.35">
       <c r="A927" s="2" t="s">
@@ -32118,7 +33368,9 @@
       <c r="G927" s="2">
         <v>10</v>
       </c>
-      <c r="H927" s="2"/>
+      <c r="H927" s="2" t="s">
+        <v>2945</v>
+      </c>
     </row>
     <row r="928" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A928" s="2" t="s">
@@ -32142,7 +33394,9 @@
       <c r="G928" s="2">
         <v>10</v>
       </c>
-      <c r="H928" s="2"/>
+      <c r="H928" s="2" t="s">
+        <v>2946</v>
+      </c>
     </row>
     <row r="929" spans="1:8" ht="29" x14ac:dyDescent="0.35">
       <c r="A929" s="2" t="s">
@@ -32166,7 +33420,9 @@
       <c r="G929" s="2">
         <v>10</v>
       </c>
-      <c r="H929" s="2"/>
+      <c r="H929" s="2" t="s">
+        <v>2946</v>
+      </c>
     </row>
     <row r="930" spans="1:8" ht="29" x14ac:dyDescent="0.35">
       <c r="A930" s="2" t="s">
@@ -32190,7 +33446,9 @@
       <c r="G930" s="2">
         <v>10</v>
       </c>
-      <c r="H930" s="2"/>
+      <c r="H930" s="2" t="s">
+        <v>2946</v>
+      </c>
     </row>
     <row r="931" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A931" s="2" t="s">
@@ -32214,7 +33472,9 @@
       <c r="G931" s="2">
         <v>10</v>
       </c>
-      <c r="H931" s="2"/>
+      <c r="H931" s="2" t="s">
+        <v>2945</v>
+      </c>
     </row>
     <row r="932" spans="1:8" ht="29" x14ac:dyDescent="0.35">
       <c r="A932" s="2" t="s">
@@ -32238,7 +33498,9 @@
       <c r="G932" s="2">
         <v>10</v>
       </c>
-      <c r="H932" s="2"/>
+      <c r="H932" s="2" t="s">
+        <v>2945</v>
+      </c>
     </row>
     <row r="933" spans="1:8" ht="29" x14ac:dyDescent="0.35">
       <c r="A933" s="2" t="s">
@@ -32262,7 +33524,9 @@
       <c r="G933" s="2">
         <v>10</v>
       </c>
-      <c r="H933" s="2"/>
+      <c r="H933" s="2" t="s">
+        <v>2945</v>
+      </c>
     </row>
     <row r="934" spans="1:8" ht="87" x14ac:dyDescent="0.35">
       <c r="A934" s="2" t="s">
@@ -32286,7 +33550,9 @@
       <c r="G934" s="2">
         <v>10</v>
       </c>
-      <c r="H934" s="2"/>
+      <c r="H934" s="2">
+        <v>0</v>
+      </c>
     </row>
     <row r="935" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A935" s="2" t="s">
@@ -32310,7 +33576,9 @@
       <c r="G935" s="2">
         <v>10</v>
       </c>
-      <c r="H935" s="2"/>
+      <c r="H935" s="2" t="s">
+        <v>2946</v>
+      </c>
     </row>
     <row r="936" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A936" s="2" t="s">
@@ -32334,7 +33602,9 @@
       <c r="G936" s="2">
         <v>10</v>
       </c>
-      <c r="H936" s="2"/>
+      <c r="H936" s="2" t="s">
+        <v>2945</v>
+      </c>
     </row>
     <row r="937" spans="1:8" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A937" s="2" t="s">
@@ -32358,7 +33628,9 @@
       <c r="G937" s="2">
         <v>10</v>
       </c>
-      <c r="H937" s="2"/>
+      <c r="H937" s="2">
+        <v>0</v>
+      </c>
     </row>
     <row r="938" spans="1:8" ht="72.5" x14ac:dyDescent="0.35">
       <c r="A938" s="2" t="s">
@@ -32382,7 +33654,9 @@
       <c r="G938" s="2">
         <v>10</v>
       </c>
-      <c r="H938" s="2"/>
+      <c r="H938" s="2">
+        <v>0</v>
+      </c>
     </row>
     <row r="939" spans="1:8" ht="29" x14ac:dyDescent="0.35">
       <c r="A939" s="2" t="s">
@@ -32406,7 +33680,9 @@
       <c r="G939" s="2">
         <v>10</v>
       </c>
-      <c r="H939" s="2"/>
+      <c r="H939" s="2" t="s">
+        <v>2945</v>
+      </c>
     </row>
     <row r="940" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A940" s="2" t="s">
@@ -32430,7 +33706,9 @@
       <c r="G940" s="2">
         <v>10</v>
       </c>
-      <c r="H940" s="2"/>
+      <c r="H940" s="2" t="s">
+        <v>2946</v>
+      </c>
     </row>
     <row r="941" spans="1:8" ht="29" x14ac:dyDescent="0.35">
       <c r="A941" s="2" t="s">
@@ -32454,7 +33732,9 @@
       <c r="G941" s="2">
         <v>10</v>
       </c>
-      <c r="H941" s="2"/>
+      <c r="H941" s="2" t="s">
+        <v>2945</v>
+      </c>
     </row>
     <row r="942" spans="1:8" ht="29" x14ac:dyDescent="0.35">
       <c r="A942" s="2" t="s">
@@ -32478,7 +33758,9 @@
       <c r="G942" s="2">
         <v>10</v>
       </c>
-      <c r="H942" s="2"/>
+      <c r="H942" s="2" t="s">
+        <v>2946</v>
+      </c>
     </row>
     <row r="943" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A943" s="2" t="s">
@@ -32502,7 +33784,9 @@
       <c r="G943" s="2">
         <v>10</v>
       </c>
-      <c r="H943" s="2"/>
+      <c r="H943" s="2" t="s">
+        <v>2945</v>
+      </c>
     </row>
     <row r="944" spans="1:8" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A944" s="2" t="s">
@@ -32526,7 +33810,9 @@
       <c r="G944" s="2">
         <v>10</v>
       </c>
-      <c r="H944" s="2"/>
+      <c r="H944" s="2" t="s">
+        <v>2946</v>
+      </c>
     </row>
     <row r="945" spans="1:8" ht="58" x14ac:dyDescent="0.35">
       <c r="A945" s="2" t="s">
@@ -32550,7 +33836,9 @@
       <c r="G945" s="2">
         <v>10</v>
       </c>
-      <c r="H945" s="2"/>
+      <c r="H945" s="2" t="s">
+        <v>2946</v>
+      </c>
     </row>
     <row r="946" spans="1:8" ht="29" x14ac:dyDescent="0.35">
       <c r="A946" s="2" t="s">
@@ -32574,7 +33862,9 @@
       <c r="G946" s="2">
         <v>10</v>
       </c>
-      <c r="H946" s="2"/>
+      <c r="H946" s="2" t="s">
+        <v>2946</v>
+      </c>
     </row>
     <row r="947" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A947" s="2" t="s">
@@ -32598,7 +33888,9 @@
       <c r="G947" s="2">
         <v>10</v>
       </c>
-      <c r="H947" s="2"/>
+      <c r="H947" s="2" t="s">
+        <v>2946</v>
+      </c>
     </row>
     <row r="948" spans="1:8" ht="87" x14ac:dyDescent="0.35">
       <c r="A948" s="2" t="s">
@@ -32622,7 +33914,9 @@
       <c r="G948" s="2">
         <v>10</v>
       </c>
-      <c r="H948" s="2"/>
+      <c r="H948" s="2">
+        <v>0</v>
+      </c>
     </row>
     <row r="949" spans="1:8" ht="29" x14ac:dyDescent="0.35">
       <c r="A949" s="2" t="s">
@@ -32646,7 +33940,9 @@
       <c r="G949" s="2">
         <v>10</v>
       </c>
-      <c r="H949" s="2"/>
+      <c r="H949" s="2" t="s">
+        <v>2946</v>
+      </c>
     </row>
     <row r="950" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A950" s="2" t="s">
@@ -32670,7 +33966,9 @@
       <c r="G950" s="2">
         <v>10</v>
       </c>
-      <c r="H950" s="2"/>
+      <c r="H950" s="2" t="s">
+        <v>2945</v>
+      </c>
     </row>
     <row r="951" spans="1:8" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A951" s="2" t="s">
@@ -32694,7 +33992,9 @@
       <c r="G951" s="2">
         <v>10</v>
       </c>
-      <c r="H951" s="2"/>
+      <c r="H951" s="2" t="s">
+        <v>2946</v>
+      </c>
     </row>
     <row r="952" spans="1:8" ht="29" x14ac:dyDescent="0.35">
       <c r="A952" s="2" t="s">
@@ -32718,7 +34018,9 @@
       <c r="G952" s="2">
         <v>10</v>
       </c>
-      <c r="H952" s="2"/>
+      <c r="H952" s="2" t="s">
+        <v>2946</v>
+      </c>
     </row>
     <row r="953" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A953" s="2" t="s">
@@ -32742,7 +34044,9 @@
       <c r="G953" s="2">
         <v>10</v>
       </c>
-      <c r="H953" s="2"/>
+      <c r="H953" s="2" t="s">
+        <v>2946</v>
+      </c>
     </row>
     <row r="954" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A954" s="2" t="s">
@@ -32766,7 +34070,9 @@
       <c r="G954" s="2">
         <v>10</v>
       </c>
-      <c r="H954" s="2"/>
+      <c r="H954" s="2" t="s">
+        <v>2945</v>
+      </c>
     </row>
     <row r="955" spans="1:8" ht="29" x14ac:dyDescent="0.35">
       <c r="A955" s="2" t="s">
@@ -32790,7 +34096,9 @@
       <c r="G955" s="2">
         <v>10</v>
       </c>
-      <c r="H955" s="2"/>
+      <c r="H955" s="2" t="s">
+        <v>2946</v>
+      </c>
     </row>
     <row r="956" spans="1:8" ht="29" x14ac:dyDescent="0.35">
       <c r="A956" s="2" t="s">
@@ -32814,7 +34122,9 @@
       <c r="G956" s="2">
         <v>10</v>
       </c>
-      <c r="H956" s="2"/>
+      <c r="H956" s="2" t="s">
+        <v>2945</v>
+      </c>
     </row>
     <row r="957" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A957" s="2" t="s">
@@ -32838,7 +34148,9 @@
       <c r="G957" s="2">
         <v>10</v>
       </c>
-      <c r="H957" s="2"/>
+      <c r="H957" s="2" t="s">
+        <v>2945</v>
+      </c>
     </row>
     <row r="958" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A958" s="2" t="s">
@@ -32862,7 +34174,9 @@
       <c r="G958" s="2">
         <v>10</v>
       </c>
-      <c r="H958" s="2"/>
+      <c r="H958" s="2">
+        <v>0</v>
+      </c>
     </row>
     <row r="959" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A959" s="2" t="s">
@@ -32886,7 +34200,9 @@
       <c r="G959" s="2">
         <v>10</v>
       </c>
-      <c r="H959" s="2"/>
+      <c r="H959" s="2" t="s">
+        <v>2946</v>
+      </c>
     </row>
     <row r="960" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A960" s="2" t="s">
@@ -32910,7 +34226,9 @@
       <c r="G960" s="2">
         <v>10</v>
       </c>
-      <c r="H960" s="2"/>
+      <c r="H960" s="2" t="s">
+        <v>2945</v>
+      </c>
     </row>
     <row r="961" spans="1:8" ht="29" x14ac:dyDescent="0.35">
       <c r="A961" s="2" t="s">
@@ -32934,7 +34252,9 @@
       <c r="G961" s="2">
         <v>10</v>
       </c>
-      <c r="H961" s="2"/>
+      <c r="H961" s="2" t="s">
+        <v>2946</v>
+      </c>
     </row>
     <row r="962" spans="1:8" ht="29" x14ac:dyDescent="0.35">
       <c r="A962" s="2" t="s">
@@ -32958,7 +34278,9 @@
       <c r="G962" s="2">
         <v>10</v>
       </c>
-      <c r="H962" s="2"/>
+      <c r="H962" s="2" t="s">
+        <v>2946</v>
+      </c>
     </row>
     <row r="963" spans="1:8" ht="58" x14ac:dyDescent="0.35">
       <c r="A963" s="2" t="s">
@@ -32982,7 +34304,9 @@
       <c r="G963" s="2">
         <v>10</v>
       </c>
-      <c r="H963" s="2"/>
+      <c r="H963" s="2">
+        <v>0</v>
+      </c>
     </row>
     <row r="964" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A964" s="2" t="s">
@@ -33006,7 +34330,9 @@
       <c r="G964" s="2">
         <v>10</v>
       </c>
-      <c r="H964" s="2"/>
+      <c r="H964" s="2" t="s">
+        <v>2945</v>
+      </c>
     </row>
     <row r="965" spans="1:8" ht="29" x14ac:dyDescent="0.35">
       <c r="A965" s="2" t="s">
@@ -33030,7 +34356,9 @@
       <c r="G965" s="2">
         <v>10</v>
       </c>
-      <c r="H965" s="2"/>
+      <c r="H965" s="2" t="s">
+        <v>2946</v>
+      </c>
     </row>
     <row r="966" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A966" s="2" t="s">
@@ -33054,7 +34382,9 @@
       <c r="G966" s="2">
         <v>10</v>
       </c>
-      <c r="H966" s="2"/>
+      <c r="H966" s="2">
+        <v>0</v>
+      </c>
     </row>
     <row r="967" spans="1:8" ht="29" x14ac:dyDescent="0.35">
       <c r="A967" s="2" t="s">
@@ -33078,7 +34408,9 @@
       <c r="G967" s="2">
         <v>10</v>
       </c>
-      <c r="H967" s="2"/>
+      <c r="H967" s="2">
+        <v>0</v>
+      </c>
     </row>
     <row r="968" spans="1:8" ht="29" x14ac:dyDescent="0.35">
       <c r="A968" s="2" t="s">
@@ -33102,7 +34434,9 @@
       <c r="G968" s="2">
         <v>10</v>
       </c>
-      <c r="H968" s="2"/>
+      <c r="H968" s="2" t="s">
+        <v>2945</v>
+      </c>
     </row>
     <row r="969" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A969" s="2" t="s">
@@ -33126,7 +34460,9 @@
       <c r="G969" s="2">
         <v>10</v>
       </c>
-      <c r="H969" s="2"/>
+      <c r="H969" s="2">
+        <v>0</v>
+      </c>
     </row>
     <row r="970" spans="1:8" ht="29" x14ac:dyDescent="0.35">
       <c r="A970" s="2" t="s">
@@ -33150,7 +34486,9 @@
       <c r="G970" s="2">
         <v>10</v>
       </c>
-      <c r="H970" s="2"/>
+      <c r="H970" s="2" t="s">
+        <v>2946</v>
+      </c>
     </row>
     <row r="971" spans="1:8" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A971" s="2" t="s">
@@ -33174,7 +34512,9 @@
       <c r="G971" s="2">
         <v>10</v>
       </c>
-      <c r="H971" s="2"/>
+      <c r="H971" s="2">
+        <v>0</v>
+      </c>
     </row>
     <row r="972" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A972" s="2" t="s">
@@ -33198,7 +34538,9 @@
       <c r="G972" s="2">
         <v>10</v>
       </c>
-      <c r="H972" s="2"/>
+      <c r="H972" s="2" t="s">
+        <v>2945</v>
+      </c>
     </row>
     <row r="973" spans="1:8" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A973" s="2" t="s">
@@ -33222,7 +34564,9 @@
       <c r="G973" s="2">
         <v>10</v>
       </c>
-      <c r="H973" s="2"/>
+      <c r="H973" s="2" t="s">
+        <v>2946</v>
+      </c>
     </row>
     <row r="974" spans="1:8" ht="29" x14ac:dyDescent="0.35">
       <c r="A974" s="2" t="s">
@@ -33246,7 +34590,9 @@
       <c r="G974" s="2">
         <v>10</v>
       </c>
-      <c r="H974" s="2"/>
+      <c r="H974" s="2" t="s">
+        <v>2946</v>
+      </c>
     </row>
     <row r="975" spans="1:8" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A975" s="2" t="s">
@@ -33270,7 +34616,9 @@
       <c r="G975" s="2">
         <v>10</v>
       </c>
-      <c r="H975" s="2"/>
+      <c r="H975" s="2" t="s">
+        <v>2946</v>
+      </c>
     </row>
     <row r="976" spans="1:8" ht="29" x14ac:dyDescent="0.35">
       <c r="A976" s="2" t="s">
@@ -33294,7 +34642,9 @@
       <c r="G976" s="2">
         <v>10</v>
       </c>
-      <c r="H976" s="2"/>
+      <c r="H976" s="2" t="s">
+        <v>2946</v>
+      </c>
     </row>
     <row r="977" spans="1:8" ht="58" x14ac:dyDescent="0.35">
       <c r="A977" s="2" t="s">
@@ -33318,7 +34668,9 @@
       <c r="G977" s="2">
         <v>10</v>
       </c>
-      <c r="H977" s="2"/>
+      <c r="H977" s="2" t="s">
+        <v>2946</v>
+      </c>
     </row>
     <row r="978" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A978" s="2" t="s">
@@ -33342,7 +34694,9 @@
       <c r="G978" s="2">
         <v>10</v>
       </c>
-      <c r="H978" s="2"/>
+      <c r="H978" s="2" t="s">
+        <v>2946</v>
+      </c>
     </row>
     <row r="979" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A979" s="2" t="s">
@@ -33366,7 +34720,9 @@
       <c r="G979" s="2">
         <v>10</v>
       </c>
-      <c r="H979" s="2"/>
+      <c r="H979" s="2" t="s">
+        <v>2945</v>
+      </c>
     </row>
     <row r="980" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A980" s="2" t="s">
@@ -33390,7 +34746,9 @@
       <c r="G980" s="2">
         <v>10</v>
       </c>
-      <c r="H980" s="2"/>
+      <c r="H980" s="2" t="s">
+        <v>2945</v>
+      </c>
     </row>
     <row r="981" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A981" s="2" t="s">
@@ -33414,7 +34772,9 @@
       <c r="G981" s="2">
         <v>10</v>
       </c>
-      <c r="H981" s="2"/>
+      <c r="H981" s="2" t="s">
+        <v>2945</v>
+      </c>
     </row>
     <row r="982" spans="1:8" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A982" s="2" t="s">
@@ -33438,7 +34798,9 @@
       <c r="G982" s="2">
         <v>10</v>
       </c>
-      <c r="H982" s="2"/>
+      <c r="H982" s="2" t="s">
+        <v>2946</v>
+      </c>
     </row>
     <row r="983" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A983" s="2" t="s">
@@ -33462,7 +34824,9 @@
       <c r="G983" s="2">
         <v>10</v>
       </c>
-      <c r="H983" s="2"/>
+      <c r="H983" s="2" t="s">
+        <v>2946</v>
+      </c>
     </row>
     <row r="984" spans="1:8" ht="29" x14ac:dyDescent="0.35">
       <c r="A984" s="2" t="s">
@@ -33486,7 +34850,9 @@
       <c r="G984" s="2">
         <v>10</v>
       </c>
-      <c r="H984" s="2"/>
+      <c r="H984" s="2" t="s">
+        <v>2946</v>
+      </c>
     </row>
     <row r="985" spans="1:8" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A985" s="2" t="s">
@@ -33510,7 +34876,9 @@
       <c r="G985" s="2">
         <v>10</v>
       </c>
-      <c r="H985" s="2"/>
+      <c r="H985" s="2" t="s">
+        <v>2945</v>
+      </c>
     </row>
     <row r="986" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A986" s="2" t="s">
@@ -33534,7 +34902,9 @@
       <c r="G986" s="2">
         <v>10</v>
       </c>
-      <c r="H986" s="2"/>
+      <c r="H986" s="2" t="s">
+        <v>2945</v>
+      </c>
     </row>
     <row r="987" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A987" s="2" t="s">
@@ -33558,7 +34928,9 @@
       <c r="G987" s="2">
         <v>10</v>
       </c>
-      <c r="H987" s="2"/>
+      <c r="H987" s="2" t="s">
+        <v>2946</v>
+      </c>
     </row>
     <row r="988" spans="1:8" ht="29" x14ac:dyDescent="0.35">
       <c r="A988" s="2" t="s">
@@ -33582,7 +34954,9 @@
       <c r="G988" s="2">
         <v>10</v>
       </c>
-      <c r="H988" s="2"/>
+      <c r="H988" s="2" t="s">
+        <v>2946</v>
+      </c>
     </row>
     <row r="989" spans="1:8" ht="29" x14ac:dyDescent="0.35">
       <c r="A989" s="2" t="s">
@@ -33606,7 +34980,9 @@
       <c r="G989" s="2">
         <v>10</v>
       </c>
-      <c r="H989" s="2"/>
+      <c r="H989" s="2" t="s">
+        <v>2946</v>
+      </c>
     </row>
     <row r="990" spans="1:8" ht="58" x14ac:dyDescent="0.35">
       <c r="A990" s="2" t="s">
@@ -33630,7 +35006,9 @@
       <c r="G990" s="2">
         <v>10</v>
       </c>
-      <c r="H990" s="2"/>
+      <c r="H990" s="2">
+        <v>0</v>
+      </c>
     </row>
     <row r="991" spans="1:8" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A991" s="2" t="s">
@@ -33654,7 +35032,9 @@
       <c r="G991" s="2">
         <v>10</v>
       </c>
-      <c r="H991" s="2"/>
+      <c r="H991" s="2" t="s">
+        <v>2945</v>
+      </c>
     </row>
     <row r="992" spans="1:8" ht="29" x14ac:dyDescent="0.35">
       <c r="A992" s="2" t="s">
@@ -33678,7 +35058,9 @@
       <c r="G992" s="2">
         <v>10</v>
       </c>
-      <c r="H992" s="2"/>
+      <c r="H992" s="2" t="s">
+        <v>2945</v>
+      </c>
     </row>
     <row r="993" spans="1:8" ht="29" x14ac:dyDescent="0.35">
       <c r="A993" s="2" t="s">
@@ -33702,7 +35084,9 @@
       <c r="G993" s="2">
         <v>10</v>
       </c>
-      <c r="H993" s="2"/>
+      <c r="H993" s="2" t="s">
+        <v>2946</v>
+      </c>
     </row>
     <row r="994" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A994" s="2" t="s">
@@ -33726,7 +35110,9 @@
       <c r="G994" s="2">
         <v>10</v>
       </c>
-      <c r="H994" s="2"/>
+      <c r="H994" s="2" t="s">
+        <v>2946</v>
+      </c>
     </row>
     <row r="995" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A995" s="2" t="s">
@@ -33750,7 +35136,9 @@
       <c r="G995" s="2">
         <v>10</v>
       </c>
-      <c r="H995" s="2"/>
+      <c r="H995" s="2" t="s">
+        <v>2945</v>
+      </c>
     </row>
     <row r="996" spans="1:8" ht="29" x14ac:dyDescent="0.35">
       <c r="A996" s="2" t="s">
@@ -33774,7 +35162,9 @@
       <c r="G996" s="2">
         <v>10</v>
       </c>
-      <c r="H996" s="2"/>
+      <c r="H996" s="2" t="s">
+        <v>2945</v>
+      </c>
     </row>
     <row r="997" spans="1:8" ht="29" x14ac:dyDescent="0.35">
       <c r="A997" s="2" t="s">
@@ -33798,7 +35188,9 @@
       <c r="G997" s="2">
         <v>10</v>
       </c>
-      <c r="H997" s="2"/>
+      <c r="H997" s="2">
+        <v>0</v>
+      </c>
     </row>
     <row r="998" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A998" s="2" t="s">
@@ -33822,7 +35214,9 @@
       <c r="G998" s="2">
         <v>10</v>
       </c>
-      <c r="H998" s="2"/>
+      <c r="H998" s="2" t="s">
+        <v>2945</v>
+      </c>
     </row>
     <row r="999" spans="1:8" ht="29" x14ac:dyDescent="0.35">
       <c r="A999" s="2" t="s">
@@ -33846,7 +35240,9 @@
       <c r="G999" s="2">
         <v>10</v>
       </c>
-      <c r="H999" s="2"/>
+      <c r="H999" s="2">
+        <v>0</v>
+      </c>
     </row>
     <row r="1000" spans="1:8" ht="29" x14ac:dyDescent="0.35">
       <c r="A1000" s="2" t="s">
@@ -33870,7 +35266,9 @@
       <c r="G1000" s="2">
         <v>10</v>
       </c>
-      <c r="H1000" s="2"/>
+      <c r="H1000" s="2">
+        <v>0</v>
+      </c>
     </row>
     <row r="1001" spans="1:8" ht="29" x14ac:dyDescent="0.35">
       <c r="A1001" s="2" t="s">
@@ -33894,7 +35292,9 @@
       <c r="G1001" s="2">
         <v>10</v>
       </c>
-      <c r="H1001" s="2"/>
+      <c r="H1001" s="2">
+        <v>0</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
